--- a/data/issuer_financials.xlsx
+++ b/data/issuer_financials.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,6 +508,6598 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ЛИЗИНГОВАЯ КОМПАНИЯ ПРОСТЫЕ РЕШЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0278181110</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2194489</v>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>155122</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-2086627</v>
+      </c>
+      <c r="J2" t="n">
+        <v>463109</v>
+      </c>
+      <c r="K2" t="n">
+        <v>11391448</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3335362</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1453344</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5990866</v>
+      </c>
+      <c r="P2" t="n">
+        <v>3989488</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/508857</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "СЕЛИГДАР"</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1402047184</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>2544757</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>2167066</v>
+      </c>
+      <c r="I3" t="n">
+        <v>670497</v>
+      </c>
+      <c r="J3" t="n">
+        <v>9197581</v>
+      </c>
+      <c r="K3" t="n">
+        <v>117580865</v>
+      </c>
+      <c r="L3" t="n">
+        <v>34008934</v>
+      </c>
+      <c r="M3" t="n">
+        <v>9772454</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32871266</v>
+      </c>
+      <c r="O3" t="n">
+        <v>83540871</v>
+      </c>
+      <c r="P3" t="n">
+        <v>59226373</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3036741</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Новые технологии"</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1652009537</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>17547586</v>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>295278</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-2971495</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1026965</v>
+      </c>
+      <c r="K4" t="n">
+        <v>17051148</v>
+      </c>
+      <c r="L4" t="n">
+        <v>7664293</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3634189</v>
+      </c>
+      <c r="N4" t="n">
+        <v>2471937</v>
+      </c>
+      <c r="O4" t="n">
+        <v>14046469</v>
+      </c>
+      <c r="P4" t="n">
+        <v>15900789</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/316263</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Акционерное общество "ДЖИ-ГРУПП"</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1660359180</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>79082</v>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>8994</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-3456694</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1176954</v>
+      </c>
+      <c r="K5" t="n">
+        <v>8483318</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4983318</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2017862</v>
+      </c>
+      <c r="N5" t="n">
+        <v>29615697</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1366631</v>
+      </c>
+      <c r="P5" t="n">
+        <v>5134672</v>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11527158</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СЕЛО ЗЕЛЁНОЕ ХОЛДИНГ"</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1832043008</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>2734259</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>25300</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-508138</v>
+      </c>
+      <c r="J6" t="n">
+        <v>431176</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>704410</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1845908</v>
+      </c>
+      <c r="O6" t="n">
+        <v>704894</v>
+      </c>
+      <c r="P6" t="n">
+        <v>141640</v>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/1410574</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ "СЛУЖБА ЗАЩИТЫ АКТИВОВ"</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2310197022</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>429239</v>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>112977</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-710830</v>
+      </c>
+      <c r="J7" t="n">
+        <v>8123</v>
+      </c>
+      <c r="K7" t="n">
+        <v>865965</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7361</v>
+      </c>
+      <c r="M7" t="n">
+        <v>110563</v>
+      </c>
+      <c r="N7" t="n">
+        <v>303889</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1165803</v>
+      </c>
+      <c r="P7" t="n">
+        <v>62128</v>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10041570</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "МАГНИТ"</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2309085638</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>412062</v>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>5354640</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-52552646</v>
+      </c>
+      <c r="J8" t="n">
+        <v>623</v>
+      </c>
+      <c r="K8" t="n">
+        <v>378873287</v>
+      </c>
+      <c r="L8" t="n">
+        <v>200823287</v>
+      </c>
+      <c r="M8" t="n">
+        <v>49921724</v>
+      </c>
+      <c r="N8" t="n">
+        <v>213482646</v>
+      </c>
+      <c r="O8" t="n">
+        <v>351410295</v>
+      </c>
+      <c r="P8" t="n">
+        <v>205979865</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3644000</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Торговый дом РКС"</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2317084067</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>378077</v>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>28255</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-333069</v>
+      </c>
+      <c r="J9" t="n">
+        <v>156343</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3727499</v>
+      </c>
+      <c r="L9" t="n">
+        <v>950000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>184863</v>
+      </c>
+      <c r="N9" t="n">
+        <v>332485</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1447423</v>
+      </c>
+      <c r="P9" t="n">
+        <v>954306</v>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10121687</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Восточная Стивидорная Компания"</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2508064833</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>10029455</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="n">
+        <v>2896029</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2488486</v>
+      </c>
+      <c r="J10" t="n">
+        <v>266653</v>
+      </c>
+      <c r="K10" t="n">
+        <v>38468111</v>
+      </c>
+      <c r="L10" t="n">
+        <v>8468111</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4657692</v>
+      </c>
+      <c r="N10" t="n">
+        <v>72515756</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6880037</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9090610</v>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2926803</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Новабев Групп"</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>7705634425</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>3900773</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="n">
+        <v>3314072</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-2057228</v>
+      </c>
+      <c r="J11" t="n">
+        <v>438687</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21451914</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5201914</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2531399</v>
+      </c>
+      <c r="N11" t="n">
+        <v>20744863</v>
+      </c>
+      <c r="O11" t="n">
+        <v>8429304</v>
+      </c>
+      <c r="P11" t="n">
+        <v>7174938</v>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2815194</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ДЕЛЬТАЛИЗИНГ"</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2536247123</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>18325733</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>4366232</v>
+      </c>
+      <c r="I12" t="n">
+        <v>49238605</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2511568</v>
+      </c>
+      <c r="K12" t="n">
+        <v>42758726</v>
+      </c>
+      <c r="L12" t="n">
+        <v>22504345</v>
+      </c>
+      <c r="M12" t="n">
+        <v>8289186</v>
+      </c>
+      <c r="N12" t="n">
+        <v>18604665</v>
+      </c>
+      <c r="O12" t="n">
+        <v>32482684</v>
+      </c>
+      <c r="P12" t="n">
+        <v>28257955</v>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/983920</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>НЕПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ «ПЕРВОЕ КЛИЕНТСКОЕ БЮРО»</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2723115222</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>22501574</v>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="n">
+        <v>7200301</v>
+      </c>
+      <c r="I13" t="n">
+        <v>10878561</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1166700</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15825031</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2369260</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2984377</v>
+      </c>
+      <c r="N13" t="n">
+        <v>11636585</v>
+      </c>
+      <c r="O13" t="n">
+        <v>4307999</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3627580</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/540986</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ЭкоНива"</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3652904371</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>3053</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>484</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-45</v>
+      </c>
+      <c r="J14" t="n">
+        <v>269</v>
+      </c>
+      <c r="K14" t="n">
+        <v>256</v>
+      </c>
+      <c r="L14" t="n">
+        <v>256</v>
+      </c>
+      <c r="M14" t="n">
+        <v>6</v>
+      </c>
+      <c r="N14" t="n">
+        <v>9502040</v>
+      </c>
+      <c r="O14" t="n">
+        <v>6377</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6193</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12587302</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>МЕЖДУНАРОДНАЯ КОМПАНИЯ ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ЯНДЕКС"</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3900019850</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>87999120</v>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>825819172</v>
+      </c>
+      <c r="I15" t="n">
+        <v>58738057</v>
+      </c>
+      <c r="J15" t="n">
+        <v>267</v>
+      </c>
+      <c r="K15" t="n">
+        <v>105741950</v>
+      </c>
+      <c r="L15" t="n">
+        <v>741950</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7504950</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2623731887</v>
+      </c>
+      <c r="O15" t="n">
+        <v>37979183</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1428939</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12348996</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Международная компания Публичное акционерное общество "Озон"</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3900045916</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>194141</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>30319216</v>
+      </c>
+      <c r="I16" t="n">
+        <v>25025317</v>
+      </c>
+      <c r="J16" t="n">
+        <v>132739</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>152986102</v>
+      </c>
+      <c r="O16" t="n">
+        <v>7305844</v>
+      </c>
+      <c r="P16" t="n">
+        <v>5558853</v>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12758251</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Международная компания акционерное общество "Совко Капитал Партнерс"</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3906406196</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>10120977</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>-16741244</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1363704</v>
+      </c>
+      <c r="J17" t="n">
+        <v>201429</v>
+      </c>
+      <c r="K17" t="n">
+        <v>18185066</v>
+      </c>
+      <c r="L17" t="n">
+        <v>8185066</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3286537</v>
+      </c>
+      <c r="N17" t="n">
+        <v>239100426</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9096034</v>
+      </c>
+      <c r="P17" t="n">
+        <v>8329043</v>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11665010</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Акционерное общество Холдинговая Компания "Новотранс"</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4205119220</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>15304887</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>1996911</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2430012</v>
+      </c>
+      <c r="J18" t="n">
+        <v>5490568</v>
+      </c>
+      <c r="K18" t="n">
+        <v>74915074</v>
+      </c>
+      <c r="L18" t="n">
+        <v>28165074</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7737096</v>
+      </c>
+      <c r="N18" t="n">
+        <v>45825791</v>
+      </c>
+      <c r="O18" t="n">
+        <v>27374395</v>
+      </c>
+      <c r="P18" t="n">
+        <v>32659899</v>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/5896946</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВИС ФИНАНС"</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>4705081944</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>2500610</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>51321</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-7155471</v>
+      </c>
+      <c r="J19" t="n">
+        <v>70855</v>
+      </c>
+      <c r="K19" t="n">
+        <v>17082187</v>
+      </c>
+      <c r="L19" t="n">
+        <v>5115905</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="n">
+        <v>130206</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5391395</v>
+      </c>
+      <c r="P19" t="n">
+        <v>5119974</v>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11036812</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Россети Московский регион"</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5036065113</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>284566717</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>40035443</v>
+      </c>
+      <c r="I20" t="n">
+        <v>101669143</v>
+      </c>
+      <c r="J20" t="n">
+        <v>13365063</v>
+      </c>
+      <c r="K20" t="n">
+        <v>74030598</v>
+      </c>
+      <c r="L20" t="n">
+        <v>28570598</v>
+      </c>
+      <c r="M20" t="n">
+        <v>10096771</v>
+      </c>
+      <c r="N20" t="n">
+        <v>260977867</v>
+      </c>
+      <c r="O20" t="n">
+        <v>68802218</v>
+      </c>
+      <c r="P20" t="n">
+        <v>206694050</v>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4796897</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>АО "РОЛЬФ"</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5047254063</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>218583671</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>1597465</v>
+      </c>
+      <c r="I21" t="n">
+        <v>9766338</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3975641</v>
+      </c>
+      <c r="K21" t="n">
+        <v>15101967</v>
+      </c>
+      <c r="L21" t="n">
+        <v>11101967</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4637198</v>
+      </c>
+      <c r="N21" t="n">
+        <v>30249925</v>
+      </c>
+      <c r="O21" t="n">
+        <v>36790861</v>
+      </c>
+      <c r="P21" t="n">
+        <v>24454356</v>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11640744</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество ХЭНДЕРСОН ФЭШН ГРУПП</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>5047265516</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>1290000</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>1316065</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-751643</v>
+      </c>
+      <c r="J22" t="n">
+        <v>363666</v>
+      </c>
+      <c r="K22" t="n">
+        <v>1800954</v>
+      </c>
+      <c r="L22" t="n">
+        <v>954</v>
+      </c>
+      <c r="M22" t="n">
+        <v>202932</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4604956</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2813775</v>
+      </c>
+      <c r="P22" t="n">
+        <v>6213</v>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11895173</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>ПАО "АКРОН"</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>5321029508</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>171997329</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>52415054</v>
+      </c>
+      <c r="I23" t="n">
+        <v>25931936</v>
+      </c>
+      <c r="J23" t="n">
+        <v>11537385</v>
+      </c>
+      <c r="K23" t="n">
+        <v>135516907</v>
+      </c>
+      <c r="L23" t="n">
+        <v>63762318</v>
+      </c>
+      <c r="M23" t="n">
+        <v>18287531</v>
+      </c>
+      <c r="N23" t="n">
+        <v>190765693</v>
+      </c>
+      <c r="O23" t="n">
+        <v>74253156</v>
+      </c>
+      <c r="P23" t="n">
+        <v>90915954</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2347012</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО ПО СТРОИТЕЛЬСТВУ, РЕМОНТУ И СОДЕРЖАНИЮ АВТОМОБИЛЬНЫХ ДОРОГ И ИНЖЕНЕРНЫХ СООРУЖЕНИЙ "НОВОСИБИРСКАВТОДОР"</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5405162714</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>17966056</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
+        <v>433539</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1543133</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2598969</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5141662</v>
+      </c>
+      <c r="L24" t="n">
+        <v>3441662</v>
+      </c>
+      <c r="M24" t="n">
+        <v>1154039</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2066842</v>
+      </c>
+      <c r="O24" t="n">
+        <v>12008431</v>
+      </c>
+      <c r="P24" t="n">
+        <v>10712898</v>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6043515</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью профессиональная коллекторская организация "ЗАЩИТА ОНЛАЙН"</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>5407973637</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2905275</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>174936</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-496952</v>
+      </c>
+      <c r="J25" t="n">
+        <v>284500</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2598700</v>
+      </c>
+      <c r="L25" t="n">
+        <v>683714</v>
+      </c>
+      <c r="M25" t="n">
+        <v>410727</v>
+      </c>
+      <c r="N25" t="n">
+        <v>413426</v>
+      </c>
+      <c r="O25" t="n">
+        <v>3090052</v>
+      </c>
+      <c r="P25" t="n">
+        <v>928735</v>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10947263</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Уральская Сталь"</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>5607019523</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>105454369</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>-27277878</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1619940</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1224621</v>
+      </c>
+      <c r="K26" t="n">
+        <v>86309927</v>
+      </c>
+      <c r="L26" t="n">
+        <v>78357375</v>
+      </c>
+      <c r="M26" t="n">
+        <v>14118686</v>
+      </c>
+      <c r="N26" t="n">
+        <v>18618354</v>
+      </c>
+      <c r="O26" t="n">
+        <v>94532062</v>
+      </c>
+      <c r="P26" t="n">
+        <v>131566321</v>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4662411</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АТОМНЫЙ ЭНЕРГОПРОМЫШЛЕННЫЙ КОМПЛЕКС"</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>7706664260</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>5950351</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>-85699460</v>
+      </c>
+      <c r="I27" t="n">
+        <v>-219664013</v>
+      </c>
+      <c r="J27" t="n">
+        <v>55323672</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1446926765</v>
+      </c>
+      <c r="L27" t="n">
+        <v>738167987</v>
+      </c>
+      <c r="M27" t="n">
+        <v>221756065</v>
+      </c>
+      <c r="N27" t="n">
+        <v>1386949587</v>
+      </c>
+      <c r="O27" t="n">
+        <v>520700401</v>
+      </c>
+      <c r="P27" t="n">
+        <v>757359793</v>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6651267</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью профессиональная коллекторская организация "Вернём"</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>5611067262</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1656036</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>135809</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-443417</v>
+      </c>
+      <c r="J28" t="n">
+        <v>55363</v>
+      </c>
+      <c r="K28" t="n">
+        <v>1984195</v>
+      </c>
+      <c r="L28" t="n">
+        <v>1099128</v>
+      </c>
+      <c r="M28" t="n">
+        <v>459607</v>
+      </c>
+      <c r="N28" t="n">
+        <v>271169</v>
+      </c>
+      <c r="O28" t="n">
+        <v>2394072</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1179666</v>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7702700</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Брусника. Строительство и Девелопмент"</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>6685151087</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>11764</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>3669771</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-5014711</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1290</v>
+      </c>
+      <c r="K29" t="n">
+        <v>39379258</v>
+      </c>
+      <c r="L29" t="n">
+        <v>9100001</v>
+      </c>
+      <c r="M29" t="n">
+        <v>5650736</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10383538</v>
+      </c>
+      <c r="O29" t="n">
+        <v>19168970</v>
+      </c>
+      <c r="P29" t="n">
+        <v>10209840</v>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10736015</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "РОССЕТИ ЦЕНТР"</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6901067107</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>149813246</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>10155773</v>
+      </c>
+      <c r="I30" t="n">
+        <v>28796730</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6243096</v>
+      </c>
+      <c r="K30" t="n">
+        <v>36024622</v>
+      </c>
+      <c r="L30" t="n">
+        <v>13184718</v>
+      </c>
+      <c r="M30" t="n">
+        <v>6455777</v>
+      </c>
+      <c r="N30" t="n">
+        <v>72315825</v>
+      </c>
+      <c r="O30" t="n">
+        <v>26830525</v>
+      </c>
+      <c r="P30" t="n">
+        <v>51688362</v>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/1314752</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АПРИ"</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>7453326003</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>3058612</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>231140</v>
+      </c>
+      <c r="I31" t="n">
+        <v>15101</v>
+      </c>
+      <c r="J31" t="n">
+        <v>295040</v>
+      </c>
+      <c r="K31" t="n">
+        <v>11510301</v>
+      </c>
+      <c r="L31" t="n">
+        <v>5779169</v>
+      </c>
+      <c r="M31" t="n">
+        <v>94450</v>
+      </c>
+      <c r="N31" t="n">
+        <v>3695650</v>
+      </c>
+      <c r="O31" t="n">
+        <v>14512044</v>
+      </c>
+      <c r="P31" t="n">
+        <v>11821680</v>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10906877</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Элит Строй"</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>7204090319</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>1007045</v>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>2191316</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-1165538</v>
+      </c>
+      <c r="J32" t="n">
+        <v>669599</v>
+      </c>
+      <c r="K32" t="n">
+        <v>45970941</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1609540</v>
+      </c>
+      <c r="M32" t="n">
+        <v>4548151</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7071438</v>
+      </c>
+      <c r="O32" t="n">
+        <v>18014341</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1661048</v>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3504558</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "РОСАГРОЛИЗИНГ"</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>7704221591</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>31327555</v>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>1511285</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-15722941</v>
+      </c>
+      <c r="J33" t="n">
+        <v>5050692</v>
+      </c>
+      <c r="K33" t="n">
+        <v>138689053</v>
+      </c>
+      <c r="L33" t="n">
+        <v>56161430</v>
+      </c>
+      <c r="M33" t="n">
+        <v>23573052</v>
+      </c>
+      <c r="N33" t="n">
+        <v>113259877</v>
+      </c>
+      <c r="O33" t="n">
+        <v>75412579</v>
+      </c>
+      <c r="P33" t="n">
+        <v>65018097</v>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4547978</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Публичное Акционерное Общество "Территориальная генерирующая компания № 14"</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>7534018889</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>21333260</v>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>460944</v>
+      </c>
+      <c r="I34" t="n">
+        <v>3564527</v>
+      </c>
+      <c r="J34" t="n">
+        <v>8156340</v>
+      </c>
+      <c r="K34" t="n">
+        <v>19804235</v>
+      </c>
+      <c r="L34" t="n">
+        <v>5813933</v>
+      </c>
+      <c r="M34" t="n">
+        <v>2689720</v>
+      </c>
+      <c r="N34" t="n">
+        <v>8234169</v>
+      </c>
+      <c r="O34" t="n">
+        <v>12624099</v>
+      </c>
+      <c r="P34" t="n">
+        <v>12484258</v>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/1178818</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Акционерное общество "ПОЛИПЛАСТ"</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>7708186108</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>2672312</v>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>674988</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-6078380</v>
+      </c>
+      <c r="J35" t="n">
+        <v>958181</v>
+      </c>
+      <c r="K35" t="n">
+        <v>46531139</v>
+      </c>
+      <c r="L35" t="n">
+        <v>7980825</v>
+      </c>
+      <c r="M35" t="n">
+        <v>4460162</v>
+      </c>
+      <c r="N35" t="n">
+        <v>1054490</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10572743</v>
+      </c>
+      <c r="P35" t="n">
+        <v>8104372</v>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2277439</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ДелоПортс"</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>7706420120</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>124512</v>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>73553032</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-4022056</v>
+      </c>
+      <c r="J36" t="n">
+        <v>80452</v>
+      </c>
+      <c r="K36" t="n">
+        <v>63744005</v>
+      </c>
+      <c r="L36" t="n">
+        <v>22368376</v>
+      </c>
+      <c r="M36" t="n">
+        <v>11369181</v>
+      </c>
+      <c r="N36" t="n">
+        <v>88264659</v>
+      </c>
+      <c r="O36" t="n">
+        <v>22183196</v>
+      </c>
+      <c r="P36" t="n">
+        <v>22990992</v>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/9184684</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "А101"</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>7704810149</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>21202430</v>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>16040081</v>
+      </c>
+      <c r="I37" t="n">
+        <v>11327840</v>
+      </c>
+      <c r="J37" t="n">
+        <v>3944321</v>
+      </c>
+      <c r="K37" t="n">
+        <v>75879853</v>
+      </c>
+      <c r="L37" t="n">
+        <v>15570300</v>
+      </c>
+      <c r="M37" t="n">
+        <v>4121425</v>
+      </c>
+      <c r="N37" t="n">
+        <v>38081901</v>
+      </c>
+      <c r="O37" t="n">
+        <v>41317852</v>
+      </c>
+      <c r="P37" t="n">
+        <v>50340260</v>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/587902</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Эталон-Финанс"</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>7705619586</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>29228</v>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>2745058</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-7266612</v>
+      </c>
+      <c r="J38" t="n">
+        <v>110385</v>
+      </c>
+      <c r="K38" t="n">
+        <v>84443748</v>
+      </c>
+      <c r="L38" t="n">
+        <v>25203437</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8929388</v>
+      </c>
+      <c r="N38" t="n">
+        <v>35229067</v>
+      </c>
+      <c r="O38" t="n">
+        <v>4753665</v>
+      </c>
+      <c r="P38" t="n">
+        <v>25403641</v>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2380269</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "РЕСО-Лизинг"</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>7709431786</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>30347758</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>408506</v>
+      </c>
+      <c r="I39" t="n">
+        <v>36344239</v>
+      </c>
+      <c r="J39" t="n">
+        <v>17737597</v>
+      </c>
+      <c r="K39" t="n">
+        <v>94245992</v>
+      </c>
+      <c r="L39" t="n">
+        <v>52538388</v>
+      </c>
+      <c r="M39" t="n">
+        <v>18836863</v>
+      </c>
+      <c r="N39" t="n">
+        <v>25624330</v>
+      </c>
+      <c r="O39" t="n">
+        <v>73862867</v>
+      </c>
+      <c r="P39" t="n">
+        <v>60252372</v>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2464306</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АВТОБАН-ФИНАНС"</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>7708813750</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>2595484</v>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>8251</v>
+      </c>
+      <c r="I40" t="n">
+        <v>34686</v>
+      </c>
+      <c r="J40" t="n">
+        <v>52339</v>
+      </c>
+      <c r="K40" t="n">
+        <v>23223573</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8233755</v>
+      </c>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>71788</v>
+      </c>
+      <c r="O40" t="n">
+        <v>23322669</v>
+      </c>
+      <c r="P40" t="n">
+        <v>8266063</v>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/8573680</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "ФЕДЕРАЛЬНАЯ ПАССАЖИРСКАЯ КОМПАНИЯ"</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>7708709686</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>427758435</v>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>19596889</v>
+      </c>
+      <c r="I41" t="n">
+        <v>76910023</v>
+      </c>
+      <c r="J41" t="n">
+        <v>7774844</v>
+      </c>
+      <c r="K41" t="n">
+        <v>92653852</v>
+      </c>
+      <c r="L41" t="n">
+        <v>751192</v>
+      </c>
+      <c r="M41" t="n">
+        <v>13255112</v>
+      </c>
+      <c r="N41" t="n">
+        <v>293516869</v>
+      </c>
+      <c r="O41" t="n">
+        <v>43777290</v>
+      </c>
+      <c r="P41" t="n">
+        <v>72972691</v>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3615924</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ТРАНСКОНТЕЙНЕР"</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>7708591995</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>159888098</v>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="n">
+        <v>-9221825</v>
+      </c>
+      <c r="I42" t="n">
+        <v>-8853321</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1574985</v>
+      </c>
+      <c r="K42" t="n">
+        <v>125836199</v>
+      </c>
+      <c r="L42" t="n">
+        <v>61127838</v>
+      </c>
+      <c r="M42" t="n">
+        <v>24364741</v>
+      </c>
+      <c r="N42" t="n">
+        <v>15449282</v>
+      </c>
+      <c r="O42" t="n">
+        <v>36335898</v>
+      </c>
+      <c r="P42" t="n">
+        <v>82194584</v>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6412227</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВУШ"</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>9717068640</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>10694433</v>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="n">
+        <v>-2549955</v>
+      </c>
+      <c r="I43" t="n">
+        <v>213787</v>
+      </c>
+      <c r="J43" t="n">
+        <v>330829</v>
+      </c>
+      <c r="K43" t="n">
+        <v>13895537</v>
+      </c>
+      <c r="L43" t="n">
+        <v>4607881</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2583863</v>
+      </c>
+      <c r="N43" t="n">
+        <v>410758</v>
+      </c>
+      <c r="O43" t="n">
+        <v>4971431</v>
+      </c>
+      <c r="P43" t="n">
+        <v>5382399</v>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10703464</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьютиризация»</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>9704138298</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="n">
+        <v>-110007</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-2651331</v>
+      </c>
+      <c r="J44" t="n">
+        <v>465777</v>
+      </c>
+      <c r="K44" t="n">
+        <v>6436164</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1374585</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2595164</v>
+      </c>
+      <c r="N44" t="n">
+        <v>285806</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1960665</v>
+      </c>
+      <c r="P44" t="n">
+        <v>1374860</v>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11849209</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>ООО «СФО ВТБ РКС ЭТАЛОН»</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>9704147373</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="n">
+        <v>6112293</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-9926195</v>
+      </c>
+      <c r="J45" t="n">
+        <v>20467815</v>
+      </c>
+      <c r="K45" t="n">
+        <v>144460215</v>
+      </c>
+      <c r="L45" t="n">
+        <v>31592025</v>
+      </c>
+      <c r="M45" t="n">
+        <v>10095850</v>
+      </c>
+      <c r="N45" t="n">
+        <v>9955602</v>
+      </c>
+      <c r="O45" t="n">
+        <v>62360167</v>
+      </c>
+      <c r="P45" t="n">
+        <v>35761493</v>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11883254</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьюритизация 2»</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>9704160303</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="n">
+        <v>406160</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1846540</v>
+      </c>
+      <c r="J46" t="n">
+        <v>788495</v>
+      </c>
+      <c r="K46" t="n">
+        <v>10097440</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1629792</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1867484</v>
+      </c>
+      <c r="N46" t="n">
+        <v>406093</v>
+      </c>
+      <c r="O46" t="n">
+        <v>2587855</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1629933</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11930756</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>ООО "СОВКОМБАНК ЛИЗИНГ"</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>7709780434</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>23835197</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="n">
+        <v>522708</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-77248713</v>
+      </c>
+      <c r="J47" t="n">
+        <v>5979137</v>
+      </c>
+      <c r="K47" t="n">
+        <v>116313981</v>
+      </c>
+      <c r="L47" t="n">
+        <v>74703384</v>
+      </c>
+      <c r="M47" t="n">
+        <v>14436303</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6523589</v>
+      </c>
+      <c r="O47" t="n">
+        <v>52476129</v>
+      </c>
+      <c r="P47" t="n">
+        <v>81969714</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3727556</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "реСтор"</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>7709678550</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>22437973</v>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="n">
+        <v>-241871</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2508012</v>
+      </c>
+      <c r="J48" t="n">
+        <v>576677</v>
+      </c>
+      <c r="K48" t="n">
+        <v>3786701</v>
+      </c>
+      <c r="L48" t="n">
+        <v>2786701</v>
+      </c>
+      <c r="M48" t="n">
+        <v>1635073</v>
+      </c>
+      <c r="N48" t="n">
+        <v>4345419</v>
+      </c>
+      <c r="O48" t="n">
+        <v>8995976</v>
+      </c>
+      <c r="P48" t="n">
+        <v>5486584</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3032486</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>АО «Аэрофьюэлз»</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>7714216826</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>3728700</v>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="n">
+        <v>7332</v>
+      </c>
+      <c r="I49" t="n">
+        <v>120682</v>
+      </c>
+      <c r="J49" t="n">
+        <v>223096</v>
+      </c>
+      <c r="K49" t="n">
+        <v>8276872</v>
+      </c>
+      <c r="L49" t="n">
+        <v>1476872</v>
+      </c>
+      <c r="M49" t="n">
+        <v>1187691</v>
+      </c>
+      <c r="N49" t="n">
+        <v>612662</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2376107</v>
+      </c>
+      <c r="P49" t="n">
+        <v>3935053</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6619191</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АЭРОФЛОТ-РОССИЙСКИЕ АВИАЛИНИИ"</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>7712040126</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>760401133</v>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="n">
+        <v>123037451</v>
+      </c>
+      <c r="I50" t="n">
+        <v>37946658</v>
+      </c>
+      <c r="J50" t="n">
+        <v>29187913</v>
+      </c>
+      <c r="K50" t="n">
+        <v>176229912</v>
+      </c>
+      <c r="L50" t="n">
+        <v>36986045</v>
+      </c>
+      <c r="M50" t="n">
+        <v>39832097</v>
+      </c>
+      <c r="N50" t="n">
+        <v>26745345</v>
+      </c>
+      <c r="O50" t="n">
+        <v>244264335</v>
+      </c>
+      <c r="P50" t="n">
+        <v>311968276</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4444528</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Группа Черкизово"</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>7718560636</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>26760125</v>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="n">
+        <v>13328027</v>
+      </c>
+      <c r="I51" t="n">
+        <v>6647219</v>
+      </c>
+      <c r="J51" t="n">
+        <v>127133</v>
+      </c>
+      <c r="K51" t="n">
+        <v>42950184</v>
+      </c>
+      <c r="L51" t="n">
+        <v>10370584</v>
+      </c>
+      <c r="M51" t="n">
+        <v>6818015</v>
+      </c>
+      <c r="N51" t="n">
+        <v>42441028</v>
+      </c>
+      <c r="O51" t="n">
+        <v>75918407</v>
+      </c>
+      <c r="P51" t="n">
+        <v>14684828</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2165532</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ЭЛЕКТРОРЕШЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>7721403552</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>21521540</v>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="n">
+        <v>-223905</v>
+      </c>
+      <c r="I52" t="n">
+        <v>1089672</v>
+      </c>
+      <c r="J52" t="n">
+        <v>1697179</v>
+      </c>
+      <c r="K52" t="n">
+        <v>6168848</v>
+      </c>
+      <c r="L52" t="n">
+        <v>4705327</v>
+      </c>
+      <c r="M52" t="n">
+        <v>1289262</v>
+      </c>
+      <c r="N52" t="n">
+        <v>3672686</v>
+      </c>
+      <c r="O52" t="n">
+        <v>14337129</v>
+      </c>
+      <c r="P52" t="n">
+        <v>12398474</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/9558270</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ИКС 5 ФИНАНС"</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>7715630469</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="n">
+        <v>824259</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-68407</v>
+      </c>
+      <c r="J53" t="n">
+        <v>4174</v>
+      </c>
+      <c r="K53" t="n">
+        <v>202529873</v>
+      </c>
+      <c r="L53" t="n">
+        <v>78821657</v>
+      </c>
+      <c r="M53" t="n">
+        <v>29610326</v>
+      </c>
+      <c r="N53" t="n">
+        <v>5109696</v>
+      </c>
+      <c r="O53" t="n">
+        <v>79069557</v>
+      </c>
+      <c r="P53" t="n">
+        <v>79066163</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3294399</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>ГОСУДАРСТВЕННАЯ КОМПАНИЯ "РОССИЙСКИЕ АВТОМОБИЛЬНЫЕ ДОРОГИ"</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>7717151380</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="n">
+        <v>88803615</v>
+      </c>
+      <c r="K54" t="n">
+        <v>874623492</v>
+      </c>
+      <c r="L54" t="n">
+        <v>105867965</v>
+      </c>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="n">
+        <v>1188643663</v>
+      </c>
+      <c r="P54" t="n">
+        <v>137612078</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2363264</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "ПЕРВАЯ ГРУЗОВАЯ КОМПАНИЯ"</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>7725806898</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>127694204</v>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="n">
+        <v>21069621</v>
+      </c>
+      <c r="I55" t="n">
+        <v>38744345</v>
+      </c>
+      <c r="J55" t="n">
+        <v>10957889</v>
+      </c>
+      <c r="K55" t="n">
+        <v>127579859</v>
+      </c>
+      <c r="L55" t="n">
+        <v>13549979</v>
+      </c>
+      <c r="M55" t="n">
+        <v>27469731</v>
+      </c>
+      <c r="N55" t="n">
+        <v>76257726</v>
+      </c>
+      <c r="O55" t="n">
+        <v>68782080</v>
+      </c>
+      <c r="P55" t="n">
+        <v>40312889</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/8153588</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ГАЗПРОМ КАПИТАЛ"</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>7726588547</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>255587508</v>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="n">
+        <v>47477495</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-93259357</v>
+      </c>
+      <c r="J56" t="n">
+        <v>2</v>
+      </c>
+      <c r="K56" t="n">
+        <v>1816745257</v>
+      </c>
+      <c r="L56" t="n">
+        <v>234030896</v>
+      </c>
+      <c r="M56" t="n">
+        <v>199460449</v>
+      </c>
+      <c r="N56" t="n">
+        <v>1517919504</v>
+      </c>
+      <c r="O56" t="n">
+        <v>345060152</v>
+      </c>
+      <c r="P56" t="n">
+        <v>234152191</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3280371</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "АЙДИ КОЛЛЕКТ"</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>7730233723</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F57" t="n">
+        <v>13385777</v>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="n">
+        <v>2822485</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-4653393</v>
+      </c>
+      <c r="J57" t="n">
+        <v>905627</v>
+      </c>
+      <c r="K57" t="n">
+        <v>20833978</v>
+      </c>
+      <c r="L57" t="n">
+        <v>9616449</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3590318</v>
+      </c>
+      <c r="N57" t="n">
+        <v>6388641</v>
+      </c>
+      <c r="O57" t="n">
+        <v>25146186</v>
+      </c>
+      <c r="P57" t="n">
+        <v>9957816</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10178314</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Сибур Холдинг"</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>7727547261</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F58" t="n">
+        <v>1161179501</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="n">
+        <v>176772395</v>
+      </c>
+      <c r="I58" t="n">
+        <v>27705480</v>
+      </c>
+      <c r="J58" t="n">
+        <v>132919086</v>
+      </c>
+      <c r="K58" t="n">
+        <v>1085975337</v>
+      </c>
+      <c r="L58" t="n">
+        <v>168385812</v>
+      </c>
+      <c r="M58" t="n">
+        <v>133854196</v>
+      </c>
+      <c r="N58" t="n">
+        <v>1000189134</v>
+      </c>
+      <c r="O58" t="n">
+        <v>494671950</v>
+      </c>
+      <c r="P58" t="n">
+        <v>475585507</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4918019</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Селектел"</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>7810962785</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>16049975</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="n">
+        <v>2783286</v>
+      </c>
+      <c r="I59" t="n">
+        <v>4083327</v>
+      </c>
+      <c r="J59" t="n">
+        <v>603311</v>
+      </c>
+      <c r="K59" t="n">
+        <v>18736466</v>
+      </c>
+      <c r="L59" t="n">
+        <v>7416234</v>
+      </c>
+      <c r="M59" t="n">
+        <v>2693274</v>
+      </c>
+      <c r="N59" t="n">
+        <v>4668499</v>
+      </c>
+      <c r="O59" t="n">
+        <v>2366382</v>
+      </c>
+      <c r="P59" t="n">
+        <v>12799984</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12489652</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Акционерное общество "АСФАЛЬТОБЕТОННЫЙ ЗАВОД № 1"</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>7804016807</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>9221435</v>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="n">
+        <v>740510</v>
+      </c>
+      <c r="I60" t="n">
+        <v>-2235493</v>
+      </c>
+      <c r="J60" t="n">
+        <v>2733758</v>
+      </c>
+      <c r="K60" t="n">
+        <v>11859777</v>
+      </c>
+      <c r="L60" t="n">
+        <v>2519772</v>
+      </c>
+      <c r="M60" t="n">
+        <v>1548669</v>
+      </c>
+      <c r="N60" t="n">
+        <v>4129194</v>
+      </c>
+      <c r="O60" t="n">
+        <v>16016256</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3422702</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6492191</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "ФосАгро"</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>7736216869</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>65994934</v>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="n">
+        <v>72557476</v>
+      </c>
+      <c r="I61" t="n">
+        <v>33253943</v>
+      </c>
+      <c r="J61" t="n">
+        <v>102857</v>
+      </c>
+      <c r="K61" t="n">
+        <v>237249564</v>
+      </c>
+      <c r="L61" t="n">
+        <v>120519682</v>
+      </c>
+      <c r="M61" t="n">
+        <v>24591473</v>
+      </c>
+      <c r="N61" t="n">
+        <v>82626377</v>
+      </c>
+      <c r="O61" t="n">
+        <v>183614926</v>
+      </c>
+      <c r="P61" t="n">
+        <v>132846377</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4499052</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Софтлайн"</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>7736227885</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>26297499</v>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="n">
+        <v>262302</v>
+      </c>
+      <c r="I62" t="n">
+        <v>-7996798</v>
+      </c>
+      <c r="J62" t="n">
+        <v>1989588</v>
+      </c>
+      <c r="K62" t="n">
+        <v>24815793</v>
+      </c>
+      <c r="L62" t="n">
+        <v>24815793</v>
+      </c>
+      <c r="M62" t="n">
+        <v>4907477</v>
+      </c>
+      <c r="N62" t="n">
+        <v>22994710</v>
+      </c>
+      <c r="O62" t="n">
+        <v>58488360</v>
+      </c>
+      <c r="P62" t="n">
+        <v>37832470</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7152470</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "МЕДСКАН"</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>7736328675</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>114398</v>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="n">
+        <v>-1954241</v>
+      </c>
+      <c r="I63" t="n">
+        <v>-3463650</v>
+      </c>
+      <c r="J63" t="n">
+        <v>210293</v>
+      </c>
+      <c r="K63" t="n">
+        <v>10883764</v>
+      </c>
+      <c r="L63" t="n">
+        <v>2438241</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1905512</v>
+      </c>
+      <c r="N63" t="n">
+        <v>11167761</v>
+      </c>
+      <c r="O63" t="n">
+        <v>4303532</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2667429</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11352704</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Мобильные ТелеСистемы"</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>7740000076</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F64" t="n">
+        <v>476837411</v>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="n">
+        <v>26025836</v>
+      </c>
+      <c r="I64" t="n">
+        <v>66160709</v>
+      </c>
+      <c r="J64" t="n">
+        <v>7076512</v>
+      </c>
+      <c r="K64" t="n">
+        <v>975762072</v>
+      </c>
+      <c r="L64" t="n">
+        <v>394064198</v>
+      </c>
+      <c r="M64" t="n">
+        <v>183657184</v>
+      </c>
+      <c r="N64" t="n">
+        <v>126241392</v>
+      </c>
+      <c r="O64" t="n">
+        <v>140594093</v>
+      </c>
+      <c r="P64" t="n">
+        <v>646413416</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7155648</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ИНТЕРЛИЗИНГ"</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>7802131219</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>15617549</v>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="n">
+        <v>1360216</v>
+      </c>
+      <c r="I65" t="n">
+        <v>12804691</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3411231</v>
+      </c>
+      <c r="K65" t="n">
+        <v>46966786</v>
+      </c>
+      <c r="L65" t="n">
+        <v>30193215</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="n">
+        <v>16029601</v>
+      </c>
+      <c r="O65" t="n">
+        <v>36280782</v>
+      </c>
+      <c r="P65" t="n">
+        <v>37865717</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6475614</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Россети Ленэнерго"</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>7803002209</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>142913416</v>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="n">
+        <v>34251000</v>
+      </c>
+      <c r="I66" t="n">
+        <v>73224364</v>
+      </c>
+      <c r="J66" t="n">
+        <v>48361489</v>
+      </c>
+      <c r="K66" t="n">
+        <v>26560960</v>
+      </c>
+      <c r="L66" t="n">
+        <v>16560960</v>
+      </c>
+      <c r="M66" t="n">
+        <v>385713</v>
+      </c>
+      <c r="N66" t="n">
+        <v>233316079</v>
+      </c>
+      <c r="O66" t="n">
+        <v>66874847</v>
+      </c>
+      <c r="P66" t="n">
+        <v>76842723</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7044724</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Публичное Акционерное Общество "Инарктика"</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>7816430057</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>1410028</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="n">
+        <v>1130289</v>
+      </c>
+      <c r="I67" t="n">
+        <v>45720</v>
+      </c>
+      <c r="J67" t="n">
+        <v>700723</v>
+      </c>
+      <c r="K67" t="n">
+        <v>10047195</v>
+      </c>
+      <c r="L67" t="n">
+        <v>47195</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1091903</v>
+      </c>
+      <c r="N67" t="n">
+        <v>11973285</v>
+      </c>
+      <c r="O67" t="n">
+        <v>2177851</v>
+      </c>
+      <c r="P67" t="n">
+        <v>69325</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/112740</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>АО ЛК "РОДЕЛЕН"</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>7813379412</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>1348020</v>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="n">
+        <v>151933</v>
+      </c>
+      <c r="I68" t="n">
+        <v>1991103</v>
+      </c>
+      <c r="J68" t="n">
+        <v>426055</v>
+      </c>
+      <c r="K68" t="n">
+        <v>6411813</v>
+      </c>
+      <c r="L68" t="n">
+        <v>53039</v>
+      </c>
+      <c r="M68" t="n">
+        <v>1136499</v>
+      </c>
+      <c r="N68" t="n">
+        <v>754993</v>
+      </c>
+      <c r="O68" t="n">
+        <v>6587642</v>
+      </c>
+      <c r="P68" t="n">
+        <v>613953</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6099662</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Акционерное общество "Первый контейнерный терминал"</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>7805113497</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>6203239</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="n">
+        <v>1407136</v>
+      </c>
+      <c r="I69" t="n">
+        <v>-128768</v>
+      </c>
+      <c r="J69" t="n">
+        <v>652569</v>
+      </c>
+      <c r="K69" t="n">
+        <v>14147311</v>
+      </c>
+      <c r="L69" t="n">
+        <v>255384</v>
+      </c>
+      <c r="M69" t="n">
+        <v>2032410</v>
+      </c>
+      <c r="N69" t="n">
+        <v>8678846</v>
+      </c>
+      <c r="O69" t="n">
+        <v>1289863</v>
+      </c>
+      <c r="P69" t="n">
+        <v>753349</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7066135</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Сэтл Групп"</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>7810245481</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>13167515</v>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="n">
+        <v>11312897</v>
+      </c>
+      <c r="I70" t="n">
+        <v>1184853</v>
+      </c>
+      <c r="J70" t="n">
+        <v>1345291</v>
+      </c>
+      <c r="K70" t="n">
+        <v>56921724</v>
+      </c>
+      <c r="L70" t="n">
+        <v>15976724</v>
+      </c>
+      <c r="M70" t="n">
+        <v>8935923</v>
+      </c>
+      <c r="N70" t="n">
+        <v>15386096</v>
+      </c>
+      <c r="O70" t="n">
+        <v>29645490</v>
+      </c>
+      <c r="P70" t="n">
+        <v>22550613</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7065187</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>АО ГК "АЗОТ"</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>7838365595</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>2571736</v>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="n">
+        <v>36420149</v>
+      </c>
+      <c r="I71" t="n">
+        <v>-1732698</v>
+      </c>
+      <c r="J71" t="n">
+        <v>29984</v>
+      </c>
+      <c r="K71" t="n">
+        <v>1141544</v>
+      </c>
+      <c r="L71" t="n">
+        <v>141544</v>
+      </c>
+      <c r="M71" t="n">
+        <v>508238</v>
+      </c>
+      <c r="N71" t="n">
+        <v>32473493</v>
+      </c>
+      <c r="O71" t="n">
+        <v>24407949</v>
+      </c>
+      <c r="P71" t="n">
+        <v>3776569</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4460769</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Группа ЛСР"</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>7838360491</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>18527068</v>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="n">
+        <v>9609955</v>
+      </c>
+      <c r="I72" t="n">
+        <v>-26787483</v>
+      </c>
+      <c r="J72" t="n">
+        <v>2273568</v>
+      </c>
+      <c r="K72" t="n">
+        <v>165830803</v>
+      </c>
+      <c r="L72" t="n">
+        <v>28617745</v>
+      </c>
+      <c r="M72" t="n">
+        <v>22629744</v>
+      </c>
+      <c r="N72" t="n">
+        <v>135293714</v>
+      </c>
+      <c r="O72" t="n">
+        <v>33615684</v>
+      </c>
+      <c r="P72" t="n">
+        <v>30329614</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4288365</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БАЛТИЙСКИЙ ЛИЗИНГ"</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>7826705374</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>45104129</v>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="n">
+        <v>2466201</v>
+      </c>
+      <c r="I73" t="n">
+        <v>-4449111</v>
+      </c>
+      <c r="J73" t="n">
+        <v>6963921</v>
+      </c>
+      <c r="K73" t="n">
+        <v>165574135</v>
+      </c>
+      <c r="L73" t="n">
+        <v>93653647</v>
+      </c>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="n">
+        <v>23274827</v>
+      </c>
+      <c r="O73" t="n">
+        <v>87273492</v>
+      </c>
+      <c r="P73" t="n">
+        <v>103980085</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4075359</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Арлифт Интернешнл"</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>7820331348</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>5457083</v>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="n">
+        <v>520734</v>
+      </c>
+      <c r="I74" t="n">
+        <v>1663667</v>
+      </c>
+      <c r="J74" t="n">
+        <v>109268</v>
+      </c>
+      <c r="K74" t="n">
+        <v>128239</v>
+      </c>
+      <c r="L74" t="n">
+        <v>102399</v>
+      </c>
+      <c r="M74" t="n">
+        <v>987970</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1208716</v>
+      </c>
+      <c r="O74" t="n">
+        <v>2219692</v>
+      </c>
+      <c r="P74" t="n">
+        <v>3792606</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7720538</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГЛОРАКС"</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>9729387137</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>3057693</v>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="n">
+        <v>352891</v>
+      </c>
+      <c r="I75" t="n">
+        <v>-2487508</v>
+      </c>
+      <c r="J75" t="n">
+        <v>17468</v>
+      </c>
+      <c r="K75" t="n">
+        <v>15888211</v>
+      </c>
+      <c r="L75" t="n">
+        <v>7131352</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3563226</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5262202</v>
+      </c>
+      <c r="O75" t="n">
+        <v>9887498</v>
+      </c>
+      <c r="P75" t="n">
+        <v>7607515</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12558009</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГРУППА ПОЗИТИВ"</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>9718077239</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
+        <v>-2319012</v>
+      </c>
+      <c r="I76" t="n">
+        <v>-3043148</v>
+      </c>
+      <c r="J76" t="n">
+        <v>85073</v>
+      </c>
+      <c r="K76" t="n">
+        <v>20333431</v>
+      </c>
+      <c r="L76" t="n">
+        <v>533431</v>
+      </c>
+      <c r="M76" t="n">
+        <v>3093490</v>
+      </c>
+      <c r="N76" t="n">
+        <v>14618010</v>
+      </c>
+      <c r="O76" t="n">
+        <v>6251325</v>
+      </c>
+      <c r="P76" t="n">
+        <v>542917</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10388722</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "КАРШЕРИНГ РУССИЯ"</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>9718236471</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>26088727</v>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="n">
+        <v>-3628694</v>
+      </c>
+      <c r="I77" t="n">
+        <v>6086337</v>
+      </c>
+      <c r="J77" t="n">
+        <v>1230217</v>
+      </c>
+      <c r="K77" t="n">
+        <v>18535372</v>
+      </c>
+      <c r="L77" t="n">
+        <v>10535372</v>
+      </c>
+      <c r="M77" t="n">
+        <v>5647179</v>
+      </c>
+      <c r="N77" t="n">
+        <v>6060673</v>
+      </c>
+      <c r="O77" t="n">
+        <v>6682880</v>
+      </c>
+      <c r="P77" t="n">
+        <v>17515458</v>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12289607</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ФАБРИКА ПО"</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>9726092897</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="n">
+        <v>26111</v>
+      </c>
+      <c r="I78" t="n">
+        <v>-116300</v>
+      </c>
+      <c r="J78" t="n">
+        <v>58920</v>
+      </c>
+      <c r="K78" t="n">
+        <v>2012480</v>
+      </c>
+      <c r="L78" t="n">
+        <v>1961794</v>
+      </c>
+      <c r="M78" t="n">
+        <v>94487</v>
+      </c>
+      <c r="N78" t="n">
+        <v>15655004</v>
+      </c>
+      <c r="O78" t="n">
+        <v>3749182</v>
+      </c>
+      <c r="P78" t="n">
+        <v>3460790</v>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12624794</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Профессиональная коллекторская организация "Агентство судебного взыскания"</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>7841019595</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>2813950</v>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="n">
+        <v>289449</v>
+      </c>
+      <c r="I79" t="n">
+        <v>-782507</v>
+      </c>
+      <c r="J79" t="n">
+        <v>439421</v>
+      </c>
+      <c r="K79" t="n">
+        <v>3335265</v>
+      </c>
+      <c r="L79" t="n">
+        <v>1661751</v>
+      </c>
+      <c r="M79" t="n">
+        <v>634394</v>
+      </c>
+      <c r="N79" t="n">
+        <v>718092</v>
+      </c>
+      <c r="O79" t="n">
+        <v>4036728</v>
+      </c>
+      <c r="P79" t="n">
+        <v>1804336</v>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/9111808</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ЛЕГЕНДА"</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>7840438730</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>2574338</v>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="n">
+        <v>676819</v>
+      </c>
+      <c r="I80" t="n">
+        <v>1424991</v>
+      </c>
+      <c r="J80" t="n">
+        <v>2369150</v>
+      </c>
+      <c r="K80" t="n">
+        <v>13269288</v>
+      </c>
+      <c r="L80" t="n">
+        <v>5143359</v>
+      </c>
+      <c r="M80" t="n">
+        <v>1792096</v>
+      </c>
+      <c r="N80" t="n">
+        <v>988224</v>
+      </c>
+      <c r="O80" t="n">
+        <v>7760068</v>
+      </c>
+      <c r="P80" t="n">
+        <v>5682975</v>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/122728</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "Филберт"</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>7841430420</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>8586868</v>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="n">
+        <v>3152859</v>
+      </c>
+      <c r="I81" t="n">
+        <v>-2961381</v>
+      </c>
+      <c r="J81" t="n">
+        <v>130669</v>
+      </c>
+      <c r="K81" t="n">
+        <v>4275711</v>
+      </c>
+      <c r="L81" t="n">
+        <v>2275535</v>
+      </c>
+      <c r="M81" t="n">
+        <v>560901</v>
+      </c>
+      <c r="N81" t="n">
+        <v>9134906</v>
+      </c>
+      <c r="O81" t="n">
+        <v>13555399</v>
+      </c>
+      <c r="P81" t="n">
+        <v>2486647</v>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/1655225</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "МВ ФИНАНС"</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>9701168311</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="n">
+        <v>3493</v>
+      </c>
+      <c r="I82" t="n">
+        <v>-2391603</v>
+      </c>
+      <c r="J82" t="n">
+        <v>44911</v>
+      </c>
+      <c r="K82" t="n">
+        <v>7725451</v>
+      </c>
+      <c r="L82" t="n">
+        <v>5759320</v>
+      </c>
+      <c r="M82" t="n">
+        <v>2261066</v>
+      </c>
+      <c r="N82" t="n">
+        <v>95811</v>
+      </c>
+      <c r="O82" t="n">
+        <v>5828974</v>
+      </c>
+      <c r="P82" t="n">
+        <v>5765046</v>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11476959</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Специализированное финансовое общество ТБ-5"</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>9703206788</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="n">
+        <v>627562</v>
+      </c>
+      <c r="I83" t="n">
+        <v>2054</v>
+      </c>
+      <c r="J83" t="n">
+        <v>2567719</v>
+      </c>
+      <c r="K83" t="n">
+        <v>16587377</v>
+      </c>
+      <c r="L83" t="n">
+        <v>336877</v>
+      </c>
+      <c r="M83" t="n">
+        <v>337763</v>
+      </c>
+      <c r="N83" t="n">
+        <v>627572</v>
+      </c>
+      <c r="O83" t="n">
+        <v>6522558</v>
+      </c>
+      <c r="P83" t="n">
+        <v>636777</v>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12646488</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ГРУППА КОМПАНИЙ "СЕГЕЖА"</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>9703024202</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>3234274</v>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="n">
+        <v>-81659202</v>
+      </c>
+      <c r="I84" t="n">
+        <v>-15560254</v>
+      </c>
+      <c r="J84" t="n">
+        <v>2171160</v>
+      </c>
+      <c r="K84" t="n">
+        <v>68989930</v>
+      </c>
+      <c r="L84" t="n">
+        <v>28619951</v>
+      </c>
+      <c r="M84" t="n">
+        <v>17966508</v>
+      </c>
+      <c r="N84" t="n">
+        <v>69901335</v>
+      </c>
+      <c r="O84" t="n">
+        <v>16693441</v>
+      </c>
+      <c r="P84" t="n">
+        <v>29540756</v>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11477936</t>
+        </is>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО "СБ СЕКЬЮРИТИЗАЦИЯ 5"</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>9703163693</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="n">
+        <v>-65</v>
+      </c>
+      <c r="I85" t="n">
+        <v>-266</v>
+      </c>
+      <c r="J85" t="n">
+        <v>13</v>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="n">
+        <v>13</v>
+      </c>
+      <c r="O85" t="n">
+        <v>13</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12333197</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Совком Секьюр"</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>9703193909</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="n">
+        <v>764758</v>
+      </c>
+      <c r="I86" t="n">
+        <v>35192</v>
+      </c>
+      <c r="J86" t="n">
+        <v>1286080</v>
+      </c>
+      <c r="K86" t="n">
+        <v>10632078</v>
+      </c>
+      <c r="L86" t="n">
+        <v>3400068</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1853940</v>
+      </c>
+      <c r="N86" t="n">
+        <v>764768</v>
+      </c>
+      <c r="O86" t="n">
+        <v>5356352</v>
+      </c>
+      <c r="P86" t="n">
+        <v>3590518</v>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12558868</t>
+        </is>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-4"</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>9703211185</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
+        <v>977720</v>
+      </c>
+      <c r="I87" t="n">
+        <v>-1274588</v>
+      </c>
+      <c r="J87" t="n">
+        <v>2631244</v>
+      </c>
+      <c r="K87" t="n">
+        <v>20526472</v>
+      </c>
+      <c r="L87" t="n">
+        <v>4223028</v>
+      </c>
+      <c r="M87" t="n">
+        <v>1495620</v>
+      </c>
+      <c r="N87" t="n">
+        <v>977730</v>
+      </c>
+      <c r="O87" t="n">
+        <v>7130263</v>
+      </c>
+      <c r="P87" t="n">
+        <v>4225049</v>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12680884</t>
+        </is>
+      </c>
+      <c r="R87" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Сплит Финанс"</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>9703209122</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="n">
+        <v>832800</v>
+      </c>
+      <c r="I88" t="n">
+        <v>-627668</v>
+      </c>
+      <c r="J88" t="n">
+        <v>3157507</v>
+      </c>
+      <c r="K88" t="n">
+        <v>12321587</v>
+      </c>
+      <c r="L88" t="n">
+        <v>4622403</v>
+      </c>
+      <c r="M88" t="n">
+        <v>794736</v>
+      </c>
+      <c r="N88" t="n">
+        <v>832810</v>
+      </c>
+      <c r="O88" t="n">
+        <v>10288657</v>
+      </c>
+      <c r="P88" t="n">
+        <v>4649009</v>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12663922</t>
+        </is>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-6"</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>9703221553</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="n">
+        <v>421691</v>
+      </c>
+      <c r="I89" t="n">
+        <v>-16243</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1996969</v>
+      </c>
+      <c r="K89" t="n">
+        <v>31400566</v>
+      </c>
+      <c r="L89" t="n">
+        <v>191416</v>
+      </c>
+      <c r="M89" t="n">
+        <v>191760</v>
+      </c>
+      <c r="N89" t="n">
+        <v>421701</v>
+      </c>
+      <c r="O89" t="n">
+        <v>11406621</v>
+      </c>
+      <c r="P89" t="n">
+        <v>592089</v>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12744848</t>
+        </is>
+      </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>ООО «БИННОФАРМ ГРУПП»</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>9704005675</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>39152023</v>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="n">
+        <v>-3437553</v>
+      </c>
+      <c r="I90" t="n">
+        <v>-10088180</v>
+      </c>
+      <c r="J90" t="n">
+        <v>2741369</v>
+      </c>
+      <c r="K90" t="n">
+        <v>31048484</v>
+      </c>
+      <c r="L90" t="n">
+        <v>27198484</v>
+      </c>
+      <c r="M90" t="n">
+        <v>6612689</v>
+      </c>
+      <c r="N90" t="n">
+        <v>28187621</v>
+      </c>
+      <c r="O90" t="n">
+        <v>49838344</v>
+      </c>
+      <c r="P90" t="n">
+        <v>65495561</v>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11181494</t>
+        </is>
+      </c>
+      <c r="R90" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "ЛИЗИНГОВАЯ КОМПАНИЯ ПРОСТЫЕ РЕШЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>278181110</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>2194489</v>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="n">
+        <v>155122</v>
+      </c>
+      <c r="I91" t="n">
+        <v>-2086627</v>
+      </c>
+      <c r="J91" t="n">
+        <v>463109</v>
+      </c>
+      <c r="K91" t="n">
+        <v>11391448</v>
+      </c>
+      <c r="L91" t="n">
+        <v>3335362</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="n">
+        <v>1453344</v>
+      </c>
+      <c r="O91" t="n">
+        <v>5990866</v>
+      </c>
+      <c r="P91" t="n">
+        <v>3989488</v>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/508857</t>
+        </is>
+      </c>
+      <c r="R91" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БОРЕЦ КАПИТАЛ"</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>9731098069</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1023</v>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="n">
+        <v>5086</v>
+      </c>
+      <c r="I92" t="n">
+        <v>-8655</v>
+      </c>
+      <c r="J92" t="n">
+        <v>219</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" t="n">
+        <v>25</v>
+      </c>
+      <c r="N92" t="n">
+        <v>223227</v>
+      </c>
+      <c r="O92" t="n">
+        <v>33333869</v>
+      </c>
+      <c r="P92" t="n">
+        <v>33311146</v>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/11927098</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Публичное Акционерное общество "Лизинговая компания "Европлан"</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>9705101614</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>59966125</v>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="n">
+        <v>4034508</v>
+      </c>
+      <c r="I93" t="n">
+        <v>84799387</v>
+      </c>
+      <c r="J93" t="n">
+        <v>7477939</v>
+      </c>
+      <c r="K93" t="n">
+        <v>136124027</v>
+      </c>
+      <c r="L93" t="n">
+        <v>73233527</v>
+      </c>
+      <c r="M93" t="n">
+        <v>35514645</v>
+      </c>
+      <c r="N93" t="n">
+        <v>36127674</v>
+      </c>
+      <c r="O93" t="n">
+        <v>113385304</v>
+      </c>
+      <c r="P93" t="n">
+        <v>85482683</v>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/10283154</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-1"</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>9704256936</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="n">
+        <v>462857</v>
+      </c>
+      <c r="I94" t="n">
+        <v>-690900</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1467792</v>
+      </c>
+      <c r="K94" t="n">
+        <v>12652034</v>
+      </c>
+      <c r="L94" t="n">
+        <v>2707767</v>
+      </c>
+      <c r="M94" t="n">
+        <v>740205</v>
+      </c>
+      <c r="N94" t="n">
+        <v>462867</v>
+      </c>
+      <c r="O94" t="n">
+        <v>4761718</v>
+      </c>
+      <c r="P94" t="n">
+        <v>2710789</v>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12624837</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО СБ СЕКЬЮРИТИЗАЦИЯ 3"</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>9704262880</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="n">
+        <v>867964</v>
+      </c>
+      <c r="I95" t="n">
+        <v>-10844</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1901818</v>
+      </c>
+      <c r="K95" t="n">
+        <v>22434769</v>
+      </c>
+      <c r="L95" t="n">
+        <v>2918653</v>
+      </c>
+      <c r="M95" t="n">
+        <v>268761</v>
+      </c>
+      <c r="N95" t="n">
+        <v>867973</v>
+      </c>
+      <c r="O95" t="n">
+        <v>5010242</v>
+      </c>
+      <c r="P95" t="n">
+        <v>2921170</v>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12724282</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-2"</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>9704264662</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="n">
+        <v>966</v>
+      </c>
+      <c r="I96" t="n">
+        <v>-439</v>
+      </c>
+      <c r="J96" t="n">
+        <v>2571</v>
+      </c>
+      <c r="K96" t="n">
+        <v>3133</v>
+      </c>
+      <c r="L96" t="n">
+        <v>3133</v>
+      </c>
+      <c r="M96" t="n">
+        <v>133</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-956</v>
+      </c>
+      <c r="O96" t="n">
+        <v>2571</v>
+      </c>
+      <c r="P96" t="n">
+        <v>3527</v>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/12755483</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ ООО "ХРОМОС ИНЖИНИРИНГ"</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>5249111131</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1997642</v>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="n">
+        <v>405970</v>
+      </c>
+      <c r="I97" t="n">
+        <v>94073</v>
+      </c>
+      <c r="J97" t="n">
+        <v>231941</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1379142</v>
+      </c>
+      <c r="L97" t="n">
+        <v>318550</v>
+      </c>
+      <c r="M97" t="n">
+        <v>138385</v>
+      </c>
+      <c r="N97" t="n">
+        <v>792684</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2488601</v>
+      </c>
+      <c r="P97" t="n">
+        <v>1259493</v>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2992692</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "О'КЕЙ"</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>7826087713</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>150619116</v>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="n">
+        <v>-1361960</v>
+      </c>
+      <c r="I98" t="n">
+        <v>7127898</v>
+      </c>
+      <c r="J98" t="n">
+        <v>5313318</v>
+      </c>
+      <c r="K98" t="n">
+        <v>53888334</v>
+      </c>
+      <c r="L98" t="n">
+        <v>13010079</v>
+      </c>
+      <c r="M98" t="n">
+        <v>9853935</v>
+      </c>
+      <c r="N98" t="n">
+        <v>9520347</v>
+      </c>
+      <c r="O98" t="n">
+        <v>36805981</v>
+      </c>
+      <c r="P98" t="n">
+        <v>44805029</v>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/3965165</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Общество с ограниченной ответственностью "СУЭК-Финанс"</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>7709851798</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>5282365</v>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="n">
+        <v>23992</v>
+      </c>
+      <c r="I99" t="n">
+        <v>16794</v>
+      </c>
+      <c r="J99" t="n">
+        <v>162</v>
+      </c>
+      <c r="K99" t="n">
+        <v>77330378</v>
+      </c>
+      <c r="L99" t="n">
+        <v>20423888</v>
+      </c>
+      <c r="M99" t="n">
+        <v>70</v>
+      </c>
+      <c r="N99" t="n">
+        <v>78439</v>
+      </c>
+      <c r="O99" t="n">
+        <v>20503494</v>
+      </c>
+      <c r="P99" t="n">
+        <v>20425556</v>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4697028</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>АО "ЮЖУРАЛЗОЛОТО ГРУППА КОМПАНИЙ"</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>7424024375</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>29914981</v>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="n">
+        <v>-16323173</v>
+      </c>
+      <c r="I100" t="n">
+        <v>4075973</v>
+      </c>
+      <c r="J100" t="n">
+        <v>320549</v>
+      </c>
+      <c r="K100" t="n">
+        <v>47336871</v>
+      </c>
+      <c r="L100" t="n">
+        <v>38107992</v>
+      </c>
+      <c r="M100" t="n">
+        <v>2025312</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2048905</v>
+      </c>
+      <c r="O100" t="n">
+        <v>14377840</v>
+      </c>
+      <c r="P100" t="n">
+        <v>44953151</v>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6540211</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ТАТНЕФТЕХИМ"</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>1655201119</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>4756836</v>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="n">
+        <v>137122</v>
+      </c>
+      <c r="I101" t="n">
+        <v>-327274</v>
+      </c>
+      <c r="J101" t="n">
+        <v>192</v>
+      </c>
+      <c r="K101" t="n">
+        <v>870000</v>
+      </c>
+      <c r="L101" t="n">
+        <v>270000</v>
+      </c>
+      <c r="M101" t="n">
+        <v>95489</v>
+      </c>
+      <c r="N101" t="n">
+        <v>1268161</v>
+      </c>
+      <c r="O101" t="n">
+        <v>1241059</v>
+      </c>
+      <c r="P101" t="n">
+        <v>401385</v>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2882491</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Газпром Нефть"</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>5504036333</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>2675243941</v>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="n">
+        <v>344113223</v>
+      </c>
+      <c r="I102" t="n">
+        <v>-672668577</v>
+      </c>
+      <c r="J102" t="n">
+        <v>120090279</v>
+      </c>
+      <c r="K102" t="n">
+        <v>1018546168</v>
+      </c>
+      <c r="L102" t="n">
+        <v>523221951</v>
+      </c>
+      <c r="M102" t="n">
+        <v>48313469</v>
+      </c>
+      <c r="N102" t="n">
+        <v>570812953</v>
+      </c>
+      <c r="O102" t="n">
+        <v>1115163466</v>
+      </c>
+      <c r="P102" t="n">
+        <v>1356076017</v>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6934659</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "МЕГАФОН"</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>7812014560</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>313180311</v>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="n">
+        <v>86019524</v>
+      </c>
+      <c r="I103" t="n">
+        <v>155410658</v>
+      </c>
+      <c r="J103" t="n">
+        <v>31269439</v>
+      </c>
+      <c r="K103" t="n">
+        <v>313939374</v>
+      </c>
+      <c r="L103" t="n">
+        <v>130147165</v>
+      </c>
+      <c r="M103" t="n">
+        <v>24378644</v>
+      </c>
+      <c r="N103" t="n">
+        <v>169102679</v>
+      </c>
+      <c r="O103" t="n">
+        <v>112536728</v>
+      </c>
+      <c r="P103" t="n">
+        <v>195346733</v>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7044659</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Открытое акционерное общество "Российские железные дороги"</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>7708503727</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1963646793</v>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="n">
+        <v>18763461</v>
+      </c>
+      <c r="I104" t="n">
+        <v>363885889</v>
+      </c>
+      <c r="J104" t="n">
+        <v>46487763</v>
+      </c>
+      <c r="K104" t="n">
+        <v>1551144333</v>
+      </c>
+      <c r="L104" t="n">
+        <v>270362395</v>
+      </c>
+      <c r="M104" t="n">
+        <v>81423187</v>
+      </c>
+      <c r="N104" t="n">
+        <v>4886001379</v>
+      </c>
+      <c r="O104" t="n">
+        <v>316228921</v>
+      </c>
+      <c r="P104" t="n">
+        <v>859557402</v>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2432297</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ОБЛАЧНЫЕ ТЕХНОЛОГИИ"</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>7736279160</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>8856359</v>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="n">
+        <v>393267</v>
+      </c>
+      <c r="I105" t="n">
+        <v>4817063</v>
+      </c>
+      <c r="J105" t="n">
+        <v>6339347</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="L105" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="n">
+        <v>19810081</v>
+      </c>
+      <c r="O105" t="n">
+        <v>8064422</v>
+      </c>
+      <c r="P105" t="n">
+        <v>3490434</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/9940825</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/issuer_financials.xlsx
+++ b/data/issuer_financials.xlsx
@@ -3126,58 +3126,52 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВУШ"</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>9717068640</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Совком Секьюр"</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>9703193909</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2025</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>10694433</v>
-      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>-2549955</v>
+        <v>764758</v>
       </c>
       <c r="I43" t="n">
-        <v>213787</v>
+        <v>35192</v>
       </c>
       <c r="J43" t="n">
-        <v>330829</v>
+        <v>1286080</v>
       </c>
       <c r="K43" t="n">
-        <v>13895537</v>
+        <v>10632078</v>
       </c>
       <c r="L43" t="n">
-        <v>4607881</v>
+        <v>3400068</v>
       </c>
       <c r="M43" t="n">
-        <v>2583863</v>
+        <v>1853940</v>
       </c>
       <c r="N43" t="n">
-        <v>410758</v>
+        <v>764768</v>
       </c>
       <c r="O43" t="n">
-        <v>4971431</v>
+        <v>5356352</v>
       </c>
       <c r="P43" t="n">
-        <v>5382399</v>
+        <v>3590518</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10703464</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12558868</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3190,12 +3184,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьютиризация»</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БОРЕЦ КАПИТАЛ"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9704138298</t>
+          <t>9731098069</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3208,38 +3202,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="F44" t="n">
+        <v>1023</v>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>-110007</v>
+        <v>5086</v>
       </c>
       <c r="I44" t="n">
-        <v>-2651331</v>
+        <v>-8655</v>
       </c>
       <c r="J44" t="n">
-        <v>465777</v>
+        <v>219</v>
       </c>
       <c r="K44" t="n">
-        <v>6436164</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>1374585</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2595164</v>
+        <v>25</v>
       </c>
       <c r="N44" t="n">
-        <v>285806</v>
+        <v>223227</v>
       </c>
       <c r="O44" t="n">
-        <v>1960665</v>
+        <v>33333869</v>
       </c>
       <c r="P44" t="n">
-        <v>1374860</v>
+        <v>33311146</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11849209</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11927098</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3252,56 +3248,54 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ООО «СФО ВТБ РКС ЭТАЛОН»</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>9704147373</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "ЛИЗИНГОВАЯ КОМПАНИЯ ПРОСТЫЕ РЕШЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>278181110</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2025</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="n">
+        <v>2194489</v>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>6112293</v>
+        <v>155122</v>
       </c>
       <c r="I45" t="n">
-        <v>-9926195</v>
+        <v>-2086627</v>
       </c>
       <c r="J45" t="n">
-        <v>20467815</v>
+        <v>463109</v>
       </c>
       <c r="K45" t="n">
-        <v>144460215</v>
+        <v>11391448</v>
       </c>
       <c r="L45" t="n">
-        <v>31592025</v>
+        <v>3335362</v>
       </c>
       <c r="M45" t="n">
-        <v>10095850</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>9955602</v>
+        <v>1453344</v>
       </c>
       <c r="O45" t="n">
-        <v>62360167</v>
+        <v>5990866</v>
       </c>
       <c r="P45" t="n">
-        <v>35761493</v>
+        <v>3989488</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11883254</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/508857</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3314,18 +3308,14 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьюритизация 2»</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>9704160303</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьютиризация»</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>9704138298</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2025</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3335,35 +3325,35 @@
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>406160</v>
+        <v>-110007</v>
       </c>
       <c r="I46" t="n">
-        <v>-1846540</v>
+        <v>-2651331</v>
       </c>
       <c r="J46" t="n">
-        <v>788495</v>
+        <v>465777</v>
       </c>
       <c r="K46" t="n">
-        <v>10097440</v>
+        <v>6436164</v>
       </c>
       <c r="L46" t="n">
-        <v>1629792</v>
+        <v>1374585</v>
       </c>
       <c r="M46" t="n">
-        <v>1867484</v>
+        <v>2595164</v>
       </c>
       <c r="N46" t="n">
-        <v>406093</v>
+        <v>285806</v>
       </c>
       <c r="O46" t="n">
-        <v>2587855</v>
+        <v>1960665</v>
       </c>
       <c r="P46" t="n">
-        <v>1629933</v>
+        <v>1374860</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11930756</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11849209</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -5154,58 +5144,52 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГЛОРАКС"</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>9729387137</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-4"</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9703211185</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2025</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>3057693</v>
-      </c>
+      <c r="F75" t="inlineStr"/>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>352891</v>
+        <v>977720</v>
       </c>
       <c r="I75" t="n">
-        <v>-2487508</v>
+        <v>-1274588</v>
       </c>
       <c r="J75" t="n">
-        <v>17468</v>
+        <v>2631244</v>
       </c>
       <c r="K75" t="n">
-        <v>15888211</v>
+        <v>20526472</v>
       </c>
       <c r="L75" t="n">
-        <v>7131352</v>
+        <v>4223028</v>
       </c>
       <c r="M75" t="n">
-        <v>3563226</v>
+        <v>1495620</v>
       </c>
       <c r="N75" t="n">
-        <v>5262202</v>
+        <v>977730</v>
       </c>
       <c r="O75" t="n">
-        <v>9887498</v>
+        <v>7130263</v>
       </c>
       <c r="P75" t="n">
-        <v>7607515</v>
+        <v>4225049</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12558009</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12680884</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -5218,58 +5202,52 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГРУППА ПОЗИТИВ"</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>9718077239</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Сплит Финанс"</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>9703209122</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2025</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>0</v>
-      </c>
+      <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>-2319012</v>
+        <v>832800</v>
       </c>
       <c r="I76" t="n">
-        <v>-3043148</v>
+        <v>-627668</v>
       </c>
       <c r="J76" t="n">
-        <v>85073</v>
+        <v>3157507</v>
       </c>
       <c r="K76" t="n">
-        <v>20333431</v>
+        <v>12321587</v>
       </c>
       <c r="L76" t="n">
-        <v>533431</v>
+        <v>4622403</v>
       </c>
       <c r="M76" t="n">
-        <v>3093490</v>
+        <v>794736</v>
       </c>
       <c r="N76" t="n">
-        <v>14618010</v>
+        <v>832810</v>
       </c>
       <c r="O76" t="n">
-        <v>6251325</v>
+        <v>10288657</v>
       </c>
       <c r="P76" t="n">
-        <v>542917</v>
+        <v>4649009</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10388722</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12663922</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -5282,58 +5260,52 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "КАРШЕРИНГ РУССИЯ"</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>9718236471</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-6"</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>9703221553</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2025</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>26088727</v>
-      </c>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>-3628694</v>
+        <v>421691</v>
       </c>
       <c r="I77" t="n">
-        <v>6086337</v>
+        <v>-16243</v>
       </c>
       <c r="J77" t="n">
-        <v>1230217</v>
+        <v>1996969</v>
       </c>
       <c r="K77" t="n">
-        <v>18535372</v>
+        <v>31400566</v>
       </c>
       <c r="L77" t="n">
-        <v>10535372</v>
+        <v>191416</v>
       </c>
       <c r="M77" t="n">
-        <v>5647179</v>
+        <v>191760</v>
       </c>
       <c r="N77" t="n">
-        <v>6060673</v>
+        <v>421701</v>
       </c>
       <c r="O77" t="n">
-        <v>6682880</v>
+        <v>11406621</v>
       </c>
       <c r="P77" t="n">
-        <v>17515458</v>
+        <v>592089</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12289607</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12744848</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -5346,12 +5318,12 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ФАБРИКА ПО"</t>
+          <t>Общество с ограниченной ответственностью "Профессиональная коллекторская организация "Агентство судебного взыскания"</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>9726092897</t>
+          <t>7841019595</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5364,38 +5336,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr"/>
+      <c r="F78" t="n">
+        <v>2813950</v>
+      </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>26111</v>
+        <v>289449</v>
       </c>
       <c r="I78" t="n">
-        <v>-116300</v>
+        <v>-782507</v>
       </c>
       <c r="J78" t="n">
-        <v>58920</v>
+        <v>439421</v>
       </c>
       <c r="K78" t="n">
-        <v>2012480</v>
+        <v>3335265</v>
       </c>
       <c r="L78" t="n">
-        <v>1961794</v>
+        <v>1661751</v>
       </c>
       <c r="M78" t="n">
-        <v>94487</v>
+        <v>634394</v>
       </c>
       <c r="N78" t="n">
-        <v>15655004</v>
+        <v>718092</v>
       </c>
       <c r="O78" t="n">
-        <v>3749182</v>
+        <v>4036728</v>
       </c>
       <c r="P78" t="n">
-        <v>3460790</v>
+        <v>1804336</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12624794</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/9111808</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -5408,12 +5382,12 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Профессиональная коллекторская организация "Агентство судебного взыскания"</t>
+          <t>Общество с ограниченной ответственностью "ЛЕГЕНДА"</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>7841019595</t>
+          <t>7840438730</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5427,39 +5401,39 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2813950</v>
+        <v>2574338</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>289449</v>
+        <v>676819</v>
       </c>
       <c r="I79" t="n">
-        <v>-782507</v>
+        <v>1424991</v>
       </c>
       <c r="J79" t="n">
-        <v>439421</v>
+        <v>2369150</v>
       </c>
       <c r="K79" t="n">
-        <v>3335265</v>
+        <v>13269288</v>
       </c>
       <c r="L79" t="n">
-        <v>1661751</v>
+        <v>5143359</v>
       </c>
       <c r="M79" t="n">
-        <v>634394</v>
+        <v>1792096</v>
       </c>
       <c r="N79" t="n">
-        <v>718092</v>
+        <v>988224</v>
       </c>
       <c r="O79" t="n">
-        <v>4036728</v>
+        <v>7760068</v>
       </c>
       <c r="P79" t="n">
-        <v>1804336</v>
+        <v>5682975</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/9111808</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/122728</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -5472,12 +5446,12 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ЛЕГЕНДА"</t>
+          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "Филберт"</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7840438730</t>
+          <t>7841430420</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5491,39 +5465,39 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2574338</v>
+        <v>8586868</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>676819</v>
+        <v>3152859</v>
       </c>
       <c r="I80" t="n">
-        <v>1424991</v>
+        <v>-2961381</v>
       </c>
       <c r="J80" t="n">
-        <v>2369150</v>
+        <v>130669</v>
       </c>
       <c r="K80" t="n">
-        <v>13269288</v>
+        <v>4275711</v>
       </c>
       <c r="L80" t="n">
-        <v>5143359</v>
+        <v>2275535</v>
       </c>
       <c r="M80" t="n">
-        <v>1792096</v>
+        <v>560901</v>
       </c>
       <c r="N80" t="n">
-        <v>988224</v>
+        <v>9134906</v>
       </c>
       <c r="O80" t="n">
-        <v>7760068</v>
+        <v>13555399</v>
       </c>
       <c r="P80" t="n">
-        <v>5682975</v>
+        <v>2486647</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/122728</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/1655225</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -5536,12 +5510,12 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "Филберт"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "МВ ФИНАНС"</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>7841430420</t>
+          <t>9701168311</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -5554,40 +5528,38 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>8586868</v>
-      </c>
+      <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>3152859</v>
+        <v>3493</v>
       </c>
       <c r="I81" t="n">
-        <v>-2961381</v>
+        <v>-2391603</v>
       </c>
       <c r="J81" t="n">
-        <v>130669</v>
+        <v>44911</v>
       </c>
       <c r="K81" t="n">
-        <v>4275711</v>
+        <v>7725451</v>
       </c>
       <c r="L81" t="n">
-        <v>2275535</v>
+        <v>5759320</v>
       </c>
       <c r="M81" t="n">
-        <v>560901</v>
+        <v>2261066</v>
       </c>
       <c r="N81" t="n">
-        <v>9134906</v>
+        <v>95811</v>
       </c>
       <c r="O81" t="n">
-        <v>13555399</v>
+        <v>5828974</v>
       </c>
       <c r="P81" t="n">
-        <v>2486647</v>
+        <v>5765046</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/1655225</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11476959</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -5600,12 +5572,12 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "МВ ФИНАНС"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВУШ"</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>9701168311</t>
+          <t>9717068640</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -5618,38 +5590,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
+      <c r="F82" t="n">
+        <v>10694433</v>
+      </c>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>3493</v>
+        <v>-2549955</v>
       </c>
       <c r="I82" t="n">
-        <v>-2391603</v>
+        <v>213787</v>
       </c>
       <c r="J82" t="n">
-        <v>44911</v>
+        <v>330829</v>
       </c>
       <c r="K82" t="n">
-        <v>7725451</v>
+        <v>13895537</v>
       </c>
       <c r="L82" t="n">
-        <v>5759320</v>
+        <v>4607881</v>
       </c>
       <c r="M82" t="n">
-        <v>2261066</v>
+        <v>2583863</v>
       </c>
       <c r="N82" t="n">
-        <v>95811</v>
+        <v>410758</v>
       </c>
       <c r="O82" t="n">
-        <v>5828974</v>
+        <v>4971431</v>
       </c>
       <c r="P82" t="n">
-        <v>5765046</v>
+        <v>5382399</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11476959</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10703464</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -5662,12 +5636,12 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное финансовое общество ТБ-5"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ГРУППА КОМПАНИЙ "СЕГЕЖА"</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>9703206788</t>
+          <t>9703024202</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -5680,38 +5654,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr"/>
+      <c r="F83" t="n">
+        <v>3234274</v>
+      </c>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>627562</v>
+        <v>-81659202</v>
       </c>
       <c r="I83" t="n">
-        <v>2054</v>
+        <v>-15560254</v>
       </c>
       <c r="J83" t="n">
-        <v>2567719</v>
+        <v>2171160</v>
       </c>
       <c r="K83" t="n">
-        <v>16587377</v>
+        <v>68989930</v>
       </c>
       <c r="L83" t="n">
-        <v>336877</v>
+        <v>28619951</v>
       </c>
       <c r="M83" t="n">
-        <v>337763</v>
+        <v>17966508</v>
       </c>
       <c r="N83" t="n">
-        <v>627572</v>
+        <v>69901335</v>
       </c>
       <c r="O83" t="n">
-        <v>6522558</v>
+        <v>16693441</v>
       </c>
       <c r="P83" t="n">
-        <v>636777</v>
+        <v>29540756</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12646488</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11477936</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -5724,12 +5700,12 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ГРУППА КОМПАНИЙ "СЕГЕЖА"</t>
+          <t>ООО «БИННОФАРМ ГРУПП»</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>9703024202</t>
+          <t>9704005675</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5743,39 +5719,39 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3234274</v>
+        <v>39152023</v>
       </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-81659202</v>
+        <v>-3437553</v>
       </c>
       <c r="I84" t="n">
-        <v>-15560254</v>
+        <v>-10088180</v>
       </c>
       <c r="J84" t="n">
-        <v>2171160</v>
+        <v>2741369</v>
       </c>
       <c r="K84" t="n">
-        <v>68989930</v>
+        <v>31048484</v>
       </c>
       <c r="L84" t="n">
-        <v>28619951</v>
+        <v>27198484</v>
       </c>
       <c r="M84" t="n">
-        <v>17966508</v>
+        <v>6612689</v>
       </c>
       <c r="N84" t="n">
-        <v>69901335</v>
+        <v>28187621</v>
       </c>
       <c r="O84" t="n">
-        <v>16693441</v>
+        <v>49838344</v>
       </c>
       <c r="P84" t="n">
-        <v>29540756</v>
+        <v>65495561</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11477936</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11181494</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -5788,12 +5764,12 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО "СБ СЕКЬЮРИТИЗАЦИЯ 5"</t>
+          <t>Публичное Акционерное общество "Лизинговая компания "Европлан"</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9703163693</t>
+          <t>9705101614</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5806,32 +5782,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr"/>
+      <c r="F85" t="n">
+        <v>59966125</v>
+      </c>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>-65</v>
+        <v>4034508</v>
       </c>
       <c r="I85" t="n">
-        <v>-266</v>
+        <v>84799387</v>
       </c>
       <c r="J85" t="n">
-        <v>13</v>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
+        <v>7477939</v>
+      </c>
+      <c r="K85" t="n">
+        <v>136124027</v>
+      </c>
+      <c r="L85" t="n">
+        <v>73233527</v>
+      </c>
+      <c r="M85" t="n">
+        <v>35514645</v>
+      </c>
       <c r="N85" t="n">
-        <v>13</v>
+        <v>36127674</v>
       </c>
       <c r="O85" t="n">
-        <v>13</v>
+        <v>113385304</v>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>85482683</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12333197</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10283154</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -5844,12 +5828,12 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Совком Секьюр"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "КАРШЕРИНГ РУССИЯ"</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9703193909</t>
+          <t>9718236471</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5862,38 +5846,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>26088727</v>
+      </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>764758</v>
+        <v>-3628694</v>
       </c>
       <c r="I86" t="n">
-        <v>35192</v>
+        <v>6086337</v>
       </c>
       <c r="J86" t="n">
-        <v>1286080</v>
+        <v>1230217</v>
       </c>
       <c r="K86" t="n">
-        <v>10632078</v>
+        <v>18535372</v>
       </c>
       <c r="L86" t="n">
-        <v>3400068</v>
+        <v>10535372</v>
       </c>
       <c r="M86" t="n">
-        <v>1853940</v>
+        <v>5647179</v>
       </c>
       <c r="N86" t="n">
-        <v>764768</v>
+        <v>6060673</v>
       </c>
       <c r="O86" t="n">
-        <v>5356352</v>
+        <v>6682880</v>
       </c>
       <c r="P86" t="n">
-        <v>3590518</v>
+        <v>17515458</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12558868</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12289607</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -5906,12 +5892,12 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-4"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГРУППА ПОЗИТИВ"</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9703211185</t>
+          <t>9718077239</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5924,38 +5910,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr"/>
+      <c r="F87" t="n">
+        <v>0</v>
+      </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>977720</v>
+        <v>-2319012</v>
       </c>
       <c r="I87" t="n">
-        <v>-1274588</v>
+        <v>-3043148</v>
       </c>
       <c r="J87" t="n">
-        <v>2631244</v>
+        <v>85073</v>
       </c>
       <c r="K87" t="n">
-        <v>20526472</v>
+        <v>20333431</v>
       </c>
       <c r="L87" t="n">
-        <v>4223028</v>
+        <v>533431</v>
       </c>
       <c r="M87" t="n">
-        <v>1495620</v>
+        <v>3093490</v>
       </c>
       <c r="N87" t="n">
-        <v>977730</v>
+        <v>14618010</v>
       </c>
       <c r="O87" t="n">
-        <v>7130263</v>
+        <v>6251325</v>
       </c>
       <c r="P87" t="n">
-        <v>4225049</v>
+        <v>542917</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12680884</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10388722</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -5968,12 +5956,12 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Сплит Финанс"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ФАБРИКА ПО"</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>9703209122</t>
+          <t>9726092897</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5989,35 +5977,35 @@
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>832800</v>
+        <v>26111</v>
       </c>
       <c r="I88" t="n">
-        <v>-627668</v>
+        <v>-116300</v>
       </c>
       <c r="J88" t="n">
-        <v>3157507</v>
+        <v>58920</v>
       </c>
       <c r="K88" t="n">
-        <v>12321587</v>
+        <v>2012480</v>
       </c>
       <c r="L88" t="n">
-        <v>4622403</v>
+        <v>1961794</v>
       </c>
       <c r="M88" t="n">
-        <v>794736</v>
+        <v>94487</v>
       </c>
       <c r="N88" t="n">
-        <v>832810</v>
+        <v>15655004</v>
       </c>
       <c r="O88" t="n">
-        <v>10288657</v>
+        <v>3749182</v>
       </c>
       <c r="P88" t="n">
-        <v>4649009</v>
+        <v>3460790</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12663922</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12624794</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -6030,12 +6018,12 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-6"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГЛОРАКС"</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>9703221553</t>
+          <t>9729387137</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -6048,38 +6036,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr"/>
+      <c r="F89" t="n">
+        <v>3057693</v>
+      </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>421691</v>
+        <v>352891</v>
       </c>
       <c r="I89" t="n">
-        <v>-16243</v>
+        <v>-2487508</v>
       </c>
       <c r="J89" t="n">
-        <v>1996969</v>
+        <v>17468</v>
       </c>
       <c r="K89" t="n">
-        <v>31400566</v>
+        <v>15888211</v>
       </c>
       <c r="L89" t="n">
-        <v>191416</v>
+        <v>7131352</v>
       </c>
       <c r="M89" t="n">
-        <v>191760</v>
+        <v>3563226</v>
       </c>
       <c r="N89" t="n">
-        <v>421701</v>
+        <v>5262202</v>
       </c>
       <c r="O89" t="n">
-        <v>11406621</v>
+        <v>9887498</v>
       </c>
       <c r="P89" t="n">
-        <v>592089</v>
+        <v>7607515</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12744848</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12558009</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -6092,58 +6082,52 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ООО «БИННОФАРМ ГРУПП»</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>9704005675</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО СБ СЕКЬЮРИТИЗАЦИЯ 3"</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>9704262880</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2025</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>39152023</v>
-      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>-3437553</v>
+        <v>867964</v>
       </c>
       <c r="I90" t="n">
-        <v>-10088180</v>
+        <v>-10844</v>
       </c>
       <c r="J90" t="n">
-        <v>2741369</v>
+        <v>1901818</v>
       </c>
       <c r="K90" t="n">
-        <v>31048484</v>
+        <v>22434769</v>
       </c>
       <c r="L90" t="n">
-        <v>27198484</v>
+        <v>2918653</v>
       </c>
       <c r="M90" t="n">
-        <v>6612689</v>
+        <v>268761</v>
       </c>
       <c r="N90" t="n">
-        <v>28187621</v>
+        <v>867973</v>
       </c>
       <c r="O90" t="n">
-        <v>49838344</v>
+        <v>5010242</v>
       </c>
       <c r="P90" t="n">
-        <v>65495561</v>
+        <v>2921170</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11181494</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12724282</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -6156,11 +6140,11 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ЛИЗИНГОВАЯ КОМПАНИЯ ПРОСТЫЕ РЕШЕНИЯ"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-1"</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>278181110</v>
+        <v>9704256936</v>
       </c>
       <c r="D91" t="n">
         <v>2025</v>
@@ -6170,40 +6154,38 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>2194489</v>
-      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>155122</v>
+        <v>462857</v>
       </c>
       <c r="I91" t="n">
-        <v>-2086627</v>
+        <v>-690900</v>
       </c>
       <c r="J91" t="n">
-        <v>463109</v>
+        <v>1467792</v>
       </c>
       <c r="K91" t="n">
-        <v>11391448</v>
+        <v>12652034</v>
       </c>
       <c r="L91" t="n">
-        <v>3335362</v>
+        <v>2707767</v>
       </c>
       <c r="M91" t="n">
-        <v>0</v>
+        <v>740205</v>
       </c>
       <c r="N91" t="n">
-        <v>1453344</v>
+        <v>462867</v>
       </c>
       <c r="O91" t="n">
-        <v>5990866</v>
+        <v>4761718</v>
       </c>
       <c r="P91" t="n">
-        <v>3989488</v>
+        <v>2710789</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/508857</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12624837</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -6216,58 +6198,52 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БОРЕЦ КАПИТАЛ"</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>9731098069</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-2"</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>9704264662</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2025</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>1023</v>
-      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>5086</v>
+        <v>966</v>
       </c>
       <c r="I92" t="n">
-        <v>-8655</v>
+        <v>-439</v>
       </c>
       <c r="J92" t="n">
-        <v>219</v>
+        <v>2571</v>
       </c>
       <c r="K92" t="n">
-        <v>0</v>
+        <v>3133</v>
       </c>
       <c r="L92" t="n">
-        <v>0</v>
+        <v>3133</v>
       </c>
       <c r="M92" t="n">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c r="N92" t="n">
-        <v>223227</v>
+        <v>-956</v>
       </c>
       <c r="O92" t="n">
-        <v>33333869</v>
+        <v>2571</v>
       </c>
       <c r="P92" t="n">
-        <v>33311146</v>
+        <v>3527</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11927098</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12755483</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -6280,58 +6256,46 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Публичное Акционерное общество "Лизинговая компания "Европлан"</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>9705101614</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО "СБ СЕКЬЮРИТИЗАЦИЯ 5"</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>9703163693</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2025</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>59966125</v>
-      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>4034508</v>
+        <v>-65</v>
       </c>
       <c r="I93" t="n">
-        <v>84799387</v>
+        <v>-266</v>
       </c>
       <c r="J93" t="n">
-        <v>7477939</v>
-      </c>
-      <c r="K93" t="n">
-        <v>136124027</v>
-      </c>
-      <c r="L93" t="n">
-        <v>73233527</v>
-      </c>
-      <c r="M93" t="n">
-        <v>35514645</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
-        <v>36127674</v>
+        <v>13</v>
       </c>
       <c r="O93" t="n">
-        <v>113385304</v>
+        <v>13</v>
       </c>
       <c r="P93" t="n">
-        <v>85482683</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10283154</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12333197</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -6344,18 +6308,14 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-1"</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>9704256936</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ООО «СФО ВТБ РКС ЭТАЛОН»</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>9704147373</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2025</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -6365,35 +6325,35 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>462857</v>
+        <v>6112293</v>
       </c>
       <c r="I94" t="n">
-        <v>-690900</v>
+        <v>-9926195</v>
       </c>
       <c r="J94" t="n">
-        <v>1467792</v>
+        <v>20467815</v>
       </c>
       <c r="K94" t="n">
-        <v>12652034</v>
+        <v>144460215</v>
       </c>
       <c r="L94" t="n">
-        <v>2707767</v>
+        <v>31592025</v>
       </c>
       <c r="M94" t="n">
-        <v>740205</v>
+        <v>10095850</v>
       </c>
       <c r="N94" t="n">
-        <v>462867</v>
+        <v>9955602</v>
       </c>
       <c r="O94" t="n">
-        <v>4761718</v>
+        <v>62360167</v>
       </c>
       <c r="P94" t="n">
-        <v>2710789</v>
+        <v>35761493</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12624837</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11883254</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -6406,18 +6366,14 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО СБ СЕКЬЮРИТИЗАЦИЯ 3"</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>9704262880</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьюритизация 2»</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>9704160303</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2025</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -6427,35 +6383,35 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>867964</v>
+        <v>406160</v>
       </c>
       <c r="I95" t="n">
-        <v>-10844</v>
+        <v>-1846540</v>
       </c>
       <c r="J95" t="n">
-        <v>1901818</v>
+        <v>788495</v>
       </c>
       <c r="K95" t="n">
-        <v>22434769</v>
+        <v>10097440</v>
       </c>
       <c r="L95" t="n">
-        <v>2918653</v>
+        <v>1629792</v>
       </c>
       <c r="M95" t="n">
-        <v>268761</v>
+        <v>1867484</v>
       </c>
       <c r="N95" t="n">
-        <v>867973</v>
+        <v>406093</v>
       </c>
       <c r="O95" t="n">
-        <v>5010242</v>
+        <v>2587855</v>
       </c>
       <c r="P95" t="n">
-        <v>2921170</v>
+        <v>1629933</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12724282</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11930756</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -6468,18 +6424,14 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-2"</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>9704264662</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное финансовое общество ТБ-5"</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>9703206788</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2025</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -6489,35 +6441,35 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>966</v>
+        <v>627562</v>
       </c>
       <c r="I96" t="n">
-        <v>-439</v>
+        <v>2054</v>
       </c>
       <c r="J96" t="n">
-        <v>2571</v>
+        <v>2567719</v>
       </c>
       <c r="K96" t="n">
-        <v>3133</v>
+        <v>16587377</v>
       </c>
       <c r="L96" t="n">
-        <v>3133</v>
+        <v>336877</v>
       </c>
       <c r="M96" t="n">
-        <v>133</v>
+        <v>337763</v>
       </c>
       <c r="N96" t="n">
-        <v>-956</v>
+        <v>627572</v>
       </c>
       <c r="O96" t="n">
-        <v>2571</v>
+        <v>6522558</v>
       </c>
       <c r="P96" t="n">
-        <v>3527</v>
+        <v>636777</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12755483</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12646488</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">

--- a/data/issuer_financials.xlsx
+++ b/data/issuer_financials.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -832,12 +832,12 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ "СЛУЖБА ЗАЩИТЫ АКТИВОВ"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "МАГНИТ"</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2310197022</t>
+          <t>2309085638</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -851,39 +851,39 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>429239</v>
+        <v>412062</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>112977</v>
+        <v>5354640</v>
       </c>
       <c r="I7" t="n">
-        <v>-710830</v>
+        <v>-52552646</v>
       </c>
       <c r="J7" t="n">
-        <v>8123</v>
+        <v>623</v>
       </c>
       <c r="K7" t="n">
-        <v>865965</v>
+        <v>378873287</v>
       </c>
       <c r="L7" t="n">
-        <v>7361</v>
+        <v>200823287</v>
       </c>
       <c r="M7" t="n">
-        <v>110563</v>
+        <v>49921724</v>
       </c>
       <c r="N7" t="n">
-        <v>303889</v>
+        <v>213482646</v>
       </c>
       <c r="O7" t="n">
-        <v>1165803</v>
+        <v>351410295</v>
       </c>
       <c r="P7" t="n">
-        <v>62128</v>
+        <v>205979865</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10041570</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3644000</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -896,12 +896,12 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "МАГНИТ"</t>
+          <t>Общество с ограниченной ответственностью "Торговый дом РКС"</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2309085638</t>
+          <t>2317084067</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -915,39 +915,39 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>412062</v>
+        <v>378077</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>5354640</v>
+        <v>28255</v>
       </c>
       <c r="I8" t="n">
-        <v>-52552646</v>
+        <v>-333069</v>
       </c>
       <c r="J8" t="n">
-        <v>623</v>
+        <v>156343</v>
       </c>
       <c r="K8" t="n">
-        <v>378873287</v>
+        <v>3727499</v>
       </c>
       <c r="L8" t="n">
-        <v>200823287</v>
+        <v>950000</v>
       </c>
       <c r="M8" t="n">
-        <v>49921724</v>
+        <v>184863</v>
       </c>
       <c r="N8" t="n">
-        <v>213482646</v>
+        <v>332485</v>
       </c>
       <c r="O8" t="n">
-        <v>351410295</v>
+        <v>1447423</v>
       </c>
       <c r="P8" t="n">
-        <v>205979865</v>
+        <v>954306</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3644000</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10121687</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -960,12 +960,12 @@
       <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Торговый дом РКС"</t>
+          <t>Общество с ограниченной ответственностью "ДЕЛЬТАЛИЗИНГ"</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2317084067</t>
+          <t>2536247123</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -979,39 +979,39 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>378077</v>
+        <v>18325733</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>28255</v>
+        <v>4366232</v>
       </c>
       <c r="I9" t="n">
-        <v>-333069</v>
+        <v>49238605</v>
       </c>
       <c r="J9" t="n">
-        <v>156343</v>
+        <v>2511568</v>
       </c>
       <c r="K9" t="n">
-        <v>3727499</v>
+        <v>42758726</v>
       </c>
       <c r="L9" t="n">
-        <v>950000</v>
+        <v>22504345</v>
       </c>
       <c r="M9" t="n">
-        <v>184863</v>
+        <v>8289186</v>
       </c>
       <c r="N9" t="n">
-        <v>332485</v>
+        <v>18604665</v>
       </c>
       <c r="O9" t="n">
-        <v>1447423</v>
+        <v>32482684</v>
       </c>
       <c r="P9" t="n">
-        <v>954306</v>
+        <v>28257955</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10121687</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/983920</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1024,12 +1024,12 @@
       <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Восточная Стивидорная Компания"</t>
+          <t>НЕПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ «ПЕРВОЕ КЛИЕНТСКОЕ БЮРО»</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2508064833</t>
+          <t>2723115222</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1043,39 +1043,39 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>10029455</v>
+        <v>22501574</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>2896029</v>
+        <v>7200301</v>
       </c>
       <c r="I10" t="n">
-        <v>2488486</v>
+        <v>10878561</v>
       </c>
       <c r="J10" t="n">
-        <v>266653</v>
+        <v>1166700</v>
       </c>
       <c r="K10" t="n">
-        <v>38468111</v>
+        <v>15825031</v>
       </c>
       <c r="L10" t="n">
-        <v>8468111</v>
+        <v>2369260</v>
       </c>
       <c r="M10" t="n">
-        <v>4657692</v>
+        <v>2984377</v>
       </c>
       <c r="N10" t="n">
-        <v>72515756</v>
+        <v>11636585</v>
       </c>
       <c r="O10" t="n">
-        <v>6880037</v>
+        <v>4307999</v>
       </c>
       <c r="P10" t="n">
-        <v>9090610</v>
+        <v>3627580</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2926803</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/540986</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1088,12 +1088,12 @@
       <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Новабев Групп"</t>
+          <t>Общество с ограниченной ответственностью "ЭкоНива"</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7705634425</t>
+          <t>3652904371</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1107,39 +1107,39 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3900773</v>
+        <v>3053</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>3314072</v>
+        <v>484</v>
       </c>
       <c r="I11" t="n">
-        <v>-2057228</v>
+        <v>-45</v>
       </c>
       <c r="J11" t="n">
-        <v>438687</v>
+        <v>269</v>
       </c>
       <c r="K11" t="n">
-        <v>21451914</v>
+        <v>256</v>
       </c>
       <c r="L11" t="n">
-        <v>5201914</v>
+        <v>256</v>
       </c>
       <c r="M11" t="n">
-        <v>2531399</v>
+        <v>6</v>
       </c>
       <c r="N11" t="n">
-        <v>20744863</v>
+        <v>9502040</v>
       </c>
       <c r="O11" t="n">
-        <v>8429304</v>
+        <v>6377</v>
       </c>
       <c r="P11" t="n">
-        <v>7174938</v>
+        <v>6193</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2815194</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12587302</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1152,12 +1152,12 @@
       <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ДЕЛЬТАЛИЗИНГ"</t>
+          <t>МЕЖДУНАРОДНАЯ КОМПАНИЯ ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ЯНДЕКС"</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2536247123</t>
+          <t>3900019850</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1171,39 +1171,39 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>18325733</v>
+        <v>87999120</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>4366232</v>
+        <v>825819172</v>
       </c>
       <c r="I12" t="n">
-        <v>49238605</v>
+        <v>58738057</v>
       </c>
       <c r="J12" t="n">
-        <v>2511568</v>
+        <v>267</v>
       </c>
       <c r="K12" t="n">
-        <v>42758726</v>
+        <v>105741950</v>
       </c>
       <c r="L12" t="n">
-        <v>22504345</v>
+        <v>741950</v>
       </c>
       <c r="M12" t="n">
-        <v>8289186</v>
+        <v>7504950</v>
       </c>
       <c r="N12" t="n">
-        <v>18604665</v>
+        <v>2623731887</v>
       </c>
       <c r="O12" t="n">
-        <v>32482684</v>
+        <v>37979183</v>
       </c>
       <c r="P12" t="n">
-        <v>28257955</v>
+        <v>1428939</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/983920</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12348996</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1216,12 +1216,12 @@
       <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>НЕПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ «ПЕРВОЕ КЛИЕНТСКОЕ БЮРО»</t>
+          <t>Международная компания Публичное акционерное общество "Озон"</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2723115222</t>
+          <t>3900045916</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1235,39 +1235,33 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>22501574</v>
+        <v>194141</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>7200301</v>
+        <v>30319216</v>
       </c>
       <c r="I13" t="n">
-        <v>10878561</v>
+        <v>25025317</v>
       </c>
       <c r="J13" t="n">
-        <v>1166700</v>
-      </c>
-      <c r="K13" t="n">
-        <v>15825031</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2369260</v>
-      </c>
-      <c r="M13" t="n">
-        <v>2984377</v>
-      </c>
+        <v>132739</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
-        <v>11636585</v>
+        <v>152986102</v>
       </c>
       <c r="O13" t="n">
-        <v>4307999</v>
+        <v>7305844</v>
       </c>
       <c r="P13" t="n">
-        <v>3627580</v>
+        <v>5558853</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/540986</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12758251</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1280,12 +1274,12 @@
       <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ЭкоНива"</t>
+          <t>Международная компания акционерное общество "Совко Капитал Партнерс"</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3652904371</t>
+          <t>3906406196</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1299,39 +1293,39 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3053</v>
+        <v>10120977</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>484</v>
+        <v>-16741244</v>
       </c>
       <c r="I14" t="n">
-        <v>-45</v>
+        <v>-1363704</v>
       </c>
       <c r="J14" t="n">
-        <v>269</v>
+        <v>201429</v>
       </c>
       <c r="K14" t="n">
-        <v>256</v>
+        <v>18185066</v>
       </c>
       <c r="L14" t="n">
-        <v>256</v>
+        <v>8185066</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>3286537</v>
       </c>
       <c r="N14" t="n">
-        <v>9502040</v>
+        <v>239100426</v>
       </c>
       <c r="O14" t="n">
-        <v>6377</v>
+        <v>9096034</v>
       </c>
       <c r="P14" t="n">
-        <v>6193</v>
+        <v>8329043</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12587302</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11665010</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -1344,12 +1338,12 @@
       <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>МЕЖДУНАРОДНАЯ КОМПАНИЯ ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ЯНДЕКС"</t>
+          <t>Акционерное общество Холдинговая Компания "Новотранс"</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3900019850</t>
+          <t>4205119220</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1363,39 +1357,39 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>87999120</v>
+        <v>15304887</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>825819172</v>
+        <v>1996911</v>
       </c>
       <c r="I15" t="n">
-        <v>58738057</v>
+        <v>2430012</v>
       </c>
       <c r="J15" t="n">
-        <v>267</v>
+        <v>5490568</v>
       </c>
       <c r="K15" t="n">
-        <v>105741950</v>
+        <v>74915074</v>
       </c>
       <c r="L15" t="n">
-        <v>741950</v>
+        <v>28165074</v>
       </c>
       <c r="M15" t="n">
-        <v>7504950</v>
+        <v>7737096</v>
       </c>
       <c r="N15" t="n">
-        <v>2623731887</v>
+        <v>45825791</v>
       </c>
       <c r="O15" t="n">
-        <v>37979183</v>
+        <v>27374395</v>
       </c>
       <c r="P15" t="n">
-        <v>1428939</v>
+        <v>32659899</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12348996</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/5896946</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1408,12 +1402,12 @@
       <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Международная компания Публичное акционерное общество "Озон"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВИС ФИНАНС"</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3900045916</t>
+          <t>4705081944</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1427,33 +1421,37 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>194141</v>
+        <v>2500610</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>30319216</v>
+        <v>51321</v>
       </c>
       <c r="I16" t="n">
-        <v>25025317</v>
+        <v>-7155471</v>
       </c>
       <c r="J16" t="n">
-        <v>132739</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+        <v>70855</v>
+      </c>
+      <c r="K16" t="n">
+        <v>17082187</v>
+      </c>
+      <c r="L16" t="n">
+        <v>5115905</v>
+      </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
-        <v>152986102</v>
+        <v>130206</v>
       </c>
       <c r="O16" t="n">
-        <v>7305844</v>
+        <v>5391395</v>
       </c>
       <c r="P16" t="n">
-        <v>5558853</v>
+        <v>5119974</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12758251</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11036812</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1466,12 +1464,12 @@
       <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Международная компания акционерное общество "Совко Капитал Партнерс"</t>
+          <t>Публичное акционерное общество "Россети Московский регион"</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3906406196</t>
+          <t>5036065113</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1485,39 +1483,39 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>10120977</v>
+        <v>284566717</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>-16741244</v>
+        <v>40035443</v>
       </c>
       <c r="I17" t="n">
-        <v>-1363704</v>
+        <v>101669143</v>
       </c>
       <c r="J17" t="n">
-        <v>201429</v>
+        <v>13365063</v>
       </c>
       <c r="K17" t="n">
-        <v>18185066</v>
+        <v>74030598</v>
       </c>
       <c r="L17" t="n">
-        <v>8185066</v>
+        <v>28570598</v>
       </c>
       <c r="M17" t="n">
-        <v>3286537</v>
+        <v>10096771</v>
       </c>
       <c r="N17" t="n">
-        <v>239100426</v>
+        <v>260977867</v>
       </c>
       <c r="O17" t="n">
-        <v>9096034</v>
+        <v>68802218</v>
       </c>
       <c r="P17" t="n">
-        <v>8329043</v>
+        <v>206694050</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11665010</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4796897</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1530,12 +1528,12 @@
       <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Акционерное общество Холдинговая Компания "Новотранс"</t>
+          <t>АО "РОЛЬФ"</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4205119220</t>
+          <t>5047254063</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1549,39 +1547,39 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>15304887</v>
+        <v>218583671</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
-        <v>1996911</v>
+        <v>1597465</v>
       </c>
       <c r="I18" t="n">
-        <v>2430012</v>
+        <v>9766338</v>
       </c>
       <c r="J18" t="n">
-        <v>5490568</v>
+        <v>3975641</v>
       </c>
       <c r="K18" t="n">
-        <v>74915074</v>
+        <v>15101967</v>
       </c>
       <c r="L18" t="n">
-        <v>28165074</v>
+        <v>11101967</v>
       </c>
       <c r="M18" t="n">
-        <v>7737096</v>
+        <v>4637198</v>
       </c>
       <c r="N18" t="n">
-        <v>45825791</v>
+        <v>30249925</v>
       </c>
       <c r="O18" t="n">
-        <v>27374395</v>
+        <v>36790861</v>
       </c>
       <c r="P18" t="n">
-        <v>32659899</v>
+        <v>24454356</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/5896946</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11640744</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -1594,12 +1592,12 @@
       <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВИС ФИНАНС"</t>
+          <t>Публичное акционерное общество ХЭНДЕРСОН ФЭШН ГРУПП</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4705081944</t>
+          <t>5047265516</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1613,37 +1611,39 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2500610</v>
+        <v>1290000</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>51321</v>
+        <v>1316065</v>
       </c>
       <c r="I19" t="n">
-        <v>-7155471</v>
+        <v>-751643</v>
       </c>
       <c r="J19" t="n">
-        <v>70855</v>
+        <v>363666</v>
       </c>
       <c r="K19" t="n">
-        <v>17082187</v>
+        <v>1800954</v>
       </c>
       <c r="L19" t="n">
-        <v>5115905</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
+        <v>954</v>
+      </c>
+      <c r="M19" t="n">
+        <v>202932</v>
+      </c>
       <c r="N19" t="n">
-        <v>130206</v>
+        <v>4604956</v>
       </c>
       <c r="O19" t="n">
-        <v>5391395</v>
+        <v>2813775</v>
       </c>
       <c r="P19" t="n">
-        <v>5119974</v>
+        <v>6213</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11036812</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11895173</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -1656,12 +1656,12 @@
       <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Россети Московский регион"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО ПО СТРОИТЕЛЬСТВУ, РЕМОНТУ И СОДЕРЖАНИЮ АВТОМОБИЛЬНЫХ ДОРОГ И ИНЖЕНЕРНЫХ СООРУЖЕНИЙ "НОВОСИБИРСКАВТОДОР"</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5036065113</t>
+          <t>5405162714</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1675,39 +1675,39 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>284566717</v>
+        <v>17966056</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>40035443</v>
+        <v>433539</v>
       </c>
       <c r="I20" t="n">
-        <v>101669143</v>
+        <v>1543133</v>
       </c>
       <c r="J20" t="n">
-        <v>13365063</v>
+        <v>2598969</v>
       </c>
       <c r="K20" t="n">
-        <v>74030598</v>
+        <v>5141662</v>
       </c>
       <c r="L20" t="n">
-        <v>28570598</v>
+        <v>3441662</v>
       </c>
       <c r="M20" t="n">
-        <v>10096771</v>
+        <v>1154039</v>
       </c>
       <c r="N20" t="n">
-        <v>260977867</v>
+        <v>2066842</v>
       </c>
       <c r="O20" t="n">
-        <v>68802218</v>
+        <v>12008431</v>
       </c>
       <c r="P20" t="n">
-        <v>206694050</v>
+        <v>10712898</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4796897</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6043515</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -1720,12 +1720,12 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>АО "РОЛЬФ"</t>
+          <t>Общество с ограниченной ответственностью "Брусника. Строительство и Девелопмент"</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5047254063</t>
+          <t>6685151087</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1739,39 +1739,39 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>218583671</v>
+        <v>11764</v>
       </c>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>1597465</v>
+        <v>3669771</v>
       </c>
       <c r="I21" t="n">
-        <v>9766338</v>
+        <v>-5014711</v>
       </c>
       <c r="J21" t="n">
-        <v>3975641</v>
+        <v>1290</v>
       </c>
       <c r="K21" t="n">
-        <v>15101967</v>
+        <v>39379258</v>
       </c>
       <c r="L21" t="n">
-        <v>11101967</v>
+        <v>9100001</v>
       </c>
       <c r="M21" t="n">
-        <v>4637198</v>
+        <v>5650736</v>
       </c>
       <c r="N21" t="n">
-        <v>30249925</v>
+        <v>10383538</v>
       </c>
       <c r="O21" t="n">
-        <v>36790861</v>
+        <v>19168970</v>
       </c>
       <c r="P21" t="n">
-        <v>24454356</v>
+        <v>10209840</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11640744</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10736015</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -1784,12 +1784,12 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество ХЭНДЕРСОН ФЭШН ГРУПП</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "РОССЕТИ ЦЕНТР"</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5047265516</t>
+          <t>6901067107</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1803,39 +1803,39 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1290000</v>
+        <v>149813246</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>1316065</v>
+        <v>10155773</v>
       </c>
       <c r="I22" t="n">
-        <v>-751643</v>
+        <v>28796730</v>
       </c>
       <c r="J22" t="n">
-        <v>363666</v>
+        <v>6243096</v>
       </c>
       <c r="K22" t="n">
-        <v>1800954</v>
+        <v>36024622</v>
       </c>
       <c r="L22" t="n">
-        <v>954</v>
+        <v>13184718</v>
       </c>
       <c r="M22" t="n">
-        <v>202932</v>
+        <v>6455777</v>
       </c>
       <c r="N22" t="n">
-        <v>4604956</v>
+        <v>72315825</v>
       </c>
       <c r="O22" t="n">
-        <v>2813775</v>
+        <v>26830525</v>
       </c>
       <c r="P22" t="n">
-        <v>6213</v>
+        <v>51688362</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11895173</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/1314752</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -1848,12 +1848,12 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ПАО "АКРОН"</t>
+          <t>Общество с ограниченной ответственностью "Элит Строй"</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5321029508</t>
+          <t>7204090319</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1867,39 +1867,39 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>171997329</v>
+        <v>1007045</v>
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>52415054</v>
+        <v>2191316</v>
       </c>
       <c r="I23" t="n">
-        <v>25931936</v>
+        <v>-1165538</v>
       </c>
       <c r="J23" t="n">
-        <v>11537385</v>
+        <v>669599</v>
       </c>
       <c r="K23" t="n">
-        <v>135516907</v>
+        <v>45970941</v>
       </c>
       <c r="L23" t="n">
-        <v>63762318</v>
+        <v>1609540</v>
       </c>
       <c r="M23" t="n">
-        <v>18287531</v>
+        <v>4548151</v>
       </c>
       <c r="N23" t="n">
-        <v>190765693</v>
+        <v>7071438</v>
       </c>
       <c r="O23" t="n">
-        <v>74253156</v>
+        <v>18014341</v>
       </c>
       <c r="P23" t="n">
-        <v>90915954</v>
+        <v>1661048</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2347012</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3504558</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -1912,12 +1912,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО ПО СТРОИТЕЛЬСТВУ, РЕМОНТУ И СОДЕРЖАНИЮ АВТОМОБИЛЬНЫХ ДОРОГ И ИНЖЕНЕРНЫХ СООРУЖЕНИЙ "НОВОСИБИРСКАВТОДОР"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АПРИ"</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5405162714</t>
+          <t>7453326003</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1931,39 +1931,39 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>17966056</v>
+        <v>3058612</v>
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>433539</v>
+        <v>231140</v>
       </c>
       <c r="I24" t="n">
-        <v>1543133</v>
+        <v>15101</v>
       </c>
       <c r="J24" t="n">
-        <v>2598969</v>
+        <v>295040</v>
       </c>
       <c r="K24" t="n">
-        <v>5141662</v>
+        <v>11510301</v>
       </c>
       <c r="L24" t="n">
-        <v>3441662</v>
+        <v>5779169</v>
       </c>
       <c r="M24" t="n">
-        <v>1154039</v>
+        <v>94450</v>
       </c>
       <c r="N24" t="n">
-        <v>2066842</v>
+        <v>3695650</v>
       </c>
       <c r="O24" t="n">
-        <v>12008431</v>
+        <v>14512044</v>
       </c>
       <c r="P24" t="n">
-        <v>10712898</v>
+        <v>11821680</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6043515</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10906877</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -1976,12 +1976,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью профессиональная коллекторская организация "ЗАЩИТА ОНЛАЙН"</t>
+          <t>Публичное акционерное общество "Новабев Групп"</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5407973637</t>
+          <t>7705634425</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1995,39 +1995,39 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2905275</v>
+        <v>3900773</v>
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>174936</v>
+        <v>3314072</v>
       </c>
       <c r="I25" t="n">
-        <v>-496952</v>
+        <v>-2057228</v>
       </c>
       <c r="J25" t="n">
-        <v>284500</v>
+        <v>438687</v>
       </c>
       <c r="K25" t="n">
-        <v>2598700</v>
+        <v>21451914</v>
       </c>
       <c r="L25" t="n">
-        <v>683714</v>
+        <v>5201914</v>
       </c>
       <c r="M25" t="n">
-        <v>410727</v>
+        <v>2531399</v>
       </c>
       <c r="N25" t="n">
-        <v>413426</v>
+        <v>20744863</v>
       </c>
       <c r="O25" t="n">
-        <v>3090052</v>
+        <v>8429304</v>
       </c>
       <c r="P25" t="n">
-        <v>928735</v>
+        <v>7174938</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10947263</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2815194</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2040,12 +2040,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Акционерное общество "Уральская Сталь"</t>
+          <t>Публичное Акционерное Общество "Территориальная генерирующая компания № 14"</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>5607019523</t>
+          <t>7534018889</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2059,39 +2059,39 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>105454369</v>
+        <v>21333260</v>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>-27277878</v>
+        <v>460944</v>
       </c>
       <c r="I26" t="n">
-        <v>-1619940</v>
+        <v>3564527</v>
       </c>
       <c r="J26" t="n">
-        <v>1224621</v>
+        <v>8156340</v>
       </c>
       <c r="K26" t="n">
-        <v>86309927</v>
+        <v>19804235</v>
       </c>
       <c r="L26" t="n">
-        <v>78357375</v>
+        <v>5813933</v>
       </c>
       <c r="M26" t="n">
-        <v>14118686</v>
+        <v>2689720</v>
       </c>
       <c r="N26" t="n">
-        <v>18618354</v>
+        <v>8234169</v>
       </c>
       <c r="O26" t="n">
-        <v>94532062</v>
+        <v>12624099</v>
       </c>
       <c r="P26" t="n">
-        <v>131566321</v>
+        <v>12484258</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4662411</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/1178818</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2104,12 +2104,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АТОМНЫЙ ЭНЕРГОПРОМЫШЛЕННЫЙ КОМПЛЕКС"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "РОСАГРОЛИЗИНГ"</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7706664260</t>
+          <t>7704221591</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2123,39 +2123,39 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5950351</v>
+        <v>31327555</v>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>-85699460</v>
+        <v>1511285</v>
       </c>
       <c r="I27" t="n">
-        <v>-219664013</v>
+        <v>-15722941</v>
       </c>
       <c r="J27" t="n">
-        <v>55323672</v>
+        <v>5050692</v>
       </c>
       <c r="K27" t="n">
-        <v>1446926765</v>
+        <v>138689053</v>
       </c>
       <c r="L27" t="n">
-        <v>738167987</v>
+        <v>56161430</v>
       </c>
       <c r="M27" t="n">
-        <v>221756065</v>
+        <v>23573052</v>
       </c>
       <c r="N27" t="n">
-        <v>1386949587</v>
+        <v>113259877</v>
       </c>
       <c r="O27" t="n">
-        <v>520700401</v>
+        <v>75412579</v>
       </c>
       <c r="P27" t="n">
-        <v>757359793</v>
+        <v>65018097</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6651267</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4547978</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2168,12 +2168,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью профессиональная коллекторская организация "Вернём"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "А101"</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5611067262</t>
+          <t>7704810149</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2187,39 +2187,39 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1656036</v>
+        <v>21202430</v>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>135809</v>
+        <v>16040081</v>
       </c>
       <c r="I28" t="n">
-        <v>-443417</v>
+        <v>11327840</v>
       </c>
       <c r="J28" t="n">
-        <v>55363</v>
+        <v>3944321</v>
       </c>
       <c r="K28" t="n">
-        <v>1984195</v>
+        <v>75879853</v>
       </c>
       <c r="L28" t="n">
-        <v>1099128</v>
+        <v>15570300</v>
       </c>
       <c r="M28" t="n">
-        <v>459607</v>
+        <v>4121425</v>
       </c>
       <c r="N28" t="n">
-        <v>271169</v>
+        <v>38081901</v>
       </c>
       <c r="O28" t="n">
-        <v>2394072</v>
+        <v>41317852</v>
       </c>
       <c r="P28" t="n">
-        <v>1179666</v>
+        <v>50340260</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7702700</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/587902</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2232,12 +2232,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Брусника. Строительство и Девелопмент"</t>
+          <t>Общество с ограниченной ответственностью "ДелоПортс"</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>6685151087</t>
+          <t>7706420120</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2251,39 +2251,39 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11764</v>
+        <v>124512</v>
       </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>3669771</v>
+        <v>73553032</v>
       </c>
       <c r="I29" t="n">
-        <v>-5014711</v>
+        <v>-4022056</v>
       </c>
       <c r="J29" t="n">
-        <v>1290</v>
+        <v>80452</v>
       </c>
       <c r="K29" t="n">
-        <v>39379258</v>
+        <v>63744005</v>
       </c>
       <c r="L29" t="n">
-        <v>9100001</v>
+        <v>22368376</v>
       </c>
       <c r="M29" t="n">
-        <v>5650736</v>
+        <v>11369181</v>
       </c>
       <c r="N29" t="n">
-        <v>10383538</v>
+        <v>88264659</v>
       </c>
       <c r="O29" t="n">
-        <v>19168970</v>
+        <v>22183196</v>
       </c>
       <c r="P29" t="n">
-        <v>10209840</v>
+        <v>22990992</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10736015</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/9184684</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -2296,12 +2296,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "РОССЕТИ ЦЕНТР"</t>
+          <t>Акционерное общество "Эталон-Финанс"</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>6901067107</t>
+          <t>7705619586</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2315,39 +2315,39 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>149813246</v>
+        <v>29228</v>
       </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>10155773</v>
+        <v>2745058</v>
       </c>
       <c r="I30" t="n">
-        <v>28796730</v>
+        <v>-7266612</v>
       </c>
       <c r="J30" t="n">
-        <v>6243096</v>
+        <v>110385</v>
       </c>
       <c r="K30" t="n">
-        <v>36024622</v>
+        <v>84443748</v>
       </c>
       <c r="L30" t="n">
-        <v>13184718</v>
+        <v>25203437</v>
       </c>
       <c r="M30" t="n">
-        <v>6455777</v>
+        <v>8929388</v>
       </c>
       <c r="N30" t="n">
-        <v>72315825</v>
+        <v>35229067</v>
       </c>
       <c r="O30" t="n">
-        <v>26830525</v>
+        <v>4753665</v>
       </c>
       <c r="P30" t="n">
-        <v>51688362</v>
+        <v>25403641</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/1314752</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2380269</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -2360,12 +2360,12 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АПРИ"</t>
+          <t>Акционерное общество "ПОЛИПЛАСТ"</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>7453326003</t>
+          <t>7708186108</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2379,39 +2379,39 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>3058612</v>
+        <v>2672312</v>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>231140</v>
+        <v>674988</v>
       </c>
       <c r="I31" t="n">
-        <v>15101</v>
+        <v>-6078380</v>
       </c>
       <c r="J31" t="n">
-        <v>295040</v>
+        <v>958181</v>
       </c>
       <c r="K31" t="n">
-        <v>11510301</v>
+        <v>46531139</v>
       </c>
       <c r="L31" t="n">
-        <v>5779169</v>
+        <v>7980825</v>
       </c>
       <c r="M31" t="n">
-        <v>94450</v>
+        <v>4460162</v>
       </c>
       <c r="N31" t="n">
-        <v>3695650</v>
+        <v>1054490</v>
       </c>
       <c r="O31" t="n">
-        <v>14512044</v>
+        <v>10572743</v>
       </c>
       <c r="P31" t="n">
-        <v>11821680</v>
+        <v>8104372</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10906877</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2277439</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -2424,12 +2424,12 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Элит Строй"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АТОМНЫЙ ЭНЕРГОПРОМЫШЛЕННЫЙ КОМПЛЕКС"</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>7204090319</t>
+          <t>7706664260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2443,39 +2443,39 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1007045</v>
+        <v>5950351</v>
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>2191316</v>
+        <v>-85699460</v>
       </c>
       <c r="I32" t="n">
-        <v>-1165538</v>
+        <v>-219664013</v>
       </c>
       <c r="J32" t="n">
-        <v>669599</v>
+        <v>55323672</v>
       </c>
       <c r="K32" t="n">
-        <v>45970941</v>
+        <v>1446926765</v>
       </c>
       <c r="L32" t="n">
-        <v>1609540</v>
+        <v>738167987</v>
       </c>
       <c r="M32" t="n">
-        <v>4548151</v>
+        <v>221756065</v>
       </c>
       <c r="N32" t="n">
-        <v>7071438</v>
+        <v>1386949587</v>
       </c>
       <c r="O32" t="n">
-        <v>18014341</v>
+        <v>520700401</v>
       </c>
       <c r="P32" t="n">
-        <v>1661048</v>
+        <v>757359793</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3504558</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6651267</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -2488,12 +2488,12 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "РОСАГРОЛИЗИНГ"</t>
+          <t>Общество с ограниченной ответственностью "ЭЛЕКТРОРЕШЕНИЯ"</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7704221591</t>
+          <t>7721403552</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2507,39 +2507,39 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>31327555</v>
+        <v>21521540</v>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>1511285</v>
+        <v>-223905</v>
       </c>
       <c r="I33" t="n">
-        <v>-15722941</v>
+        <v>1089672</v>
       </c>
       <c r="J33" t="n">
-        <v>5050692</v>
+        <v>1697179</v>
       </c>
       <c r="K33" t="n">
-        <v>138689053</v>
+        <v>6168848</v>
       </c>
       <c r="L33" t="n">
-        <v>56161430</v>
+        <v>4705327</v>
       </c>
       <c r="M33" t="n">
-        <v>23573052</v>
+        <v>1289262</v>
       </c>
       <c r="N33" t="n">
-        <v>113259877</v>
+        <v>3672686</v>
       </c>
       <c r="O33" t="n">
-        <v>75412579</v>
+        <v>14337129</v>
       </c>
       <c r="P33" t="n">
-        <v>65018097</v>
+        <v>12398474</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4547978</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/9558270</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -2552,12 +2552,12 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Публичное Акционерное Общество "Территориальная генерирующая компания № 14"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АЭРОФЛОТ-РОССИЙСКИЕ АВИАЛИНИИ"</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>7534018889</t>
+          <t>7712040126</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2571,39 +2571,39 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>21333260</v>
+        <v>760401133</v>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>460944</v>
+        <v>123037451</v>
       </c>
       <c r="I34" t="n">
-        <v>3564527</v>
+        <v>37946658</v>
       </c>
       <c r="J34" t="n">
-        <v>8156340</v>
+        <v>29187913</v>
       </c>
       <c r="K34" t="n">
-        <v>19804235</v>
+        <v>176229912</v>
       </c>
       <c r="L34" t="n">
-        <v>5813933</v>
+        <v>36986045</v>
       </c>
       <c r="M34" t="n">
-        <v>2689720</v>
+        <v>39832097</v>
       </c>
       <c r="N34" t="n">
-        <v>8234169</v>
+        <v>26745345</v>
       </c>
       <c r="O34" t="n">
-        <v>12624099</v>
+        <v>244264335</v>
       </c>
       <c r="P34" t="n">
-        <v>12484258</v>
+        <v>311968276</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/1178818</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4444528</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -2616,12 +2616,12 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Акционерное общество "ПОЛИПЛАСТ"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ТРАНСКОНТЕЙНЕР"</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>7708186108</t>
+          <t>7708591995</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2635,39 +2635,39 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2672312</v>
+        <v>159888098</v>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>674988</v>
+        <v>-9221825</v>
       </c>
       <c r="I35" t="n">
-        <v>-6078380</v>
+        <v>-8853321</v>
       </c>
       <c r="J35" t="n">
-        <v>958181</v>
+        <v>1574985</v>
       </c>
       <c r="K35" t="n">
-        <v>46531139</v>
+        <v>125836199</v>
       </c>
       <c r="L35" t="n">
-        <v>7980825</v>
+        <v>61127838</v>
       </c>
       <c r="M35" t="n">
-        <v>4460162</v>
+        <v>24364741</v>
       </c>
       <c r="N35" t="n">
-        <v>1054490</v>
+        <v>15449282</v>
       </c>
       <c r="O35" t="n">
-        <v>10572743</v>
+        <v>36335898</v>
       </c>
       <c r="P35" t="n">
-        <v>8104372</v>
+        <v>82194584</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2277439</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6412227</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2680,12 +2680,12 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ДелоПортс"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "ФЕДЕРАЛЬНАЯ ПАССАЖИРСКАЯ КОМПАНИЯ"</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7706420120</t>
+          <t>7708709686</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2699,39 +2699,39 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>124512</v>
+        <v>427758435</v>
       </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="n">
-        <v>73553032</v>
+        <v>19596889</v>
       </c>
       <c r="I36" t="n">
-        <v>-4022056</v>
+        <v>76910023</v>
       </c>
       <c r="J36" t="n">
-        <v>80452</v>
+        <v>7774844</v>
       </c>
       <c r="K36" t="n">
-        <v>63744005</v>
+        <v>92653852</v>
       </c>
       <c r="L36" t="n">
-        <v>22368376</v>
+        <v>751192</v>
       </c>
       <c r="M36" t="n">
-        <v>11369181</v>
+        <v>13255112</v>
       </c>
       <c r="N36" t="n">
-        <v>88264659</v>
+        <v>293516869</v>
       </c>
       <c r="O36" t="n">
-        <v>22183196</v>
+        <v>43777290</v>
       </c>
       <c r="P36" t="n">
-        <v>22990992</v>
+        <v>72972691</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/9184684</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3615924</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -2744,12 +2744,12 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "А101"</t>
+          <t>Общество с ограниченной ответственностью "РЕСО-Лизинг"</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7704810149</t>
+          <t>7709431786</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2763,39 +2763,39 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>21202430</v>
+        <v>30347758</v>
       </c>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="n">
-        <v>16040081</v>
+        <v>408506</v>
       </c>
       <c r="I37" t="n">
-        <v>11327840</v>
+        <v>36344239</v>
       </c>
       <c r="J37" t="n">
-        <v>3944321</v>
+        <v>17737597</v>
       </c>
       <c r="K37" t="n">
-        <v>75879853</v>
+        <v>94245992</v>
       </c>
       <c r="L37" t="n">
-        <v>15570300</v>
+        <v>52538388</v>
       </c>
       <c r="M37" t="n">
-        <v>4121425</v>
+        <v>18836863</v>
       </c>
       <c r="N37" t="n">
-        <v>38081901</v>
+        <v>25624330</v>
       </c>
       <c r="O37" t="n">
-        <v>41317852</v>
+        <v>73862867</v>
       </c>
       <c r="P37" t="n">
-        <v>50340260</v>
+        <v>60252372</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/587902</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2464306</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -2808,12 +2808,12 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Акционерное общество "Эталон-Финанс"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АВТОБАН-ФИНАНС"</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7705619586</t>
+          <t>7708813750</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2827,39 +2827,37 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>29228</v>
+        <v>2595484</v>
       </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>2745058</v>
+        <v>8251</v>
       </c>
       <c r="I38" t="n">
-        <v>-7266612</v>
+        <v>34686</v>
       </c>
       <c r="J38" t="n">
-        <v>110385</v>
+        <v>52339</v>
       </c>
       <c r="K38" t="n">
-        <v>84443748</v>
+        <v>23223573</v>
       </c>
       <c r="L38" t="n">
-        <v>25203437</v>
-      </c>
-      <c r="M38" t="n">
-        <v>8929388</v>
-      </c>
+        <v>8233755</v>
+      </c>
+      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
-        <v>35229067</v>
+        <v>71788</v>
       </c>
       <c r="O38" t="n">
-        <v>4753665</v>
+        <v>23322669</v>
       </c>
       <c r="P38" t="n">
-        <v>25403641</v>
+        <v>8266063</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2380269</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/8573680</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -2872,12 +2870,12 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "РЕСО-Лизинг"</t>
+          <t>Общество с ограниченной ответственностью "реСтор"</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7709431786</t>
+          <t>7709678550</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2891,39 +2889,39 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>30347758</v>
+        <v>22437973</v>
       </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>408506</v>
+        <v>-241871</v>
       </c>
       <c r="I39" t="n">
-        <v>36344239</v>
+        <v>2508012</v>
       </c>
       <c r="J39" t="n">
-        <v>17737597</v>
+        <v>576677</v>
       </c>
       <c r="K39" t="n">
-        <v>94245992</v>
+        <v>3786701</v>
       </c>
       <c r="L39" t="n">
-        <v>52538388</v>
+        <v>2786701</v>
       </c>
       <c r="M39" t="n">
-        <v>18836863</v>
+        <v>1635073</v>
       </c>
       <c r="N39" t="n">
-        <v>25624330</v>
+        <v>4345419</v>
       </c>
       <c r="O39" t="n">
-        <v>73862867</v>
+        <v>8995976</v>
       </c>
       <c r="P39" t="n">
-        <v>60252372</v>
+        <v>5486584</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2464306</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3032486</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -2936,12 +2934,12 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АВТОБАН-ФИНАНС"</t>
+          <t>ООО "СОВКОМБАНК ЛИЗИНГ"</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7708813750</t>
+          <t>7709780434</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2955,37 +2953,39 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2595484</v>
+        <v>23835197</v>
       </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>8251</v>
+        <v>522708</v>
       </c>
       <c r="I40" t="n">
-        <v>34686</v>
+        <v>-77248713</v>
       </c>
       <c r="J40" t="n">
-        <v>52339</v>
+        <v>5979137</v>
       </c>
       <c r="K40" t="n">
-        <v>23223573</v>
+        <v>116313981</v>
       </c>
       <c r="L40" t="n">
-        <v>8233755</v>
-      </c>
-      <c r="M40" t="inlineStr"/>
+        <v>74703384</v>
+      </c>
+      <c r="M40" t="n">
+        <v>14436303</v>
+      </c>
       <c r="N40" t="n">
-        <v>71788</v>
+        <v>6523589</v>
       </c>
       <c r="O40" t="n">
-        <v>23322669</v>
+        <v>52476129</v>
       </c>
       <c r="P40" t="n">
-        <v>8266063</v>
+        <v>81969714</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/8573680</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3727556</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -2998,12 +2998,12 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "ФЕДЕРАЛЬНАЯ ПАССАЖИРСКАЯ КОМПАНИЯ"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "ПЕРВАЯ ГРУЗОВАЯ КОМПАНИЯ"</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7708709686</t>
+          <t>7725806898</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3017,39 +3017,39 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>427758435</v>
+        <v>127694204</v>
       </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
-        <v>19596889</v>
+        <v>21069621</v>
       </c>
       <c r="I41" t="n">
-        <v>76910023</v>
+        <v>38744345</v>
       </c>
       <c r="J41" t="n">
-        <v>7774844</v>
+        <v>10957889</v>
       </c>
       <c r="K41" t="n">
-        <v>92653852</v>
+        <v>127579859</v>
       </c>
       <c r="L41" t="n">
-        <v>751192</v>
+        <v>13549979</v>
       </c>
       <c r="M41" t="n">
-        <v>13255112</v>
+        <v>27469731</v>
       </c>
       <c r="N41" t="n">
-        <v>293516869</v>
+        <v>76257726</v>
       </c>
       <c r="O41" t="n">
-        <v>43777290</v>
+        <v>68782080</v>
       </c>
       <c r="P41" t="n">
-        <v>72972691</v>
+        <v>40312889</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3615924</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/8153588</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -3062,12 +3062,12 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ТРАНСКОНТЕЙНЕР"</t>
+          <t>Публичное акционерное общество "Группа Черкизово"</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7708591995</t>
+          <t>7718560636</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3081,39 +3081,39 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>159888098</v>
+        <v>26760125</v>
       </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="n">
-        <v>-9221825</v>
+        <v>13328027</v>
       </c>
       <c r="I42" t="n">
-        <v>-8853321</v>
+        <v>6647219</v>
       </c>
       <c r="J42" t="n">
-        <v>1574985</v>
+        <v>127133</v>
       </c>
       <c r="K42" t="n">
-        <v>125836199</v>
+        <v>42950184</v>
       </c>
       <c r="L42" t="n">
-        <v>61127838</v>
+        <v>10370584</v>
       </c>
       <c r="M42" t="n">
-        <v>24364741</v>
+        <v>6818015</v>
       </c>
       <c r="N42" t="n">
-        <v>15449282</v>
+        <v>42441028</v>
       </c>
       <c r="O42" t="n">
-        <v>36335898</v>
+        <v>75918407</v>
       </c>
       <c r="P42" t="n">
-        <v>82194584</v>
+        <v>14684828</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6412227</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2165532</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -3126,52 +3126,58 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Совком Секьюр"</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>9703193909</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2025</v>
+          <t>АО «Аэрофьюэлз»</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>7714216826</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
+      <c r="F43" t="n">
+        <v>3728700</v>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="n">
-        <v>764758</v>
+        <v>7332</v>
       </c>
       <c r="I43" t="n">
-        <v>35192</v>
+        <v>120682</v>
       </c>
       <c r="J43" t="n">
-        <v>1286080</v>
+        <v>223096</v>
       </c>
       <c r="K43" t="n">
-        <v>10632078</v>
+        <v>8276872</v>
       </c>
       <c r="L43" t="n">
-        <v>3400068</v>
+        <v>1476872</v>
       </c>
       <c r="M43" t="n">
-        <v>1853940</v>
+        <v>1187691</v>
       </c>
       <c r="N43" t="n">
-        <v>764768</v>
+        <v>612662</v>
       </c>
       <c r="O43" t="n">
-        <v>5356352</v>
+        <v>2376107</v>
       </c>
       <c r="P43" t="n">
-        <v>3590518</v>
+        <v>3935053</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12558868</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6619191</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3184,12 +3190,12 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БОРЕЦ КАПИТАЛ"</t>
+          <t>Общество с ограниченной ответственностью "ИКС 5 ФИНАНС"</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9731098069</t>
+          <t>7715630469</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3202,40 +3208,38 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>1023</v>
-      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="n">
-        <v>5086</v>
+        <v>824259</v>
       </c>
       <c r="I44" t="n">
-        <v>-8655</v>
+        <v>-68407</v>
       </c>
       <c r="J44" t="n">
-        <v>219</v>
+        <v>4174</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>202529873</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>78821657</v>
       </c>
       <c r="M44" t="n">
-        <v>25</v>
+        <v>29610326</v>
       </c>
       <c r="N44" t="n">
-        <v>223227</v>
+        <v>5109696</v>
       </c>
       <c r="O44" t="n">
-        <v>33333869</v>
+        <v>79069557</v>
       </c>
       <c r="P44" t="n">
-        <v>33311146</v>
+        <v>79066163</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11927098</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3294399</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -3248,14 +3252,18 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ЛИЗИНГОВАЯ КОМПАНИЯ ПРОСТЫЕ РЕШЕНИЯ"</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>278181110</v>
-      </c>
-      <c r="D45" t="n">
-        <v>2025</v>
+          <t>Публичное акционерное общество "ФосАгро"</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>7736216869</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -3263,39 +3271,39 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2194489</v>
+        <v>65994934</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>155122</v>
+        <v>72557476</v>
       </c>
       <c r="I45" t="n">
-        <v>-2086627</v>
+        <v>33253943</v>
       </c>
       <c r="J45" t="n">
-        <v>463109</v>
+        <v>102857</v>
       </c>
       <c r="K45" t="n">
-        <v>11391448</v>
+        <v>237249564</v>
       </c>
       <c r="L45" t="n">
-        <v>3335362</v>
+        <v>120519682</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>24591473</v>
       </c>
       <c r="N45" t="n">
-        <v>1453344</v>
+        <v>82626377</v>
       </c>
       <c r="O45" t="n">
-        <v>5990866</v>
+        <v>183614926</v>
       </c>
       <c r="P45" t="n">
-        <v>3989488</v>
+        <v>132846377</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/508857</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4499052</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
@@ -3308,52 +3316,58 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьютиризация»</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>9704138298</v>
-      </c>
-      <c r="D46" t="n">
-        <v>2025</v>
+          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "АЙДИ КОЛЛЕКТ"</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>7730233723</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="n">
+        <v>13385777</v>
+      </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="n">
-        <v>-110007</v>
+        <v>2822485</v>
       </c>
       <c r="I46" t="n">
-        <v>-2651331</v>
+        <v>-4653393</v>
       </c>
       <c r="J46" t="n">
-        <v>465777</v>
+        <v>905627</v>
       </c>
       <c r="K46" t="n">
-        <v>6436164</v>
+        <v>20833978</v>
       </c>
       <c r="L46" t="n">
-        <v>1374585</v>
+        <v>9616449</v>
       </c>
       <c r="M46" t="n">
-        <v>2595164</v>
+        <v>3590318</v>
       </c>
       <c r="N46" t="n">
-        <v>285806</v>
+        <v>6388641</v>
       </c>
       <c r="O46" t="n">
-        <v>1960665</v>
+        <v>25146186</v>
       </c>
       <c r="P46" t="n">
-        <v>1374860</v>
+        <v>9957816</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11849209</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10178314</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -3366,12 +3380,12 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ООО "СОВКОМБАНК ЛИЗИНГ"</t>
+          <t>Публичное акционерное общество "Сибур Холдинг"</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7709780434</t>
+          <t>7727547261</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3385,39 +3399,39 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>23835197</v>
+        <v>1161179501</v>
       </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>522708</v>
+        <v>176772395</v>
       </c>
       <c r="I47" t="n">
-        <v>-77248713</v>
+        <v>27705480</v>
       </c>
       <c r="J47" t="n">
-        <v>5979137</v>
+        <v>132919086</v>
       </c>
       <c r="K47" t="n">
-        <v>116313981</v>
+        <v>1085975337</v>
       </c>
       <c r="L47" t="n">
-        <v>74703384</v>
+        <v>168385812</v>
       </c>
       <c r="M47" t="n">
-        <v>14436303</v>
+        <v>133854196</v>
       </c>
       <c r="N47" t="n">
-        <v>6523589</v>
+        <v>1000189134</v>
       </c>
       <c r="O47" t="n">
-        <v>52476129</v>
+        <v>494671950</v>
       </c>
       <c r="P47" t="n">
-        <v>81969714</v>
+        <v>475585507</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3727556</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4918019</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -3430,12 +3444,12 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "реСтор"</t>
+          <t>Общество с ограниченной ответственностью "ГАЗПРОМ КАПИТАЛ"</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7709678550</t>
+          <t>7726588547</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3449,39 +3463,39 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>22437973</v>
+        <v>255587508</v>
       </c>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="n">
-        <v>-241871</v>
+        <v>47477495</v>
       </c>
       <c r="I48" t="n">
-        <v>2508012</v>
+        <v>-93259357</v>
       </c>
       <c r="J48" t="n">
-        <v>576677</v>
+        <v>2</v>
       </c>
       <c r="K48" t="n">
-        <v>3786701</v>
+        <v>1816745257</v>
       </c>
       <c r="L48" t="n">
-        <v>2786701</v>
+        <v>234030896</v>
       </c>
       <c r="M48" t="n">
-        <v>1635073</v>
+        <v>199460449</v>
       </c>
       <c r="N48" t="n">
-        <v>4345419</v>
+        <v>1517919504</v>
       </c>
       <c r="O48" t="n">
-        <v>8995976</v>
+        <v>345060152</v>
       </c>
       <c r="P48" t="n">
-        <v>5486584</v>
+        <v>234152191</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3032486</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3280371</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -3494,58 +3508,52 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>АО «Аэрофьюэлз»</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>7714216826</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьютиризация»</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>9704138298</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2025</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>3728700</v>
-      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="n">
-        <v>7332</v>
+        <v>-110007</v>
       </c>
       <c r="I49" t="n">
-        <v>120682</v>
+        <v>-2651331</v>
       </c>
       <c r="J49" t="n">
-        <v>223096</v>
+        <v>465777</v>
       </c>
       <c r="K49" t="n">
-        <v>8276872</v>
+        <v>6436164</v>
       </c>
       <c r="L49" t="n">
-        <v>1476872</v>
+        <v>1374585</v>
       </c>
       <c r="M49" t="n">
-        <v>1187691</v>
+        <v>2595164</v>
       </c>
       <c r="N49" t="n">
-        <v>612662</v>
+        <v>285806</v>
       </c>
       <c r="O49" t="n">
-        <v>2376107</v>
+        <v>1960665</v>
       </c>
       <c r="P49" t="n">
-        <v>3935053</v>
+        <v>1374860</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6619191</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11849209</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -3558,58 +3566,44 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АЭРОФЛОТ-РОССИЙСКИЕ АВИАЛИНИИ"</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>7712040126</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ГОСУДАРСТВЕННАЯ КОМПАНИЯ "РОССИЙСКИЕ АВТОМОБИЛЬНЫЕ ДОРОГИ"</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>7717151380</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2025</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>760401133</v>
-      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
-        <v>123037451</v>
-      </c>
-      <c r="I50" t="n">
-        <v>37946658</v>
-      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
       <c r="J50" t="n">
-        <v>29187913</v>
+        <v>88803615</v>
       </c>
       <c r="K50" t="n">
-        <v>176229912</v>
+        <v>874623492</v>
       </c>
       <c r="L50" t="n">
-        <v>36986045</v>
-      </c>
-      <c r="M50" t="n">
-        <v>39832097</v>
-      </c>
-      <c r="N50" t="n">
-        <v>26745345</v>
-      </c>
+        <v>105867965</v>
+      </c>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="O50" t="n">
-        <v>244264335</v>
+        <v>1188643663</v>
       </c>
       <c r="P50" t="n">
-        <v>311968276</v>
+        <v>137612078</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4444528</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2363264</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -3622,18 +3616,14 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Группа Черкизово"</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>7718560636</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БАЛТИЙСКИЙ ЛИЗИНГ"</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>7826705374</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2025</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3641,39 +3631,37 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>26760125</v>
+        <v>45104129</v>
       </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="n">
-        <v>13328027</v>
+        <v>2466201</v>
       </c>
       <c r="I51" t="n">
-        <v>6647219</v>
+        <v>-4449111</v>
       </c>
       <c r="J51" t="n">
-        <v>127133</v>
+        <v>6963921</v>
       </c>
       <c r="K51" t="n">
-        <v>42950184</v>
+        <v>165574135</v>
       </c>
       <c r="L51" t="n">
-        <v>10370584</v>
-      </c>
-      <c r="M51" t="n">
-        <v>6818015</v>
-      </c>
+        <v>93653647</v>
+      </c>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>42441028</v>
+        <v>23274827</v>
       </c>
       <c r="O51" t="n">
-        <v>75918407</v>
+        <v>87273492</v>
       </c>
       <c r="P51" t="n">
-        <v>14684828</v>
+        <v>103980085</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2165532</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4075359</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -3686,12 +3674,12 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ЭЛЕКТРОРЕШЕНИЯ"</t>
+          <t>Акционерное общество "БИЗНЕС АЛЬЯНС"</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7721403552</t>
+          <t>7708582197</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3705,39 +3693,39 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>21521540</v>
+        <v>3287008</v>
       </c>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="n">
-        <v>-223905</v>
+        <v>164824</v>
       </c>
       <c r="I52" t="n">
-        <v>1089672</v>
+        <v>251568</v>
       </c>
       <c r="J52" t="n">
-        <v>1697179</v>
+        <v>1137165</v>
       </c>
       <c r="K52" t="n">
-        <v>6168848</v>
+        <v>13906586</v>
       </c>
       <c r="L52" t="n">
-        <v>4705327</v>
+        <v>3403746</v>
       </c>
       <c r="M52" t="n">
-        <v>1289262</v>
+        <v>3000316</v>
       </c>
       <c r="N52" t="n">
-        <v>3672686</v>
+        <v>1147511</v>
       </c>
       <c r="O52" t="n">
-        <v>14337129</v>
+        <v>15661718</v>
       </c>
       <c r="P52" t="n">
-        <v>12398474</v>
+        <v>4086389</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/9558270</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4746734</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -3750,12 +3738,12 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ИКС 5 ФИНАНС"</t>
+          <t>Публичное акционерное общество "Софтлайн"</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>7715630469</t>
+          <t>7736227885</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3768,38 +3756,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
+      <c r="F53" t="n">
+        <v>26297499</v>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="n">
-        <v>824259</v>
+        <v>262302</v>
       </c>
       <c r="I53" t="n">
-        <v>-68407</v>
+        <v>-7996798</v>
       </c>
       <c r="J53" t="n">
-        <v>4174</v>
+        <v>1989588</v>
       </c>
       <c r="K53" t="n">
-        <v>202529873</v>
+        <v>24815793</v>
       </c>
       <c r="L53" t="n">
-        <v>78821657</v>
+        <v>24815793</v>
       </c>
       <c r="M53" t="n">
-        <v>29610326</v>
+        <v>4907477</v>
       </c>
       <c r="N53" t="n">
-        <v>5109696</v>
+        <v>22994710</v>
       </c>
       <c r="O53" t="n">
-        <v>79069557</v>
+        <v>58488360</v>
       </c>
       <c r="P53" t="n">
-        <v>79066163</v>
+        <v>37832470</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3294399</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7152470</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -3812,12 +3802,12 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ГОСУДАРСТВЕННАЯ КОМПАНИЯ "РОССИЙСКИЕ АВТОМОБИЛЬНЫЕ ДОРОГИ"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "МЕДСКАН"</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>7717151380</t>
+          <t>7736328675</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3830,30 +3820,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
+      <c r="F54" t="n">
+        <v>114398</v>
+      </c>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
+      <c r="H54" t="n">
+        <v>-1954241</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-3463650</v>
+      </c>
       <c r="J54" t="n">
-        <v>88803615</v>
+        <v>210293</v>
       </c>
       <c r="K54" t="n">
-        <v>874623492</v>
+        <v>10883764</v>
       </c>
       <c r="L54" t="n">
-        <v>105867965</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+        <v>2438241</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1905512</v>
+      </c>
+      <c r="N54" t="n">
+        <v>11167761</v>
+      </c>
       <c r="O54" t="n">
-        <v>1188643663</v>
+        <v>4303532</v>
       </c>
       <c r="P54" t="n">
-        <v>137612078</v>
+        <v>2667429</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2363264</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11352704</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -3866,12 +3866,12 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "ПЕРВАЯ ГРУЗОВАЯ КОМПАНИЯ"</t>
+          <t>Публичное акционерное общество "Мобильные ТелеСистемы"</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>7725806898</t>
+          <t>7740000076</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3885,39 +3885,39 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>127694204</v>
+        <v>476837411</v>
       </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="n">
-        <v>21069621</v>
+        <v>26025836</v>
       </c>
       <c r="I55" t="n">
-        <v>38744345</v>
+        <v>66160709</v>
       </c>
       <c r="J55" t="n">
-        <v>10957889</v>
+        <v>7076512</v>
       </c>
       <c r="K55" t="n">
-        <v>127579859</v>
+        <v>975762072</v>
       </c>
       <c r="L55" t="n">
-        <v>13549979</v>
+        <v>394064198</v>
       </c>
       <c r="M55" t="n">
-        <v>27469731</v>
+        <v>183657184</v>
       </c>
       <c r="N55" t="n">
-        <v>76257726</v>
+        <v>126241392</v>
       </c>
       <c r="O55" t="n">
-        <v>68782080</v>
+        <v>140594093</v>
       </c>
       <c r="P55" t="n">
-        <v>40312889</v>
+        <v>646413416</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/8153588</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7155648</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -3930,12 +3930,12 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ГАЗПРОМ КАПИТАЛ"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ИНТЕРЛИЗИНГ"</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>7726588547</t>
+          <t>7802131219</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3949,39 +3949,39 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>255587508</v>
+        <v>15617549</v>
       </c>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>47477495</v>
+        <v>1360216</v>
       </c>
       <c r="I56" t="n">
-        <v>-93259357</v>
+        <v>12804691</v>
       </c>
       <c r="J56" t="n">
-        <v>2</v>
+        <v>3411231</v>
       </c>
       <c r="K56" t="n">
-        <v>1816745257</v>
+        <v>46966786</v>
       </c>
       <c r="L56" t="n">
-        <v>234030896</v>
+        <v>30193215</v>
       </c>
       <c r="M56" t="n">
-        <v>199460449</v>
+        <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>1517919504</v>
+        <v>16029601</v>
       </c>
       <c r="O56" t="n">
-        <v>345060152</v>
+        <v>36280782</v>
       </c>
       <c r="P56" t="n">
-        <v>234152191</v>
+        <v>37865717</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3280371</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6475614</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -3994,12 +3994,12 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "АЙДИ КОЛЛЕКТ"</t>
+          <t>Общество с ограниченной ответственностью "Сэтл Групп"</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>7730233723</t>
+          <t>7810245481</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4013,39 +4013,39 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>13385777</v>
+        <v>13167515</v>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="n">
-        <v>2822485</v>
+        <v>11312897</v>
       </c>
       <c r="I57" t="n">
-        <v>-4653393</v>
+        <v>1184853</v>
       </c>
       <c r="J57" t="n">
-        <v>905627</v>
+        <v>1345291</v>
       </c>
       <c r="K57" t="n">
-        <v>20833978</v>
+        <v>56921724</v>
       </c>
       <c r="L57" t="n">
-        <v>9616449</v>
+        <v>15976724</v>
       </c>
       <c r="M57" t="n">
-        <v>3590318</v>
+        <v>8935923</v>
       </c>
       <c r="N57" t="n">
-        <v>6388641</v>
+        <v>15386096</v>
       </c>
       <c r="O57" t="n">
-        <v>25146186</v>
+        <v>29645490</v>
       </c>
       <c r="P57" t="n">
-        <v>9957816</v>
+        <v>22550613</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10178314</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7065187</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
@@ -4058,12 +4058,12 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Сибур Холдинг"</t>
+          <t>Публичное акционерное общество "Россети Ленэнерго"</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>7727547261</t>
+          <t>7803002209</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4077,39 +4077,39 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1161179501</v>
+        <v>142913416</v>
       </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>176772395</v>
+        <v>34251000</v>
       </c>
       <c r="I58" t="n">
-        <v>27705480</v>
+        <v>73224364</v>
       </c>
       <c r="J58" t="n">
-        <v>132919086</v>
+        <v>48361489</v>
       </c>
       <c r="K58" t="n">
-        <v>1085975337</v>
+        <v>26560960</v>
       </c>
       <c r="L58" t="n">
-        <v>168385812</v>
+        <v>16560960</v>
       </c>
       <c r="M58" t="n">
-        <v>133854196</v>
+        <v>385713</v>
       </c>
       <c r="N58" t="n">
-        <v>1000189134</v>
+        <v>233316079</v>
       </c>
       <c r="O58" t="n">
-        <v>494671950</v>
+        <v>66874847</v>
       </c>
       <c r="P58" t="n">
-        <v>475585507</v>
+        <v>76842723</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4918019</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7044724</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4122,12 +4122,12 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Акционерное общество "Селектел"</t>
+          <t>Акционерное общество "АСФАЛЬТОБЕТОННЫЙ ЗАВОД № 1"</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>7810962785</t>
+          <t>7804016807</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4141,39 +4141,39 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>16049975</v>
+        <v>9221435</v>
       </c>
       <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>2783286</v>
+        <v>740510</v>
       </c>
       <c r="I59" t="n">
-        <v>4083327</v>
+        <v>-2235493</v>
       </c>
       <c r="J59" t="n">
-        <v>603311</v>
+        <v>2733758</v>
       </c>
       <c r="K59" t="n">
-        <v>18736466</v>
+        <v>11859777</v>
       </c>
       <c r="L59" t="n">
-        <v>7416234</v>
+        <v>2519772</v>
       </c>
       <c r="M59" t="n">
-        <v>2693274</v>
+        <v>1548669</v>
       </c>
       <c r="N59" t="n">
-        <v>4668499</v>
+        <v>4129194</v>
       </c>
       <c r="O59" t="n">
-        <v>2366382</v>
+        <v>16016256</v>
       </c>
       <c r="P59" t="n">
-        <v>12799984</v>
+        <v>3422702</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12489652</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6492191</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -4186,12 +4186,12 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Акционерное общество "АСФАЛЬТОБЕТОННЫЙ ЗАВОД № 1"</t>
+          <t>Акционерное общество "Первый контейнерный терминал"</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>7804016807</t>
+          <t>7805113497</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4205,39 +4205,39 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>9221435</v>
+        <v>6203239</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>740510</v>
+        <v>1407136</v>
       </c>
       <c r="I60" t="n">
-        <v>-2235493</v>
+        <v>-128768</v>
       </c>
       <c r="J60" t="n">
-        <v>2733758</v>
+        <v>652569</v>
       </c>
       <c r="K60" t="n">
-        <v>11859777</v>
+        <v>14147311</v>
       </c>
       <c r="L60" t="n">
-        <v>2519772</v>
+        <v>255384</v>
       </c>
       <c r="M60" t="n">
-        <v>1548669</v>
+        <v>2032410</v>
       </c>
       <c r="N60" t="n">
-        <v>4129194</v>
+        <v>8678846</v>
       </c>
       <c r="O60" t="n">
-        <v>16016256</v>
+        <v>1289863</v>
       </c>
       <c r="P60" t="n">
-        <v>3422702</v>
+        <v>753349</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6492191</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7066135</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -4250,12 +4250,12 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "ФосАгро"</t>
+          <t>АО ЛК "РОДЕЛЕН"</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>7736216869</t>
+          <t>7813379412</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4269,39 +4269,39 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>65994934</v>
+        <v>1348020</v>
       </c>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="n">
-        <v>72557476</v>
+        <v>151933</v>
       </c>
       <c r="I61" t="n">
-        <v>33253943</v>
+        <v>1991103</v>
       </c>
       <c r="J61" t="n">
-        <v>102857</v>
+        <v>426055</v>
       </c>
       <c r="K61" t="n">
-        <v>237249564</v>
+        <v>6411813</v>
       </c>
       <c r="L61" t="n">
-        <v>120519682</v>
+        <v>53039</v>
       </c>
       <c r="M61" t="n">
-        <v>24591473</v>
+        <v>1136499</v>
       </c>
       <c r="N61" t="n">
-        <v>82626377</v>
+        <v>754993</v>
       </c>
       <c r="O61" t="n">
-        <v>183614926</v>
+        <v>6587642</v>
       </c>
       <c r="P61" t="n">
-        <v>132846377</v>
+        <v>613953</v>
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4499052</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/6099662</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -4314,12 +4314,12 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Софтлайн"</t>
+          <t>Акционерное общество "Селектел"</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>7736227885</t>
+          <t>7810962785</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4333,39 +4333,39 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>26297499</v>
+        <v>16049975</v>
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="n">
-        <v>262302</v>
+        <v>2783286</v>
       </c>
       <c r="I62" t="n">
-        <v>-7996798</v>
+        <v>4083327</v>
       </c>
       <c r="J62" t="n">
-        <v>1989588</v>
+        <v>603311</v>
       </c>
       <c r="K62" t="n">
-        <v>24815793</v>
+        <v>18736466</v>
       </c>
       <c r="L62" t="n">
-        <v>24815793</v>
+        <v>7416234</v>
       </c>
       <c r="M62" t="n">
-        <v>4907477</v>
+        <v>2693274</v>
       </c>
       <c r="N62" t="n">
-        <v>22994710</v>
+        <v>4668499</v>
       </c>
       <c r="O62" t="n">
-        <v>58488360</v>
+        <v>2366382</v>
       </c>
       <c r="P62" t="n">
-        <v>37832470</v>
+        <v>12799984</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7152470</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12489652</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -4378,12 +4378,12 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "МЕДСКАН"</t>
+          <t>Общество с ограниченной ответственностью "Арлифт Интернешнл"</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>7736328675</t>
+          <t>7820331348</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4397,39 +4397,39 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>114398</v>
+        <v>5457083</v>
       </c>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>-1954241</v>
+        <v>520734</v>
       </c>
       <c r="I63" t="n">
-        <v>-3463650</v>
+        <v>1663667</v>
       </c>
       <c r="J63" t="n">
-        <v>210293</v>
+        <v>109268</v>
       </c>
       <c r="K63" t="n">
-        <v>10883764</v>
+        <v>128239</v>
       </c>
       <c r="L63" t="n">
-        <v>2438241</v>
+        <v>102399</v>
       </c>
       <c r="M63" t="n">
-        <v>1905512</v>
+        <v>987970</v>
       </c>
       <c r="N63" t="n">
-        <v>11167761</v>
+        <v>1208716</v>
       </c>
       <c r="O63" t="n">
-        <v>4303532</v>
+        <v>2219692</v>
       </c>
       <c r="P63" t="n">
-        <v>2667429</v>
+        <v>3792606</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11352704</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7720538</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -4442,12 +4442,12 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Мобильные ТелеСистемы"</t>
+          <t>Публичное Акционерное Общество "Инарктика"</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>7740000076</t>
+          <t>7816430057</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4461,39 +4461,39 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>476837411</v>
+        <v>1410028</v>
       </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>26025836</v>
+        <v>1130289</v>
       </c>
       <c r="I64" t="n">
-        <v>66160709</v>
+        <v>45720</v>
       </c>
       <c r="J64" t="n">
-        <v>7076512</v>
+        <v>700723</v>
       </c>
       <c r="K64" t="n">
-        <v>975762072</v>
+        <v>10047195</v>
       </c>
       <c r="L64" t="n">
-        <v>394064198</v>
+        <v>47195</v>
       </c>
       <c r="M64" t="n">
-        <v>183657184</v>
+        <v>1091903</v>
       </c>
       <c r="N64" t="n">
-        <v>126241392</v>
+        <v>11973285</v>
       </c>
       <c r="O64" t="n">
-        <v>140594093</v>
+        <v>2177851</v>
       </c>
       <c r="P64" t="n">
-        <v>646413416</v>
+        <v>69325</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7155648</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/112740</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -4506,12 +4506,12 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ИНТЕРЛИЗИНГ"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГРУППА ПОЗИТИВ"</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>7802131219</t>
+          <t>9718077239</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4525,39 +4525,39 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>15617549</v>
+        <v>0</v>
       </c>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="n">
-        <v>1360216</v>
+        <v>-2319012</v>
       </c>
       <c r="I65" t="n">
-        <v>12804691</v>
+        <v>-3043148</v>
       </c>
       <c r="J65" t="n">
-        <v>3411231</v>
+        <v>85073</v>
       </c>
       <c r="K65" t="n">
-        <v>46966786</v>
+        <v>20333431</v>
       </c>
       <c r="L65" t="n">
-        <v>30193215</v>
+        <v>533431</v>
       </c>
       <c r="M65" t="n">
-        <v>0</v>
+        <v>3093490</v>
       </c>
       <c r="N65" t="n">
-        <v>16029601</v>
+        <v>14618010</v>
       </c>
       <c r="O65" t="n">
-        <v>36280782</v>
+        <v>6251325</v>
       </c>
       <c r="P65" t="n">
-        <v>37865717</v>
+        <v>542917</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6475614</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10388722</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
@@ -4570,12 +4570,12 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Россети Ленэнерго"</t>
+          <t>ООО «БИННОФАРМ ГРУПП»</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>7803002209</t>
+          <t>9704005675</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4589,39 +4589,39 @@
         </is>
       </c>
       <c r="F66" t="n">
-        <v>142913416</v>
+        <v>39152023</v>
       </c>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="n">
-        <v>34251000</v>
+        <v>-3437553</v>
       </c>
       <c r="I66" t="n">
-        <v>73224364</v>
+        <v>-10088180</v>
       </c>
       <c r="J66" t="n">
-        <v>48361489</v>
+        <v>2741369</v>
       </c>
       <c r="K66" t="n">
-        <v>26560960</v>
+        <v>31048484</v>
       </c>
       <c r="L66" t="n">
-        <v>16560960</v>
+        <v>27198484</v>
       </c>
       <c r="M66" t="n">
-        <v>385713</v>
+        <v>6612689</v>
       </c>
       <c r="N66" t="n">
-        <v>233316079</v>
+        <v>28187621</v>
       </c>
       <c r="O66" t="n">
-        <v>66874847</v>
+        <v>49838344</v>
       </c>
       <c r="P66" t="n">
-        <v>76842723</v>
+        <v>65495561</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7044724</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11181494</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -4634,12 +4634,12 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Публичное Акционерное Общество "Инарктика"</t>
+          <t>Публичное акционерное общество "Группа ЛСР"</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>7816430057</t>
+          <t>7838360491</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4653,39 +4653,39 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1410028</v>
+        <v>18527068</v>
       </c>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>1130289</v>
+        <v>9609955</v>
       </c>
       <c r="I67" t="n">
-        <v>45720</v>
+        <v>-26787483</v>
       </c>
       <c r="J67" t="n">
-        <v>700723</v>
+        <v>2273568</v>
       </c>
       <c r="K67" t="n">
-        <v>10047195</v>
+        <v>165830803</v>
       </c>
       <c r="L67" t="n">
-        <v>47195</v>
+        <v>28617745</v>
       </c>
       <c r="M67" t="n">
-        <v>1091903</v>
+        <v>22629744</v>
       </c>
       <c r="N67" t="n">
-        <v>11973285</v>
+        <v>135293714</v>
       </c>
       <c r="O67" t="n">
-        <v>2177851</v>
+        <v>33615684</v>
       </c>
       <c r="P67" t="n">
-        <v>69325</v>
+        <v>30329614</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/112740</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4288365</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -4698,12 +4698,12 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>АО ЛК "РОДЕЛЕН"</t>
+          <t>АО ГК "АЗОТ"</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>7813379412</t>
+          <t>7838365595</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4717,39 +4717,39 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>1348020</v>
+        <v>2571736</v>
       </c>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>151933</v>
+        <v>36420149</v>
       </c>
       <c r="I68" t="n">
-        <v>1991103</v>
+        <v>-1732698</v>
       </c>
       <c r="J68" t="n">
-        <v>426055</v>
+        <v>29984</v>
       </c>
       <c r="K68" t="n">
-        <v>6411813</v>
+        <v>1141544</v>
       </c>
       <c r="L68" t="n">
-        <v>53039</v>
+        <v>141544</v>
       </c>
       <c r="M68" t="n">
-        <v>1136499</v>
+        <v>508238</v>
       </c>
       <c r="N68" t="n">
-        <v>754993</v>
+        <v>32473493</v>
       </c>
       <c r="O68" t="n">
-        <v>6587642</v>
+        <v>24407949</v>
       </c>
       <c r="P68" t="n">
-        <v>613953</v>
+        <v>3776569</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6099662</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4460769</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -4762,12 +4762,12 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Акционерное общество "Первый контейнерный терминал"</t>
+          <t>Общество с ограниченной ответственностью "Профессиональная коллекторская организация "Агентство судебного взыскания"</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>7805113497</t>
+          <t>7841019595</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4781,39 +4781,39 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>6203239</v>
+        <v>2813950</v>
       </c>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>1407136</v>
+        <v>289449</v>
       </c>
       <c r="I69" t="n">
-        <v>-128768</v>
+        <v>-782507</v>
       </c>
       <c r="J69" t="n">
-        <v>652569</v>
+        <v>439421</v>
       </c>
       <c r="K69" t="n">
-        <v>14147311</v>
+        <v>3335265</v>
       </c>
       <c r="L69" t="n">
-        <v>255384</v>
+        <v>1661751</v>
       </c>
       <c r="M69" t="n">
-        <v>2032410</v>
+        <v>634394</v>
       </c>
       <c r="N69" t="n">
-        <v>8678846</v>
+        <v>718092</v>
       </c>
       <c r="O69" t="n">
-        <v>1289863</v>
+        <v>4036728</v>
       </c>
       <c r="P69" t="n">
-        <v>753349</v>
+        <v>1804336</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7066135</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/9111808</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -4826,12 +4826,12 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Сэтл Групп"</t>
+          <t>Общество с ограниченной ответственностью "ЛЕГЕНДА"</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>7810245481</t>
+          <t>7840438730</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4845,39 +4845,39 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>13167515</v>
+        <v>2574338</v>
       </c>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="n">
-        <v>11312897</v>
+        <v>676819</v>
       </c>
       <c r="I70" t="n">
-        <v>1184853</v>
+        <v>1424991</v>
       </c>
       <c r="J70" t="n">
-        <v>1345291</v>
+        <v>2369150</v>
       </c>
       <c r="K70" t="n">
-        <v>56921724</v>
+        <v>13269288</v>
       </c>
       <c r="L70" t="n">
-        <v>15976724</v>
+        <v>5143359</v>
       </c>
       <c r="M70" t="n">
-        <v>8935923</v>
+        <v>1792096</v>
       </c>
       <c r="N70" t="n">
-        <v>15386096</v>
+        <v>988224</v>
       </c>
       <c r="O70" t="n">
-        <v>29645490</v>
+        <v>7760068</v>
       </c>
       <c r="P70" t="n">
-        <v>22550613</v>
+        <v>5682975</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7065187</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/122728</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -4890,12 +4890,12 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>АО ГК "АЗОТ"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "МВ ФИНАНС"</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>7838365595</t>
+          <t>9701168311</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4908,40 +4908,38 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>2571736</v>
-      </c>
+      <c r="F71" t="inlineStr"/>
       <c r="G71" t="inlineStr"/>
       <c r="H71" t="n">
-        <v>36420149</v>
+        <v>3493</v>
       </c>
       <c r="I71" t="n">
-        <v>-1732698</v>
+        <v>-2391603</v>
       </c>
       <c r="J71" t="n">
-        <v>29984</v>
+        <v>44911</v>
       </c>
       <c r="K71" t="n">
-        <v>1141544</v>
+        <v>7725451</v>
       </c>
       <c r="L71" t="n">
-        <v>141544</v>
+        <v>5759320</v>
       </c>
       <c r="M71" t="n">
-        <v>508238</v>
+        <v>2261066</v>
       </c>
       <c r="N71" t="n">
-        <v>32473493</v>
+        <v>95811</v>
       </c>
       <c r="O71" t="n">
-        <v>24407949</v>
+        <v>5828974</v>
       </c>
       <c r="P71" t="n">
-        <v>3776569</v>
+        <v>5765046</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4460769</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11476959</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -4954,12 +4952,12 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Группа ЛСР"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ГРУППА КОМПАНИЙ "СЕГЕЖА"</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>7838360491</t>
+          <t>9703024202</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4973,39 +4971,39 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>18527068</v>
+        <v>3234274</v>
       </c>
       <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>9609955</v>
+        <v>-81659202</v>
       </c>
       <c r="I72" t="n">
-        <v>-26787483</v>
+        <v>-15560254</v>
       </c>
       <c r="J72" t="n">
-        <v>2273568</v>
+        <v>2171160</v>
       </c>
       <c r="K72" t="n">
-        <v>165830803</v>
+        <v>68989930</v>
       </c>
       <c r="L72" t="n">
-        <v>28617745</v>
+        <v>28619951</v>
       </c>
       <c r="M72" t="n">
-        <v>22629744</v>
+        <v>17966508</v>
       </c>
       <c r="N72" t="n">
-        <v>135293714</v>
+        <v>69901335</v>
       </c>
       <c r="O72" t="n">
-        <v>33615684</v>
+        <v>16693441</v>
       </c>
       <c r="P72" t="n">
-        <v>30329614</v>
+        <v>29540756</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4288365</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11477936</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
@@ -5018,12 +5016,12 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БАЛТИЙСКИЙ ЛИЗИНГ"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ФАБРИКА ПО"</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>7826705374</t>
+          <t>9726092897</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5036,38 +5034,38 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>45104129</v>
-      </c>
+      <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="n">
-        <v>2466201</v>
+        <v>26111</v>
       </c>
       <c r="I73" t="n">
-        <v>-4449111</v>
+        <v>-116300</v>
       </c>
       <c r="J73" t="n">
-        <v>6963921</v>
+        <v>58920</v>
       </c>
       <c r="K73" t="n">
-        <v>165574135</v>
+        <v>2012480</v>
       </c>
       <c r="L73" t="n">
-        <v>93653647</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
+        <v>1961794</v>
+      </c>
+      <c r="M73" t="n">
+        <v>94487</v>
+      </c>
       <c r="N73" t="n">
-        <v>23274827</v>
+        <v>15655004</v>
       </c>
       <c r="O73" t="n">
-        <v>87273492</v>
+        <v>3749182</v>
       </c>
       <c r="P73" t="n">
-        <v>103980085</v>
+        <v>3460790</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4075359</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12624794</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -5080,12 +5078,12 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Арлифт Интернешнл"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "КАРШЕРИНГ РУССИЯ"</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>7820331348</t>
+          <t>9718236471</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5099,39 +5097,39 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>5457083</v>
+        <v>26088727</v>
       </c>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>520734</v>
+        <v>-3628694</v>
       </c>
       <c r="I74" t="n">
-        <v>1663667</v>
+        <v>6086337</v>
       </c>
       <c r="J74" t="n">
-        <v>109268</v>
+        <v>1230217</v>
       </c>
       <c r="K74" t="n">
-        <v>128239</v>
+        <v>18535372</v>
       </c>
       <c r="L74" t="n">
-        <v>102399</v>
+        <v>10535372</v>
       </c>
       <c r="M74" t="n">
-        <v>987970</v>
+        <v>5647179</v>
       </c>
       <c r="N74" t="n">
-        <v>1208716</v>
+        <v>6060673</v>
       </c>
       <c r="O74" t="n">
-        <v>2219692</v>
+        <v>6682880</v>
       </c>
       <c r="P74" t="n">
-        <v>3792606</v>
+        <v>17515458</v>
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7720538</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12289607</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
@@ -5144,52 +5142,58 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-4"</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>9703211185</v>
-      </c>
-      <c r="D75" t="n">
-        <v>2025</v>
+          <t>Публичное Акционерное общество "Лизинговая компания "Европлан"</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>9705101614</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr"/>
+      <c r="F75" t="n">
+        <v>59966125</v>
+      </c>
       <c r="G75" t="inlineStr"/>
       <c r="H75" t="n">
-        <v>977720</v>
+        <v>4034508</v>
       </c>
       <c r="I75" t="n">
-        <v>-1274588</v>
+        <v>84799387</v>
       </c>
       <c r="J75" t="n">
-        <v>2631244</v>
+        <v>7477939</v>
       </c>
       <c r="K75" t="n">
-        <v>20526472</v>
+        <v>136124027</v>
       </c>
       <c r="L75" t="n">
-        <v>4223028</v>
+        <v>73233527</v>
       </c>
       <c r="M75" t="n">
-        <v>1495620</v>
+        <v>35514645</v>
       </c>
       <c r="N75" t="n">
-        <v>977730</v>
+        <v>36127674</v>
       </c>
       <c r="O75" t="n">
-        <v>7130263</v>
+        <v>113385304</v>
       </c>
       <c r="P75" t="n">
-        <v>4225049</v>
+        <v>85482683</v>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12680884</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10283154</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
@@ -5202,52 +5206,58 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Сплит Финанс"</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>9703209122</v>
-      </c>
-      <c r="D76" t="n">
-        <v>2025</v>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВУШ"</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>9717068640</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr"/>
+      <c r="F76" t="n">
+        <v>10694433</v>
+      </c>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="n">
-        <v>832800</v>
+        <v>-2549955</v>
       </c>
       <c r="I76" t="n">
-        <v>-627668</v>
+        <v>213787</v>
       </c>
       <c r="J76" t="n">
-        <v>3157507</v>
+        <v>330829</v>
       </c>
       <c r="K76" t="n">
-        <v>12321587</v>
+        <v>13895537</v>
       </c>
       <c r="L76" t="n">
-        <v>4622403</v>
+        <v>4607881</v>
       </c>
       <c r="M76" t="n">
-        <v>794736</v>
+        <v>2583863</v>
       </c>
       <c r="N76" t="n">
-        <v>832810</v>
+        <v>410758</v>
       </c>
       <c r="O76" t="n">
-        <v>10288657</v>
+        <v>4971431</v>
       </c>
       <c r="P76" t="n">
-        <v>4649009</v>
+        <v>5382399</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12663922</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10703464</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
@@ -5260,52 +5270,58 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-6"</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>9703221553</v>
-      </c>
-      <c r="D77" t="n">
-        <v>2025</v>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГЛОРАКС"</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>9729387137</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr"/>
+      <c r="F77" t="n">
+        <v>3057693</v>
+      </c>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>421691</v>
+        <v>352891</v>
       </c>
       <c r="I77" t="n">
-        <v>-16243</v>
+        <v>-2487508</v>
       </c>
       <c r="J77" t="n">
-        <v>1996969</v>
+        <v>17468</v>
       </c>
       <c r="K77" t="n">
-        <v>31400566</v>
+        <v>15888211</v>
       </c>
       <c r="L77" t="n">
-        <v>191416</v>
+        <v>7131352</v>
       </c>
       <c r="M77" t="n">
-        <v>191760</v>
+        <v>3563226</v>
       </c>
       <c r="N77" t="n">
-        <v>421701</v>
+        <v>5262202</v>
       </c>
       <c r="O77" t="n">
-        <v>11406621</v>
+        <v>9887498</v>
       </c>
       <c r="P77" t="n">
-        <v>592089</v>
+        <v>7607515</v>
       </c>
       <c r="Q77" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12744848</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12558009</t>
         </is>
       </c>
       <c r="R77" t="inlineStr">
@@ -5318,12 +5334,12 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Профессиональная коллекторская организация "Агентство судебного взыскания"</t>
+          <t>АКЦИОНЕРНОЕ ОБЩЕСТВО "АВТОАССИСТАНС"</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>7841019595</t>
+          <t>7706640206</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -5337,39 +5353,39 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2813950</v>
+        <v>1503909</v>
       </c>
       <c r="G78" t="inlineStr"/>
       <c r="H78" t="n">
-        <v>289449</v>
+        <v>105842</v>
       </c>
       <c r="I78" t="n">
-        <v>-782507</v>
+        <v>181309</v>
       </c>
       <c r="J78" t="n">
-        <v>439421</v>
+        <v>65389</v>
       </c>
       <c r="K78" t="n">
-        <v>3335265</v>
+        <v>19559</v>
       </c>
       <c r="L78" t="n">
-        <v>1661751</v>
+        <v>3013</v>
       </c>
       <c r="M78" t="n">
-        <v>634394</v>
+        <v>9644</v>
       </c>
       <c r="N78" t="n">
-        <v>718092</v>
+        <v>140239</v>
       </c>
       <c r="O78" t="n">
-        <v>4036728</v>
+        <v>197135</v>
       </c>
       <c r="P78" t="n">
-        <v>1804336</v>
+        <v>358396</v>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/9111808</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3042951</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
@@ -5382,12 +5398,12 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "ЛЕГЕНДА"</t>
+          <t>Общество с ограниченной ответственностью "ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ "ФИНЭКВА"</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>7840438730</t>
+          <t>7300023241</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -5401,39 +5417,39 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2574338</v>
+        <v>508111</v>
       </c>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>676819</v>
+        <v>61451</v>
       </c>
       <c r="I79" t="n">
-        <v>1424991</v>
+        <v>-429754</v>
       </c>
       <c r="J79" t="n">
-        <v>2369150</v>
+        <v>20163</v>
       </c>
       <c r="K79" t="n">
-        <v>13269288</v>
+        <v>1396326</v>
       </c>
       <c r="L79" t="n">
-        <v>5143359</v>
+        <v>781396</v>
       </c>
       <c r="M79" t="n">
-        <v>1792096</v>
+        <v>235294</v>
       </c>
       <c r="N79" t="n">
-        <v>988224</v>
+        <v>99413</v>
       </c>
       <c r="O79" t="n">
-        <v>7760068</v>
+        <v>1493301</v>
       </c>
       <c r="P79" t="n">
-        <v>5682975</v>
+        <v>798708</v>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/122728</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12249089</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
@@ -5446,12 +5462,12 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "Филберт"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "БОРЕЦ КАПИТАЛ"</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>7841430420</t>
+          <t>9731098069</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -5465,39 +5481,39 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>8586868</v>
+        <v>1023</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>3152859</v>
+        <v>5086</v>
       </c>
       <c r="I80" t="n">
-        <v>-2961381</v>
+        <v>-8655</v>
       </c>
       <c r="J80" t="n">
-        <v>130669</v>
+        <v>219</v>
       </c>
       <c r="K80" t="n">
-        <v>4275711</v>
+        <v>0</v>
       </c>
       <c r="L80" t="n">
-        <v>2275535</v>
+        <v>0</v>
       </c>
       <c r="M80" t="n">
-        <v>560901</v>
+        <v>25</v>
       </c>
       <c r="N80" t="n">
-        <v>9134906</v>
+        <v>223227</v>
       </c>
       <c r="O80" t="n">
-        <v>13555399</v>
+        <v>33333869</v>
       </c>
       <c r="P80" t="n">
-        <v>2486647</v>
+        <v>33311146</v>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/1655225</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11927098</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
@@ -5510,18 +5526,14 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "МВ ФИНАНС"</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>9701168311</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-1"</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>9704256936</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2025</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5531,35 +5543,35 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>3493</v>
+        <v>462857</v>
       </c>
       <c r="I81" t="n">
-        <v>-2391603</v>
+        <v>-690900</v>
       </c>
       <c r="J81" t="n">
-        <v>44911</v>
+        <v>1467792</v>
       </c>
       <c r="K81" t="n">
-        <v>7725451</v>
+        <v>12652034</v>
       </c>
       <c r="L81" t="n">
-        <v>5759320</v>
+        <v>2707767</v>
       </c>
       <c r="M81" t="n">
-        <v>2261066</v>
+        <v>740205</v>
       </c>
       <c r="N81" t="n">
-        <v>95811</v>
+        <v>462867</v>
       </c>
       <c r="O81" t="n">
-        <v>5828974</v>
+        <v>4761718</v>
       </c>
       <c r="P81" t="n">
-        <v>5765046</v>
+        <v>2710789</v>
       </c>
       <c r="Q81" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11476959</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12624837</t>
         </is>
       </c>
       <c r="R81" t="inlineStr">
@@ -5572,58 +5584,52 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ВУШ"</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>9717068640</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-2"</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>9704264662</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2025</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>10694433</v>
-      </c>
+      <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="n">
-        <v>-2549955</v>
+        <v>966</v>
       </c>
       <c r="I82" t="n">
-        <v>213787</v>
+        <v>-439</v>
       </c>
       <c r="J82" t="n">
-        <v>330829</v>
+        <v>2571</v>
       </c>
       <c r="K82" t="n">
-        <v>13895537</v>
+        <v>3133</v>
       </c>
       <c r="L82" t="n">
-        <v>4607881</v>
+        <v>3133</v>
       </c>
       <c r="M82" t="n">
-        <v>2583863</v>
+        <v>133</v>
       </c>
       <c r="N82" t="n">
-        <v>410758</v>
+        <v>-956</v>
       </c>
       <c r="O82" t="n">
-        <v>4971431</v>
+        <v>2571</v>
       </c>
       <c r="P82" t="n">
-        <v>5382399</v>
+        <v>3527</v>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10703464</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12755483</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
@@ -5636,58 +5642,46 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО ГРУППА КОМПАНИЙ "СЕГЕЖА"</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>9703024202</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО "СБ СЕКЬЮРИТИЗАЦИЯ 5"</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>9703163693</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2025</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>3234274</v>
-      </c>
+      <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="n">
-        <v>-81659202</v>
+        <v>-65</v>
       </c>
       <c r="I83" t="n">
-        <v>-15560254</v>
+        <v>-266</v>
       </c>
       <c r="J83" t="n">
-        <v>2171160</v>
-      </c>
-      <c r="K83" t="n">
-        <v>68989930</v>
-      </c>
-      <c r="L83" t="n">
-        <v>28619951</v>
-      </c>
-      <c r="M83" t="n">
-        <v>17966508</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
-        <v>69901335</v>
+        <v>13</v>
       </c>
       <c r="O83" t="n">
-        <v>16693441</v>
+        <v>13</v>
       </c>
       <c r="P83" t="n">
-        <v>29540756</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11477936</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12333197</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
@@ -5700,58 +5694,52 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ООО «БИННОФАРМ ГРУПП»</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>9704005675</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-4"</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>9703211185</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2025</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>39152023</v>
-      </c>
+      <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="n">
-        <v>-3437553</v>
+        <v>977720</v>
       </c>
       <c r="I84" t="n">
-        <v>-10088180</v>
+        <v>-1274588</v>
       </c>
       <c r="J84" t="n">
-        <v>2741369</v>
+        <v>2631244</v>
       </c>
       <c r="K84" t="n">
-        <v>31048484</v>
+        <v>20526472</v>
       </c>
       <c r="L84" t="n">
-        <v>27198484</v>
+        <v>4223028</v>
       </c>
       <c r="M84" t="n">
-        <v>6612689</v>
+        <v>1495620</v>
       </c>
       <c r="N84" t="n">
-        <v>28187621</v>
+        <v>977730</v>
       </c>
       <c r="O84" t="n">
-        <v>49838344</v>
+        <v>7130263</v>
       </c>
       <c r="P84" t="n">
-        <v>65495561</v>
+        <v>4225049</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11181494</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12680884</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
@@ -5764,12 +5752,12 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Публичное Акционерное общество "Лизинговая компания "Европлан"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ  "МЭЙЛ.РУ ФИНАНС"</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>9705101614</t>
+          <t>7714431630</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -5782,40 +5770,38 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>59966125</v>
-      </c>
+      <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="n">
-        <v>4034508</v>
+        <v>24100</v>
       </c>
       <c r="I85" t="n">
-        <v>84799387</v>
+        <v>-1276602</v>
       </c>
       <c r="J85" t="n">
-        <v>7477939</v>
+        <v>1337</v>
       </c>
       <c r="K85" t="n">
-        <v>136124027</v>
+        <v>15344121</v>
       </c>
       <c r="L85" t="n">
-        <v>73233527</v>
+        <v>15344121</v>
       </c>
       <c r="M85" t="n">
-        <v>35514645</v>
+        <v>1214827</v>
       </c>
       <c r="N85" t="n">
-        <v>36127674</v>
+        <v>72448</v>
       </c>
       <c r="O85" t="n">
-        <v>113385304</v>
+        <v>15494691</v>
       </c>
       <c r="P85" t="n">
-        <v>85482683</v>
+        <v>15422243</v>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10283154</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10789823</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
@@ -5828,12 +5814,12 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "КАРШЕРИНГ РУССИЯ"</t>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "АПТЕЧНАЯ СЕТЬ 36,6"</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>9718236471</t>
+          <t>7722266450</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5847,39 +5833,39 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>26088727</v>
+        <v>6445395</v>
       </c>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="n">
-        <v>-3628694</v>
+        <v>43524</v>
       </c>
       <c r="I86" t="n">
-        <v>6086337</v>
+        <v>-4513236</v>
       </c>
       <c r="J86" t="n">
-        <v>1230217</v>
+        <v>27107</v>
       </c>
       <c r="K86" t="n">
-        <v>18535372</v>
+        <v>31638100</v>
       </c>
       <c r="L86" t="n">
-        <v>10535372</v>
+        <v>388100</v>
       </c>
       <c r="M86" t="n">
-        <v>5647179</v>
+        <v>7235175</v>
       </c>
       <c r="N86" t="n">
-        <v>6060673</v>
+        <v>45731066</v>
       </c>
       <c r="O86" t="n">
-        <v>6682880</v>
+        <v>6233276</v>
       </c>
       <c r="P86" t="n">
-        <v>17515458</v>
+        <v>2405937</v>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12289607</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4348499</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
@@ -5892,12 +5878,12 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГРУППА ПОЗИТИВ"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "НАЦПРОЕКТСТРОЙ КАПИТАЛ"</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>9718077239</t>
+          <t>9714070850</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -5910,40 +5896,34 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
+      <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>-2319012</v>
+        <v>-568</v>
       </c>
       <c r="I87" t="n">
-        <v>-3043148</v>
+        <v>-870</v>
       </c>
       <c r="J87" t="n">
-        <v>85073</v>
-      </c>
-      <c r="K87" t="n">
-        <v>20333431</v>
-      </c>
-      <c r="L87" t="n">
-        <v>533431</v>
-      </c>
+        <v>6630</v>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="M87" t="n">
-        <v>3093490</v>
+        <v>69</v>
       </c>
       <c r="N87" t="n">
-        <v>14618010</v>
+        <v>6932</v>
       </c>
       <c r="O87" t="n">
-        <v>6251325</v>
+        <v>6977</v>
       </c>
       <c r="P87" t="n">
-        <v>542917</v>
+        <v>229</v>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/10388722</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12639477</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -5956,56 +5936,54 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ФАБРИКА ПО"</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>9726092897</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "ЛИЗИНГОВАЯ КОМПАНИЯ ПРОСТЫЕ РЕШЕНИЯ"</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>278181110</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2025</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr"/>
+      <c r="F88" t="n">
+        <v>2194489</v>
+      </c>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="n">
-        <v>26111</v>
+        <v>155122</v>
       </c>
       <c r="I88" t="n">
-        <v>-116300</v>
+        <v>-2086627</v>
       </c>
       <c r="J88" t="n">
-        <v>58920</v>
+        <v>463109</v>
       </c>
       <c r="K88" t="n">
-        <v>2012480</v>
+        <v>11391448</v>
       </c>
       <c r="L88" t="n">
-        <v>1961794</v>
+        <v>3335362</v>
       </c>
       <c r="M88" t="n">
-        <v>94487</v>
+        <v>0</v>
       </c>
       <c r="N88" t="n">
-        <v>15655004</v>
+        <v>1453344</v>
       </c>
       <c r="O88" t="n">
-        <v>3749182</v>
+        <v>5990866</v>
       </c>
       <c r="P88" t="n">
-        <v>3460790</v>
+        <v>3989488</v>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12624794</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/508857</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
@@ -6018,18 +5996,14 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "ГЛОРАКС"</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>9729387137</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
+          <t>Общество с ограниченной ответственностью ПРОФЕССИОНАЛЬНАЯ КОЛЛЕКТОРСКАЯ ОРГАНИЗАЦИЯ "СЛУЖБА ЗАЩИТЫ АКТИВОВ"</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2310197022</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2025</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -6037,39 +6011,39 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>3057693</v>
+        <v>429239</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>352891</v>
+        <v>112977</v>
       </c>
       <c r="I89" t="n">
-        <v>-2487508</v>
+        <v>-710830</v>
       </c>
       <c r="J89" t="n">
-        <v>17468</v>
+        <v>8123</v>
       </c>
       <c r="K89" t="n">
-        <v>15888211</v>
+        <v>865965</v>
       </c>
       <c r="L89" t="n">
-        <v>7131352</v>
+        <v>7361</v>
       </c>
       <c r="M89" t="n">
-        <v>3563226</v>
+        <v>110563</v>
       </c>
       <c r="N89" t="n">
-        <v>5262202</v>
+        <v>303889</v>
       </c>
       <c r="O89" t="n">
-        <v>9887498</v>
+        <v>1165803</v>
       </c>
       <c r="P89" t="n">
-        <v>7607515</v>
+        <v>62128</v>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12558009</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10041570</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
@@ -6082,11 +6056,11 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО СБ СЕКЬЮРИТИЗАЦИЯ 3"</t>
+          <t>Общество с ограниченной ответственностью "Восточная Стивидорная Компания"</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9704262880</v>
+        <v>2508064833</v>
       </c>
       <c r="D90" t="n">
         <v>2025</v>
@@ -6096,38 +6070,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr"/>
+      <c r="F90" t="n">
+        <v>10029455</v>
+      </c>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="n">
-        <v>867964</v>
+        <v>2896029</v>
       </c>
       <c r="I90" t="n">
-        <v>-10844</v>
+        <v>2488486</v>
       </c>
       <c r="J90" t="n">
-        <v>1901818</v>
+        <v>266653</v>
       </c>
       <c r="K90" t="n">
-        <v>22434769</v>
+        <v>38468111</v>
       </c>
       <c r="L90" t="n">
-        <v>2918653</v>
+        <v>8468111</v>
       </c>
       <c r="M90" t="n">
-        <v>268761</v>
+        <v>4657692</v>
       </c>
       <c r="N90" t="n">
-        <v>867973</v>
+        <v>72515756</v>
       </c>
       <c r="O90" t="n">
-        <v>5010242</v>
+        <v>6880037</v>
       </c>
       <c r="P90" t="n">
-        <v>2921170</v>
+        <v>9090610</v>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12724282</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2926803</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
@@ -6140,11 +6116,11 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-1"</t>
+          <t>ПАО "АКРОН"</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9704256936</v>
+        <v>5321029508</v>
       </c>
       <c r="D91" t="n">
         <v>2025</v>
@@ -6154,38 +6130,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr"/>
+      <c r="F91" t="n">
+        <v>171997329</v>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>462857</v>
+        <v>52415054</v>
       </c>
       <c r="I91" t="n">
-        <v>-690900</v>
+        <v>25931936</v>
       </c>
       <c r="J91" t="n">
-        <v>1467792</v>
+        <v>11537385</v>
       </c>
       <c r="K91" t="n">
-        <v>12652034</v>
+        <v>135516907</v>
       </c>
       <c r="L91" t="n">
-        <v>2707767</v>
+        <v>63762318</v>
       </c>
       <c r="M91" t="n">
-        <v>740205</v>
+        <v>18287531</v>
       </c>
       <c r="N91" t="n">
-        <v>462867</v>
+        <v>190765693</v>
       </c>
       <c r="O91" t="n">
-        <v>4761718</v>
+        <v>74253156</v>
       </c>
       <c r="P91" t="n">
-        <v>2710789</v>
+        <v>90915954</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12624837</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2347012</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
@@ -6198,11 +6176,11 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО АЛЬФА ФАБРИКА ПК-2"</t>
+          <t>Общество с ограниченной ответственностью профессиональная коллекторская организация "ЗАЩИТА ОНЛАЙН"</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>9704264662</v>
+        <v>5407973637</v>
       </c>
       <c r="D92" t="n">
         <v>2025</v>
@@ -6212,38 +6190,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr"/>
+      <c r="F92" t="n">
+        <v>2905275</v>
+      </c>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="n">
-        <v>966</v>
+        <v>174936</v>
       </c>
       <c r="I92" t="n">
-        <v>-439</v>
+        <v>-496952</v>
       </c>
       <c r="J92" t="n">
-        <v>2571</v>
+        <v>284500</v>
       </c>
       <c r="K92" t="n">
-        <v>3133</v>
+        <v>2598700</v>
       </c>
       <c r="L92" t="n">
-        <v>3133</v>
+        <v>683714</v>
       </c>
       <c r="M92" t="n">
-        <v>133</v>
+        <v>410727</v>
       </c>
       <c r="N92" t="n">
-        <v>-956</v>
+        <v>413426</v>
       </c>
       <c r="O92" t="n">
-        <v>2571</v>
+        <v>3090052</v>
       </c>
       <c r="P92" t="n">
-        <v>3527</v>
+        <v>928735</v>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12755483</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/10947263</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
@@ -6256,11 +6236,11 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО "СБ СЕКЬЮРИТИЗАЦИЯ 5"</t>
+          <t>Акционерное общество "Уральская Сталь"</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>9703163693</v>
+        <v>5607019523</v>
       </c>
       <c r="D93" t="n">
         <v>2025</v>
@@ -6270,32 +6250,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>105454369</v>
+      </c>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="n">
-        <v>-65</v>
+        <v>-27277878</v>
       </c>
       <c r="I93" t="n">
-        <v>-266</v>
+        <v>-1619940</v>
       </c>
       <c r="J93" t="n">
-        <v>13</v>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
+        <v>1224621</v>
+      </c>
+      <c r="K93" t="n">
+        <v>86309927</v>
+      </c>
+      <c r="L93" t="n">
+        <v>78357375</v>
+      </c>
+      <c r="M93" t="n">
+        <v>14118686</v>
+      </c>
       <c r="N93" t="n">
-        <v>13</v>
+        <v>18618354</v>
       </c>
       <c r="O93" t="n">
-        <v>13</v>
+        <v>94532062</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>131566321</v>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12333197</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/4662411</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
@@ -6308,11 +6296,11 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ООО «СФО ВТБ РКС ЭТАЛОН»</t>
+          <t>Общество с ограниченной ответственностью профессиональная коллекторская организация "Вернём"</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>9704147373</v>
+        <v>5611067262</v>
       </c>
       <c r="D94" t="n">
         <v>2025</v>
@@ -6322,38 +6310,40 @@
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr"/>
+      <c r="F94" t="n">
+        <v>1656036</v>
+      </c>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>6112293</v>
+        <v>135809</v>
       </c>
       <c r="I94" t="n">
-        <v>-9926195</v>
+        <v>-443417</v>
       </c>
       <c r="J94" t="n">
-        <v>20467815</v>
+        <v>55363</v>
       </c>
       <c r="K94" t="n">
-        <v>144460215</v>
+        <v>1984195</v>
       </c>
       <c r="L94" t="n">
-        <v>31592025</v>
+        <v>1099128</v>
       </c>
       <c r="M94" t="n">
-        <v>10095850</v>
+        <v>459607</v>
       </c>
       <c r="N94" t="n">
-        <v>9955602</v>
+        <v>271169</v>
       </c>
       <c r="O94" t="n">
-        <v>62360167</v>
+        <v>2394072</v>
       </c>
       <c r="P94" t="n">
-        <v>35761493</v>
+        <v>1179666</v>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11883254</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/7702700</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
@@ -6366,11 +6356,11 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьюритизация 2»</t>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Совком Секьюр"</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>9704160303</v>
+        <v>9703193909</v>
       </c>
       <c r="D95" t="n">
         <v>2025</v>
@@ -6383,35 +6373,35 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>406160</v>
+        <v>764758</v>
       </c>
       <c r="I95" t="n">
-        <v>-1846540</v>
+        <v>35192</v>
       </c>
       <c r="J95" t="n">
-        <v>788495</v>
+        <v>1286080</v>
       </c>
       <c r="K95" t="n">
-        <v>10097440</v>
+        <v>10632078</v>
       </c>
       <c r="L95" t="n">
-        <v>1629792</v>
+        <v>3400068</v>
       </c>
       <c r="M95" t="n">
-        <v>1867484</v>
+        <v>1853940</v>
       </c>
       <c r="N95" t="n">
-        <v>406093</v>
+        <v>764768</v>
       </c>
       <c r="O95" t="n">
-        <v>2587855</v>
+        <v>5356352</v>
       </c>
       <c r="P95" t="n">
-        <v>1629933</v>
+        <v>3590518</v>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/11930756</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12558868</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
@@ -6424,11 +6414,11 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "Специализированное финансовое общество ТБ-5"</t>
+          <t>Общество с ограниченной ответственностью «Специализированное финансовое общество СБ Секьюритизация 2»</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>9703206788</v>
+        <v>9704160303</v>
       </c>
       <c r="D96" t="n">
         <v>2025</v>
@@ -6441,35 +6431,35 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="n">
-        <v>627562</v>
+        <v>406160</v>
       </c>
       <c r="I96" t="n">
-        <v>2054</v>
+        <v>-1846540</v>
       </c>
       <c r="J96" t="n">
-        <v>2567719</v>
+        <v>788495</v>
       </c>
       <c r="K96" t="n">
-        <v>16587377</v>
+        <v>10097440</v>
       </c>
       <c r="L96" t="n">
-        <v>336877</v>
+        <v>1629792</v>
       </c>
       <c r="M96" t="n">
-        <v>337763</v>
+        <v>1867484</v>
       </c>
       <c r="N96" t="n">
-        <v>627572</v>
+        <v>406093</v>
       </c>
       <c r="O96" t="n">
-        <v>6522558</v>
+        <v>2587855</v>
       </c>
       <c r="P96" t="n">
-        <v>636777</v>
+        <v>1629933</v>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/12646488</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11930756</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
@@ -6482,58 +6472,52 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ ООО "ХРОМОС ИНЖИНИРИНГ"</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>5249111131</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное финансовое общество ТБ-5"</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>9703206788</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2025</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>1997642</v>
-      </c>
+      <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr"/>
       <c r="H97" t="n">
-        <v>405970</v>
+        <v>627562</v>
       </c>
       <c r="I97" t="n">
-        <v>94073</v>
+        <v>2054</v>
       </c>
       <c r="J97" t="n">
-        <v>231941</v>
+        <v>2567719</v>
       </c>
       <c r="K97" t="n">
-        <v>1379142</v>
+        <v>16587377</v>
       </c>
       <c r="L97" t="n">
-        <v>318550</v>
+        <v>336877</v>
       </c>
       <c r="M97" t="n">
-        <v>138385</v>
+        <v>337763</v>
       </c>
       <c r="N97" t="n">
-        <v>792684</v>
+        <v>627572</v>
       </c>
       <c r="O97" t="n">
-        <v>2488601</v>
+        <v>6522558</v>
       </c>
       <c r="P97" t="n">
-        <v>1259493</v>
+        <v>636777</v>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2992692</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12646488</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
@@ -6546,58 +6530,52 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "О'КЕЙ"</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>7826087713</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
+          <t>ООО «СФО ВТБ РКС ЭТАЛОН»</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>9704147373</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2025</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>150619116</v>
-      </c>
+      <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr"/>
       <c r="H98" t="n">
-        <v>-1361960</v>
+        <v>6112293</v>
       </c>
       <c r="I98" t="n">
-        <v>7127898</v>
+        <v>-9926195</v>
       </c>
       <c r="J98" t="n">
-        <v>5313318</v>
+        <v>20467815</v>
       </c>
       <c r="K98" t="n">
-        <v>53888334</v>
+        <v>144460215</v>
       </c>
       <c r="L98" t="n">
-        <v>13010079</v>
+        <v>31592025</v>
       </c>
       <c r="M98" t="n">
-        <v>9853935</v>
+        <v>10095850</v>
       </c>
       <c r="N98" t="n">
-        <v>9520347</v>
+        <v>9955602</v>
       </c>
       <c r="O98" t="n">
-        <v>36805981</v>
+        <v>62360167</v>
       </c>
       <c r="P98" t="n">
-        <v>44805029</v>
+        <v>35761493</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/3965165</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/11883254</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
@@ -6610,58 +6588,52 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Общество с ограниченной ответственностью "СУЭК-Финанс"</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>7709851798</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "СПЕЦИАЛИЗИРОВАННОЕ ФИНАНСОВОЕ ОБЩЕСТВО СБ СЕКЬЮРИТИЗАЦИЯ 3"</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>9704262880</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2025</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>5282365</v>
-      </c>
+      <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="n">
-        <v>23992</v>
+        <v>867964</v>
       </c>
       <c r="I99" t="n">
-        <v>16794</v>
+        <v>-10844</v>
       </c>
       <c r="J99" t="n">
-        <v>162</v>
+        <v>1901818</v>
       </c>
       <c r="K99" t="n">
-        <v>77330378</v>
+        <v>22434769</v>
       </c>
       <c r="L99" t="n">
-        <v>20423888</v>
+        <v>2918653</v>
       </c>
       <c r="M99" t="n">
-        <v>70</v>
+        <v>268761</v>
       </c>
       <c r="N99" t="n">
-        <v>78439</v>
+        <v>867973</v>
       </c>
       <c r="O99" t="n">
-        <v>20503494</v>
+        <v>5010242</v>
       </c>
       <c r="P99" t="n">
-        <v>20425556</v>
+        <v>2921170</v>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/4697028</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12724282</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
@@ -6674,58 +6646,52 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>АО "ЮЖУРАЛЗОЛОТО ГРУППА КОМПАНИЙ"</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>7424024375</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Сплит Финанс"</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>9703209122</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2025</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>29914981</v>
-      </c>
+      <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>-16323173</v>
+        <v>832800</v>
       </c>
       <c r="I100" t="n">
-        <v>4075973</v>
+        <v>-627668</v>
       </c>
       <c r="J100" t="n">
-        <v>320549</v>
+        <v>3157507</v>
       </c>
       <c r="K100" t="n">
-        <v>47336871</v>
+        <v>12321587</v>
       </c>
       <c r="L100" t="n">
-        <v>38107992</v>
+        <v>4622403</v>
       </c>
       <c r="M100" t="n">
-        <v>2025312</v>
+        <v>794736</v>
       </c>
       <c r="N100" t="n">
-        <v>2048905</v>
+        <v>832810</v>
       </c>
       <c r="O100" t="n">
-        <v>14377840</v>
+        <v>10288657</v>
       </c>
       <c r="P100" t="n">
-        <v>44953151</v>
+        <v>4649009</v>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6540211</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12663922</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -6738,58 +6704,52 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ТАТНЕФТЕХИМ"</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>1655201119</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+          <t>Общество с ограниченной ответственностью "Специализированное Финансовое общество Тб-6"</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>9703221553</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2025</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>тыс. руб.</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>4756836</v>
-      </c>
+      <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>137122</v>
+        <v>421691</v>
       </c>
       <c r="I101" t="n">
-        <v>-327274</v>
+        <v>-16243</v>
       </c>
       <c r="J101" t="n">
-        <v>192</v>
+        <v>1996969</v>
       </c>
       <c r="K101" t="n">
-        <v>870000</v>
+        <v>31400566</v>
       </c>
       <c r="L101" t="n">
-        <v>270000</v>
+        <v>191416</v>
       </c>
       <c r="M101" t="n">
-        <v>95489</v>
+        <v>191760</v>
       </c>
       <c r="N101" t="n">
-        <v>1268161</v>
+        <v>421701</v>
       </c>
       <c r="O101" t="n">
-        <v>1241059</v>
+        <v>11406621</v>
       </c>
       <c r="P101" t="n">
-        <v>401385</v>
+        <v>592089</v>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2882491</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/12744848</t>
         </is>
       </c>
       <c r="R101" t="inlineStr">
@@ -6802,18 +6762,14 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Публичное акционерное общество "Газпром Нефть"</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>5504036333</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+          <t>Общество с ограниченной ответственностью Профессиональная коллекторская организация "Филберт"</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>7841430420</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2025</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -6821,39 +6777,39 @@
         </is>
       </c>
       <c r="F102" t="n">
-        <v>2675243941</v>
+        <v>8586868</v>
       </c>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="n">
-        <v>344113223</v>
+        <v>3152859</v>
       </c>
       <c r="I102" t="n">
-        <v>-672668577</v>
+        <v>-2961381</v>
       </c>
       <c r="J102" t="n">
-        <v>120090279</v>
+        <v>130669</v>
       </c>
       <c r="K102" t="n">
-        <v>1018546168</v>
+        <v>4275711</v>
       </c>
       <c r="L102" t="n">
-        <v>523221951</v>
+        <v>2275535</v>
       </c>
       <c r="M102" t="n">
-        <v>48313469</v>
+        <v>560901</v>
       </c>
       <c r="N102" t="n">
-        <v>570812953</v>
+        <v>9134906</v>
       </c>
       <c r="O102" t="n">
-        <v>1115163466</v>
+        <v>13555399</v>
       </c>
       <c r="P102" t="n">
-        <v>1356076017</v>
+        <v>2486647</v>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/6934659</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/1655225</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
@@ -6866,17 +6822,17 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "МЕГАФОН"</t>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "О'КЕЙ"</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>7812014560</t>
+          <t>7826087713</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6885,39 +6841,39 @@
         </is>
       </c>
       <c r="F103" t="n">
-        <v>313180311</v>
+        <v>150619116</v>
       </c>
       <c r="G103" t="inlineStr"/>
       <c r="H103" t="n">
-        <v>86019524</v>
+        <v>-1361960</v>
       </c>
       <c r="I103" t="n">
-        <v>155410658</v>
+        <v>7127898</v>
       </c>
       <c r="J103" t="n">
-        <v>31269439</v>
+        <v>5313318</v>
       </c>
       <c r="K103" t="n">
-        <v>313939374</v>
+        <v>53888334</v>
       </c>
       <c r="L103" t="n">
-        <v>130147165</v>
+        <v>13010079</v>
       </c>
       <c r="M103" t="n">
-        <v>24378644</v>
+        <v>9853935</v>
       </c>
       <c r="N103" t="n">
-        <v>169102679</v>
+        <v>9520347</v>
       </c>
       <c r="O103" t="n">
-        <v>112536728</v>
+        <v>36805981</v>
       </c>
       <c r="P103" t="n">
-        <v>195346733</v>
+        <v>44805029</v>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/7044659</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/3965165</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
@@ -6930,18 +6886,14 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Открытое акционерное общество "Российские железные дороги"</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>7708503727</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ ООО "ХРОМОС ИНЖИНИРИНГ"</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>5249111131</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2024</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -6949,39 +6901,39 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>1963646793</v>
+        <v>1997642</v>
       </c>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="n">
-        <v>18763461</v>
+        <v>405970</v>
       </c>
       <c r="I104" t="n">
-        <v>363885889</v>
+        <v>94073</v>
       </c>
       <c r="J104" t="n">
-        <v>46487763</v>
+        <v>231941</v>
       </c>
       <c r="K104" t="n">
-        <v>1551144333</v>
+        <v>1379142</v>
       </c>
       <c r="L104" t="n">
-        <v>270362395</v>
+        <v>318550</v>
       </c>
       <c r="M104" t="n">
-        <v>81423187</v>
+        <v>138385</v>
       </c>
       <c r="N104" t="n">
-        <v>4886001379</v>
+        <v>792684</v>
       </c>
       <c r="O104" t="n">
-        <v>316228921</v>
+        <v>2488601</v>
       </c>
       <c r="P104" t="n">
-        <v>859557402</v>
+        <v>1259493</v>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>https://bo.nalog.gov.ru/organizations-card/2432297</t>
+          <t>https://bo.nalog.gov.ru/organizations-card/2992692</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
@@ -6994,17 +6946,17 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ОБЛАЧНЫЕ ТЕХНОЛОГИИ"</t>
+          <t>Общество с ограниченной ответственностью "СУЭК-Финанс"</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>7736279160</t>
+          <t>7709851798</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2021</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7013,40 +6965,420 @@
         </is>
       </c>
       <c r="F105" t="n">
-        <v>8856359</v>
+        <v>5282365</v>
       </c>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="n">
+        <v>23992</v>
+      </c>
+      <c r="I105" t="n">
+        <v>16794</v>
+      </c>
+      <c r="J105" t="n">
+        <v>162</v>
+      </c>
+      <c r="K105" t="n">
+        <v>77330378</v>
+      </c>
+      <c r="L105" t="n">
+        <v>20423888</v>
+      </c>
+      <c r="M105" t="n">
+        <v>70</v>
+      </c>
+      <c r="N105" t="n">
+        <v>78439</v>
+      </c>
+      <c r="O105" t="n">
+        <v>20503494</v>
+      </c>
+      <c r="P105" t="n">
+        <v>20425556</v>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/4697028</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>АО "ЮЖУРАЛЗОЛОТО ГРУППА КОМПАНИЙ"</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>7424024375</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>29914981</v>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="n">
+        <v>-16323173</v>
+      </c>
+      <c r="I106" t="n">
+        <v>4075973</v>
+      </c>
+      <c r="J106" t="n">
+        <v>320549</v>
+      </c>
+      <c r="K106" t="n">
+        <v>47336871</v>
+      </c>
+      <c r="L106" t="n">
+        <v>38107992</v>
+      </c>
+      <c r="M106" t="n">
+        <v>2025312</v>
+      </c>
+      <c r="N106" t="n">
+        <v>2048905</v>
+      </c>
+      <c r="O106" t="n">
+        <v>14377840</v>
+      </c>
+      <c r="P106" t="n">
+        <v>44953151</v>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6540211</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Публичное акционерное общество "Газпром Нефть"</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5504036333</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>2675243941</v>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="n">
+        <v>344113223</v>
+      </c>
+      <c r="I107" t="n">
+        <v>-672668577</v>
+      </c>
+      <c r="J107" t="n">
+        <v>120090279</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1018546168</v>
+      </c>
+      <c r="L107" t="n">
+        <v>523221951</v>
+      </c>
+      <c r="M107" t="n">
+        <v>48313469</v>
+      </c>
+      <c r="N107" t="n">
+        <v>570812953</v>
+      </c>
+      <c r="O107" t="n">
+        <v>1115163466</v>
+      </c>
+      <c r="P107" t="n">
+        <v>1356076017</v>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/6934659</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Открытое акционерное общество "Российские железные дороги"</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>7708503727</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1963646793</v>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="n">
+        <v>18763461</v>
+      </c>
+      <c r="I108" t="n">
+        <v>363885889</v>
+      </c>
+      <c r="J108" t="n">
+        <v>46487763</v>
+      </c>
+      <c r="K108" t="n">
+        <v>1551144333</v>
+      </c>
+      <c r="L108" t="n">
+        <v>270362395</v>
+      </c>
+      <c r="M108" t="n">
+        <v>81423187</v>
+      </c>
+      <c r="N108" t="n">
+        <v>4886001379</v>
+      </c>
+      <c r="O108" t="n">
+        <v>316228921</v>
+      </c>
+      <c r="P108" t="n">
+        <v>859557402</v>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2432297</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr"/>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>ПУБЛИЧНОЕ АКЦИОНЕРНОЕ ОБЩЕСТВО "МЕГАФОН"</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>7812014560</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>313180311</v>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="n">
+        <v>86019524</v>
+      </c>
+      <c r="I109" t="n">
+        <v>155410658</v>
+      </c>
+      <c r="J109" t="n">
+        <v>31269439</v>
+      </c>
+      <c r="K109" t="n">
+        <v>313939374</v>
+      </c>
+      <c r="L109" t="n">
+        <v>130147165</v>
+      </c>
+      <c r="M109" t="n">
+        <v>24378644</v>
+      </c>
+      <c r="N109" t="n">
+        <v>169102679</v>
+      </c>
+      <c r="O109" t="n">
+        <v>112536728</v>
+      </c>
+      <c r="P109" t="n">
+        <v>195346733</v>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/7044659</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr"/>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ОБЛАЧНЫЕ ТЕХНОЛОГИИ"</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>7736279160</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>8856359</v>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="n">
         <v>393267</v>
       </c>
-      <c r="I105" t="n">
+      <c r="I110" t="n">
         <v>4817063</v>
       </c>
-      <c r="J105" t="n">
+      <c r="J110" t="n">
         <v>6339347</v>
       </c>
-      <c r="K105" t="n">
+      <c r="K110" t="n">
         <v>1000000</v>
       </c>
-      <c r="L105" t="n">
+      <c r="L110" t="n">
         <v>1000000</v>
       </c>
-      <c r="M105" t="inlineStr"/>
-      <c r="N105" t="n">
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="n">
         <v>19810081</v>
       </c>
-      <c r="O105" t="n">
+      <c r="O110" t="n">
         <v>8064422</v>
       </c>
-      <c r="P105" t="n">
+      <c r="P110" t="n">
         <v>3490434</v>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>https://bo.nalog.gov.ru/organizations-card/9940825</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr"/>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>ОБЩЕСТВО С ОГРАНИЧЕННОЙ ОТВЕТСТВЕННОСТЬЮ "ТАТНЕФТЕХИМ"</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>1655201119</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>тыс. руб.</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>4756836</v>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="n">
+        <v>137122</v>
+      </c>
+      <c r="I111" t="n">
+        <v>-327274</v>
+      </c>
+      <c r="J111" t="n">
+        <v>192</v>
+      </c>
+      <c r="K111" t="n">
+        <v>870000</v>
+      </c>
+      <c r="L111" t="n">
+        <v>270000</v>
+      </c>
+      <c r="M111" t="n">
+        <v>95489</v>
+      </c>
+      <c r="N111" t="n">
+        <v>1268161</v>
+      </c>
+      <c r="O111" t="n">
+        <v>1241059</v>
+      </c>
+      <c r="P111" t="n">
+        <v>401385</v>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>https://bo.nalog.gov.ru/organizations-card/2882491</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
         <is>
           <t>Автоматически из публичного JSON ГИР БО ФНС; значения форм БФО в тыс. руб.; общий долг = заёмные средства строк 1410+1510; EBITDA в стандартной бухгалтерской отчётности не публикуется и не рассчитывается искусственно</t>
         </is>
